--- a/casas_candidatas.xlsx
+++ b/casas_candidatas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U89"/>
+  <dimension ref="A1:U88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4201744792-vive-a-minutos-de-mall-los-dominicos-excelente-ubicacion-y-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2059394253-solida-cercana-al-metro-los-dominicos-bajo-valor-tasacion-_JM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rotonda Atenas</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>21.20102720971212</v>
+        <v>22.73443282500916</v>
       </c>
       <c r="F2" t="n">
-        <v>173181877</v>
+        <v>592249344</v>
       </c>
       <c r="G2" t="n">
-        <v>4240</v>
+        <v>14500</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -559,49 +559,49 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>251993734.4952614</v>
+        <v>816844224.6119645</v>
       </c>
       <c r="J2" t="n">
-        <v>371736032.95579</v>
+        <v>987906240.4622535</v>
       </c>
       <c r="K2" t="n">
-        <v>679322966.0906751</v>
+        <v>1249752218.579044</v>
       </c>
       <c r="L2" t="n">
-        <v>114.9550201516879</v>
+        <v>43.82075709578638</v>
       </c>
       <c r="M2" t="n">
-        <v>-53.41267414326868</v>
+        <v>-40.0500452631133</v>
       </c>
       <c r="N2" t="n">
-        <v>153</v>
+        <v>530</v>
       </c>
       <c r="O2" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="P2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S2" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-33.4131298</v>
+        <v>-33.4119286</v>
       </c>
       <c r="U2" t="n">
-        <v>-70.54787109999999</v>
+        <v>-70.54692420000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2059394253-solida-cercana-al-metro-los-dominicos-bajo-valor-tasacion-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4201744792-vive-a-minutos-de-mall-los-dominicos-excelente-ubicacion-y-_JM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>Rotonda Atenas</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>16.7206830607942</v>
+        <v>18.99475869940124</v>
       </c>
       <c r="F3" t="n">
-        <v>592249344</v>
+        <v>173181877</v>
       </c>
       <c r="G3" t="n">
-        <v>14500</v>
+        <v>4240</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -634,59 +634,59 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>757434015.4055009</v>
+        <v>243792239.458679</v>
       </c>
       <c r="J3" t="n">
-        <v>987906240.4622535</v>
+        <v>371736032.95579</v>
       </c>
       <c r="K3" t="n">
-        <v>1206531757.873781</v>
+        <v>583142164.3818694</v>
       </c>
       <c r="L3" t="n">
-        <v>45.45955112685</v>
+        <v>91.28787495387859</v>
       </c>
       <c r="M3" t="n">
-        <v>-40.0500452631133</v>
+        <v>-53.41267414326868</v>
       </c>
       <c r="N3" t="n">
-        <v>530</v>
+        <v>153</v>
       </c>
       <c r="O3" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q3" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R3" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="T3" t="n">
-        <v>-33.4119286</v>
+        <v>-33.4131298</v>
       </c>
       <c r="U3" t="n">
-        <v>-70.54692420000001</v>
+        <v>-70.54787109999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3853061210-excelente-casa-condominio-el-arrayan-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2059405379-gran-potencial-para-remodelar-las-tranqueras-con-las-condes-_JM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Camino A Farellones</t>
+          <t>Metro Hernando De Magallanes</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -695,73 +695,73 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12.83363813837309</v>
+        <v>12.84014173976164</v>
       </c>
       <c r="F4" t="n">
-        <v>694361299</v>
+        <v>540000000</v>
       </c>
       <c r="G4" t="n">
-        <v>17000</v>
+        <v>540000000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>UF</t>
+          <t>CLP</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>819280868.752176</v>
+        <v>629142024.8129748</v>
       </c>
       <c r="J4" t="n">
-        <v>973376126.1248401</v>
+        <v>694244865.9809703</v>
       </c>
       <c r="K4" t="n">
-        <v>1686778729.410371</v>
+        <v>899928762.4531304</v>
       </c>
       <c r="L4" t="n">
-        <v>89.1225742418645</v>
+        <v>39.00449983991355</v>
       </c>
       <c r="M4" t="n">
-        <v>-28.66464664955787</v>
+        <v>-22.21764589688708</v>
       </c>
       <c r="N4" t="n">
-        <v>1600</v>
+        <v>444</v>
       </c>
       <c r="O4" t="n">
-        <v>240</v>
+        <v>138</v>
       </c>
       <c r="P4" t="n">
         <v>3</v>
       </c>
       <c r="Q4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="T4" t="n">
-        <v>-33.3617057</v>
+        <v>-33.4006389</v>
       </c>
       <c r="U4" t="n">
-        <v>-70.47811590000001</v>
+        <v>-70.5579754</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3915739572-terreno-en-valle-escondido-precio-unico-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1913092679-casa-en-venta-de-5-dorm-en-las-condes-_JM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Valle Escondido</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -770,13 +770,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12.68013294784363</v>
+        <v>12.57283472142889</v>
       </c>
       <c r="F5" t="n">
-        <v>693952852</v>
+        <v>448884158</v>
       </c>
       <c r="G5" t="n">
-        <v>16990</v>
+        <v>10990</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -784,49 +784,49 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>985655527.8428923</v>
+        <v>519235879.5224249</v>
       </c>
       <c r="J5" t="n">
-        <v>2300470168.907014</v>
+        <v>559553379.0205544</v>
       </c>
       <c r="K5" t="n">
-        <v>3632743436.04513</v>
+        <v>747423212.0288947</v>
       </c>
       <c r="L5" t="n">
-        <v>115.0672564234948</v>
+        <v>40.78026173407982</v>
       </c>
       <c r="M5" t="n">
-        <v>-69.83430337939541</v>
+        <v>-19.77813469990486</v>
       </c>
       <c r="N5" t="n">
-        <v>2040</v>
+        <v>224</v>
       </c>
       <c r="O5" t="n">
-        <v>2040</v>
+        <v>140</v>
       </c>
       <c r="P5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q5" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-33.3448698</v>
+        <v>-33.3891264</v>
       </c>
       <c r="U5" t="n">
-        <v>-70.4937958</v>
+        <v>-70.5402646</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4182508496-linda-casa-en-exelente-sector-del-arrayan-175378-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1973911663-linda-casa-con-jardin-y-piscina-cercana-colegios-y-plazas-_JM</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>El Arrayán</t>
+          <t>Plaza San Enrique</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -845,13 +845,13 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10.76784179779212</v>
+        <v>10.73430695296489</v>
       </c>
       <c r="F6" t="n">
-        <v>702530256</v>
+        <v>420292810</v>
       </c>
       <c r="G6" t="n">
-        <v>17200</v>
+        <v>10290</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -859,59 +859,59 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>793918510.7473966</v>
+        <v>477362322.1141524</v>
       </c>
       <c r="J6" t="n">
-        <v>848714686.4113026</v>
+        <v>531655302.6126143</v>
       </c>
       <c r="K6" t="n">
-        <v>1648102448.834332</v>
+        <v>757803290.6873889</v>
       </c>
       <c r="L6" t="n">
-        <v>100.644415816434</v>
+        <v>52.74864507042775</v>
       </c>
       <c r="M6" t="n">
-        <v>-17.22421359637683</v>
+        <v>-20.94637109145088</v>
       </c>
       <c r="N6" t="n">
-        <v>1770</v>
+        <v>240</v>
       </c>
       <c r="O6" t="n">
-        <v>284</v>
+        <v>140</v>
       </c>
       <c r="P6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="n">
         <v>3</v>
       </c>
       <c r="R6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="T6" t="n">
-        <v>-33.3617083</v>
+        <v>-33.3656109</v>
       </c>
       <c r="U6" t="n">
-        <v>-70.48556809999999</v>
+        <v>-70.49900359999999</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3535169326-entorno-natural-cerca-del-newland-y-los-alerces-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4201733452-excelente-oportunidad-las-condes-ureta-bravo-propiedades-_JM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Colón Oriente - Vital Apoquindo</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -920,63 +920,63 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>8.128803483192272</v>
+        <v>10.23783523159774</v>
       </c>
       <c r="F7" t="n">
-        <v>898585211</v>
+        <v>175000000</v>
       </c>
       <c r="G7" t="n">
-        <v>22000</v>
+        <v>175000000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>UF</t>
+          <t>CLP</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1008532944.073853</v>
+        <v>207900497.4138709</v>
       </c>
       <c r="J7" t="n">
-        <v>1352569702.308454</v>
+        <v>321361856.9707766</v>
       </c>
       <c r="K7" t="n">
-        <v>2252039138.023772</v>
+        <v>584071925.9789529</v>
       </c>
       <c r="L7" t="n">
-        <v>91.93657020614954</v>
+        <v>117.0554066717661</v>
       </c>
       <c r="M7" t="n">
-        <v>-33.56459120248151</v>
+        <v>-45.54425293356647</v>
       </c>
       <c r="N7" t="n">
-        <v>1425</v>
+        <v>160</v>
       </c>
       <c r="O7" t="n">
-        <v>332</v>
+        <v>60</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="T7" t="n">
-        <v>-33.36167</v>
+        <v>-33.4130798</v>
       </c>
       <c r="U7" t="n">
-        <v>-70.52240999999999</v>
+        <v>-70.5363143</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4096296848-casa-estilo-colonial-en-calle-tranquila-en-el-arrayan-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3915739572-terreno-en-valle-escondido-precio-unico-_JM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Camino A Farellones</t>
+          <t>Valle Escondido</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8.026405834759975</v>
+        <v>8.784736699381178</v>
       </c>
       <c r="F8" t="n">
-        <v>702530256</v>
+        <v>693952852</v>
       </c>
       <c r="G8" t="n">
-        <v>17200</v>
+        <v>16990</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1009,49 +1009,49 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>775006598.9837503</v>
+        <v>896043099.1862906</v>
       </c>
       <c r="J8" t="n">
-        <v>902973815.127524</v>
+        <v>2300470168.907014</v>
       </c>
       <c r="K8" t="n">
-        <v>1729196341.812504</v>
+        <v>4650360596.862105</v>
       </c>
       <c r="L8" t="n">
-        <v>105.6719172630711</v>
+        <v>163.1978344435366</v>
       </c>
       <c r="M8" t="n">
-        <v>-22.19815854784405</v>
+        <v>-69.83430337939541</v>
       </c>
       <c r="N8" t="n">
-        <v>1760</v>
+        <v>2040</v>
       </c>
       <c r="O8" t="n">
-        <v>348</v>
+        <v>2040</v>
       </c>
       <c r="P8" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q8" t="n">
         <v>6</v>
       </c>
-      <c r="Q8" t="n">
-        <v>4</v>
-      </c>
       <c r="R8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-33.3609338</v>
+        <v>-33.3448698</v>
       </c>
       <c r="U8" t="n">
-        <v>-70.47830380000001</v>
+        <v>-70.4937958</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4152912686-casa-en-venta-en-el-huinganal-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1918940429-dehesa-central-a-pasos-del-portal-condominio-cerrado-_JM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>El Huinganal</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1070,63 +1070,63 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>7.913108925347917</v>
+        <v>8.461613750963808</v>
       </c>
       <c r="F9" t="n">
-        <v>785000000</v>
+        <v>653516517</v>
       </c>
       <c r="G9" t="n">
-        <v>785000000</v>
+        <v>16000</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>UF</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>865145012.8353792</v>
+        <v>714022291.6463907</v>
       </c>
       <c r="J9" t="n">
-        <v>1012813214.015697</v>
+        <v>715061883.313911</v>
       </c>
       <c r="K9" t="n">
-        <v>1644974093.607007</v>
+        <v>956923020.5890279</v>
       </c>
       <c r="L9" t="n">
-        <v>76.99633752601706</v>
+        <v>33.96918988562619</v>
       </c>
       <c r="M9" t="n">
-        <v>-22.49311233928733</v>
+        <v>-8.606998603908615</v>
       </c>
       <c r="N9" t="n">
-        <v>900</v>
+        <v>412</v>
       </c>
       <c r="O9" t="n">
-        <v>375</v>
+        <v>152</v>
       </c>
       <c r="P9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
         <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="T9" t="n">
-        <v>-33.3382633</v>
+        <v>-33.3554101</v>
       </c>
       <c r="U9" t="n">
-        <v>-70.49861850000001</v>
+        <v>-70.5156223</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2046359361-casa-en-venta-los-dominicosseguridad-247-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2057119567-bajo-precio-ideal-remodelar-ubicacion-colegios-terreno-_JM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>Sebastián Elcano</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6.115890867967883</v>
+        <v>7.768761615388793</v>
       </c>
       <c r="F10" t="n">
-        <v>608587257</v>
+        <v>551404561</v>
       </c>
       <c r="G10" t="n">
-        <v>14900</v>
+        <v>13500</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1159,59 +1159,59 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>651865538.138082</v>
+        <v>603622524.7366664</v>
       </c>
       <c r="J10" t="n">
-        <v>707636582.6727388</v>
+        <v>672152993.2548093</v>
       </c>
       <c r="K10" t="n">
-        <v>1006508905.702043</v>
+        <v>1045314597.480842</v>
       </c>
       <c r="L10" t="n">
-        <v>50.11659603923741</v>
+        <v>65.71302622716024</v>
       </c>
       <c r="M10" t="n">
-        <v>-13.99720253277892</v>
+        <v>-17.9644267698789</v>
       </c>
       <c r="N10" t="n">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="O10" t="n">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="P10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q10" t="n">
         <v>3</v>
       </c>
       <c r="R10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="T10" t="n">
-        <v>-33.4095244</v>
+        <v>-33.4266283</v>
       </c>
       <c r="U10" t="n">
-        <v>-70.5351452</v>
+        <v>-70.56975559999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4050080372-casa-en-venta-de-5-dorm-en-santa-maria-manquehue-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3851356140-casa-en-venta-de-4-dorm-en-lo-barnechea-las-lomas-_JM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Santa María De Manquehue</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5.574204360769952</v>
+        <v>7.621723872489305</v>
       </c>
       <c r="F11" t="n">
-        <v>1037457471</v>
+        <v>1135484948</v>
       </c>
       <c r="G11" t="n">
-        <v>25400</v>
+        <v>27800</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1234,25 +1234,25 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1248721261.545048</v>
+        <v>1271574560.305465</v>
       </c>
       <c r="J11" t="n">
-        <v>3790025927.859347</v>
+        <v>1785548972.6764</v>
       </c>
       <c r="K11" t="n">
-        <v>7076000126.589165</v>
+        <v>2468145616.618157</v>
       </c>
       <c r="L11" t="n">
-        <v>153.7530079203293</v>
+        <v>67.01418301168881</v>
       </c>
       <c r="M11" t="n">
-        <v>-72.62663921705757</v>
+        <v>-36.40695576677487</v>
       </c>
       <c r="N11" t="n">
-        <v>400000</v>
+        <v>2158</v>
       </c>
       <c r="O11" t="n">
-        <v>250000</v>
+        <v>460</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
@@ -1261,32 +1261,32 @@
         <v>5</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="T11" t="n">
-        <v>-33.3784956</v>
+        <v>-33.341676</v>
       </c>
       <c r="U11" t="n">
-        <v>-70.578636</v>
+        <v>-70.5324222</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4034196578-casa-en-venta-de-5-dorm-espectacular-vista-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1999203389-en-condominio-con-piscina-y-vistas-_JM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5.545042657686344</v>
+        <v>7.368471554592512</v>
       </c>
       <c r="F12" t="n">
-        <v>853655950</v>
+        <v>673938908</v>
       </c>
       <c r="G12" t="n">
-        <v>20900</v>
+        <v>16500</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1309,49 +1309,49 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>912692625.6437713</v>
+        <v>733985863.6822748</v>
       </c>
       <c r="J12" t="n">
-        <v>1064674868.85672</v>
+        <v>814917384.6623542</v>
       </c>
       <c r="K12" t="n">
-        <v>1318769394.752226</v>
+        <v>1051674085.690798</v>
       </c>
       <c r="L12" t="n">
-        <v>38.14091803862259</v>
+        <v>38.98410170009461</v>
       </c>
       <c r="M12" t="n">
-        <v>-19.82003379898681</v>
+        <v>-17.29972624412302</v>
       </c>
       <c r="N12" t="n">
-        <v>900</v>
+        <v>392</v>
       </c>
       <c r="O12" t="n">
-        <v>300</v>
+        <v>190</v>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="T12" t="n">
-        <v>-33.4042302</v>
+        <v>-33.3333379</v>
       </c>
       <c r="U12" t="n">
-        <v>-70.52972269999999</v>
+        <v>-70.5110471</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1913092679-casa-en-venta-de-5-dorm-en-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3762939998-amplia-casa-en-san-carlos-de-apoquindo-_JM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5.529455108265359</v>
+        <v>7.353637492009218</v>
       </c>
       <c r="F13" t="n">
-        <v>448884158</v>
+        <v>774008625</v>
       </c>
       <c r="G13" t="n">
-        <v>10990</v>
+        <v>18950</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1384,49 +1384,49 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>479824410.8997235</v>
+        <v>845269079.8858881</v>
       </c>
       <c r="J13" t="n">
-        <v>559553379.0205544</v>
+        <v>969050418.4265652</v>
       </c>
       <c r="K13" t="n">
-        <v>788029562.9276601</v>
+        <v>1086138660.46817</v>
       </c>
       <c r="L13" t="n">
-        <v>55.08056310327726</v>
+        <v>24.85624855034676</v>
       </c>
       <c r="M13" t="n">
-        <v>-19.77813469990486</v>
+        <v>-20.12710481496433</v>
       </c>
       <c r="N13" t="n">
-        <v>224</v>
+        <v>524</v>
       </c>
       <c r="O13" t="n">
-        <v>140</v>
+        <v>250</v>
       </c>
       <c r="P13" t="n">
         <v>5</v>
       </c>
       <c r="Q13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="T13" t="n">
-        <v>-33.3891264</v>
+        <v>-33.4013109</v>
       </c>
       <c r="U13" t="n">
-        <v>-70.5402646</v>
+        <v>-70.5172651</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4109455262-2-casas-a-pasos-del-metro-los-dominicos-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4179308246-exclusiva-casa-en-venta-en-las-condes-con-gran-terreno-_JM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>Sebastián Elcano</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5.337611070726759</v>
+        <v>7.167052683256014</v>
       </c>
       <c r="F14" t="n">
-        <v>694361299</v>
+        <v>445208127</v>
       </c>
       <c r="G14" t="n">
-        <v>17000</v>
+        <v>10900</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1459,59 +1459,59 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>752979247.9258503</v>
+        <v>498447751.0819235</v>
       </c>
       <c r="J14" t="n">
-        <v>1098205698.18829</v>
+        <v>742838464.2170169</v>
       </c>
       <c r="K14" t="n">
-        <v>1764467985.440061</v>
+        <v>1481077544.650872</v>
       </c>
       <c r="L14" t="n">
-        <v>92.10375972214165</v>
+        <v>132.2804136973012</v>
       </c>
       <c r="M14" t="n">
-        <v>-36.77311088938185</v>
+        <v>-40.06662976596559</v>
       </c>
       <c r="N14" t="n">
-        <v>526</v>
+        <v>368</v>
       </c>
       <c r="O14" t="n">
-        <v>526</v>
+        <v>368</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R14" t="n">
         <v>4</v>
       </c>
       <c r="S14" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="T14" t="n">
-        <v>-33.4021417</v>
+        <v>-33.4258973</v>
       </c>
       <c r="U14" t="n">
-        <v>-70.54351819999999</v>
+        <v>-70.57036069999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1909455733-los-litres-sta-martina-370-m2-construidos-en-680-m2-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1698705917-casa-en-venta-los-dominicos-_JM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>4.395281519007387</v>
+        <v>6.890160576531251</v>
       </c>
       <c r="F15" t="n">
-        <v>894500733</v>
+        <v>735206082</v>
       </c>
       <c r="G15" t="n">
-        <v>21900</v>
+        <v>18000</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1534,49 +1534,49 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>943184138.6870017</v>
+        <v>789806255.1590754</v>
       </c>
       <c r="J15" t="n">
-        <v>1107628839.619724</v>
+        <v>792436875.0570254</v>
       </c>
       <c r="K15" t="n">
-        <v>1578445666.502804</v>
+        <v>914314798.7013974</v>
       </c>
       <c r="L15" t="n">
-        <v>57.35328524254597</v>
+        <v>15.71210874473278</v>
       </c>
       <c r="M15" t="n">
-        <v>-19.24183435787895</v>
+        <v>-7.222126437882763</v>
       </c>
       <c r="N15" t="n">
-        <v>680</v>
+        <v>507</v>
       </c>
       <c r="O15" t="n">
-        <v>370</v>
+        <v>184</v>
       </c>
       <c r="P15" t="n">
         <v>4</v>
       </c>
       <c r="Q15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R15" t="n">
         <v>3</v>
       </c>
       <c r="S15" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="T15" t="n">
-        <v>-33.3164187</v>
+        <v>-33.4149605</v>
       </c>
       <c r="U15" t="n">
-        <v>-70.5500026</v>
+        <v>-70.53007049999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2059405379-gran-potencial-para-remodelar-las-tranqueras-con-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4034196578-casa-en-venta-de-5-dorm-espectacular-vista-_JM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Metro Hernando De Magallanes</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1595,73 +1595,73 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4.334878317723978</v>
+        <v>5.556951655170388</v>
       </c>
       <c r="F16" t="n">
-        <v>540000000</v>
+        <v>853655950</v>
       </c>
       <c r="G16" t="n">
-        <v>540000000</v>
+        <v>20900</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>UF</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>570094670.167321</v>
+        <v>912819417.7471167</v>
       </c>
       <c r="J16" t="n">
-        <v>694244865.9809703</v>
+        <v>1064674868.85672</v>
       </c>
       <c r="K16" t="n">
-        <v>945683215.5012082</v>
+        <v>1183409571.735484</v>
       </c>
       <c r="L16" t="n">
-        <v>54.10029857450647</v>
+        <v>25.41528516390505</v>
       </c>
       <c r="M16" t="n">
-        <v>-22.21764589688708</v>
+        <v>-19.82003379898681</v>
       </c>
       <c r="N16" t="n">
-        <v>444</v>
+        <v>900</v>
       </c>
       <c r="O16" t="n">
-        <v>138</v>
+        <v>300</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S16" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="T16" t="n">
-        <v>-33.4006389</v>
+        <v>-33.4042302</v>
       </c>
       <c r="U16" t="n">
-        <v>-70.5579754</v>
+        <v>-70.52972269999999</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1973911663-linda-casa-con-jardin-y-piscina-cercana-colegios-y-plazas-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2046359361-casa-en-venta-los-dominicosseguridad-247-_JM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plaza San Enrique</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3.66206311672694</v>
+        <v>4.90252759964082</v>
       </c>
       <c r="F17" t="n">
-        <v>420292810</v>
+        <v>608587257</v>
       </c>
       <c r="G17" t="n">
-        <v>10290</v>
+        <v>14900</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1684,49 +1684,49 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>439762362.7450995</v>
+        <v>643279335.7706861</v>
       </c>
       <c r="J17" t="n">
-        <v>531655302.6126143</v>
+        <v>707636582.6727388</v>
       </c>
       <c r="K17" t="n">
-        <v>823745214.478808</v>
+        <v>936345925.1473588</v>
       </c>
       <c r="L17" t="n">
-        <v>72.2240236948213</v>
+        <v>41.4148443640042</v>
       </c>
       <c r="M17" t="n">
-        <v>-20.94637109145088</v>
+        <v>-13.99720253277892</v>
       </c>
       <c r="N17" t="n">
-        <v>240</v>
+        <v>446</v>
       </c>
       <c r="O17" t="n">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="P17" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="T17" t="n">
-        <v>-33.3656109</v>
+        <v>-33.4095244</v>
       </c>
       <c r="U17" t="n">
-        <v>-70.49900359999999</v>
+        <v>-70.5351452</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1918940429-dehesa-central-a-pasos-del-portal-condominio-cerrado-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1904332139-casa-sector-el-monasterio-la-dehesa-_JM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3.659165183373462</v>
+        <v>4.464948680290737</v>
       </c>
       <c r="F18" t="n">
-        <v>653516517</v>
+        <v>1061555892</v>
       </c>
       <c r="G18" t="n">
-        <v>16000</v>
+        <v>25990</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1759,59 +1759,59 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>679681812.4737972</v>
+        <v>1121600032.29404</v>
       </c>
       <c r="J18" t="n">
-        <v>715061883.313911</v>
+        <v>1344789035.517647</v>
       </c>
       <c r="K18" t="n">
-        <v>1025367127.289963</v>
+        <v>1714780605.121176</v>
       </c>
       <c r="L18" t="n">
-        <v>48.34341235112518</v>
+        <v>44.10956344530312</v>
       </c>
       <c r="M18" t="n">
-        <v>-8.606998603908615</v>
+        <v>-21.06152980408729</v>
       </c>
       <c r="N18" t="n">
-        <v>412</v>
+        <v>1100</v>
       </c>
       <c r="O18" t="n">
-        <v>152</v>
+        <v>470</v>
       </c>
       <c r="P18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T18" t="n">
-        <v>-33.3554101</v>
+        <v>-33.3499985</v>
       </c>
       <c r="U18" t="n">
-        <v>-70.5156223</v>
+        <v>-70.51667019999999</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3899584074-casa-en-venta-de-5-dorm-en-lo-barnecheacondominiocolegios-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3806992554-casa-cercana-metro-colon-_JM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>El Huinganal</t>
+          <t>Barrio El Golf</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3.472815112680095</v>
+        <v>4.382564037673125</v>
       </c>
       <c r="F19" t="n">
-        <v>796473255</v>
+        <v>608587257</v>
       </c>
       <c r="G19" t="n">
-        <v>19500</v>
+        <v>14900</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1834,59 +1834,59 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>828230777.5216694</v>
+        <v>645829490.2166635</v>
       </c>
       <c r="J19" t="n">
-        <v>914460502.251183</v>
+        <v>849781837.6759381</v>
       </c>
       <c r="K19" t="n">
-        <v>1428090145.558603</v>
+        <v>1083888542.157176</v>
       </c>
       <c r="L19" t="n">
-        <v>65.59707790114754</v>
+        <v>51.54958984985569</v>
       </c>
       <c r="M19" t="n">
-        <v>-12.902388562516</v>
+        <v>-28.38311787594559</v>
       </c>
       <c r="N19" t="n">
-        <v>1156.66</v>
+        <v>375</v>
       </c>
       <c r="O19" t="n">
-        <v>315.48</v>
+        <v>170</v>
       </c>
       <c r="P19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="T19" t="n">
-        <v>-33.339371</v>
+        <v>-33.4241535</v>
       </c>
       <c r="U19" t="n">
-        <v>-70.50438560000001</v>
+        <v>-70.5920527</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4188277328-casa-en-venta-en-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1997594621-gran-terreno-potencial-de-remodelacion-_JM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>El Arrayán</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2.800634322539829</v>
+        <v>4.334237393219198</v>
       </c>
       <c r="F20" t="n">
-        <v>755628473</v>
+        <v>673530460</v>
       </c>
       <c r="G20" t="n">
-        <v>18500</v>
+        <v>16490</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1909,25 +1909,25 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>778849321.5116858</v>
+        <v>708008655.8721253</v>
       </c>
       <c r="J20" t="n">
-        <v>829128184.4545634</v>
+        <v>795484712.629389</v>
       </c>
       <c r="K20" t="n">
-        <v>1615235889.041779</v>
+        <v>947648623.4418827</v>
       </c>
       <c r="L20" t="n">
-        <v>100.8754235125061</v>
+        <v>30.12502487667593</v>
       </c>
       <c r="M20" t="n">
-        <v>-8.86469822551198</v>
+        <v>-15.33081034659766</v>
       </c>
       <c r="N20" t="n">
-        <v>1500</v>
+        <v>385</v>
       </c>
       <c r="O20" t="n">
-        <v>280</v>
+        <v>240</v>
       </c>
       <c r="P20" t="n">
         <v>5</v>
@@ -1936,32 +1936,32 @@
         <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S20" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="T20" t="n">
-        <v>-33.3619686</v>
+        <v>-33.3996367</v>
       </c>
       <c r="U20" t="n">
-        <v>-70.4865558</v>
+        <v>-70.5496942</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2045838433-amplia-casa-para-remodelar-en-las-condes-con-terreno-434-mt2-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3741540074-condominio-camino-la-laguna-_JM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>El Huinganal</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1970,13 +1970,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2.485185353562911</v>
+        <v>4.061434387716982</v>
       </c>
       <c r="F21" t="n">
-        <v>550587666</v>
+        <v>755220025</v>
       </c>
       <c r="G21" t="n">
-        <v>13480</v>
+        <v>18490</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -1984,59 +1984,59 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>567671027.7872732</v>
+        <v>791367514.2885705</v>
       </c>
       <c r="J21" t="n">
-        <v>687407953.8084124</v>
+        <v>890017807.4497908</v>
       </c>
       <c r="K21" t="n">
-        <v>951241687.1726829</v>
+        <v>1025459338.564049</v>
       </c>
       <c r="L21" t="n">
-        <v>55.79956665620933</v>
+        <v>26.30192590710438</v>
       </c>
       <c r="M21" t="n">
-        <v>-19.9037975994304</v>
+        <v>-15.14551521570486</v>
       </c>
       <c r="N21" t="n">
-        <v>434</v>
+        <v>831</v>
       </c>
       <c r="O21" t="n">
-        <v>164</v>
+        <v>242</v>
       </c>
       <c r="P21" t="n">
         <v>5</v>
       </c>
       <c r="Q21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S21" t="n">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="T21" t="n">
-        <v>-33.4031717</v>
+        <v>-33.3421149</v>
       </c>
       <c r="U21" t="n">
-        <v>-70.54493549999999</v>
+        <v>-70.4964981</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2004175013-casa-en-venta-tipo-castilo-velasco-con-vista-al-valle-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4191864430-amplia-casa-de-4-dorm-mas-servicio-piscina-en-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>El Remanso</t>
+          <t>El Huinganal</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2.363346298889625</v>
+        <v>3.751275940012375</v>
       </c>
       <c r="F22" t="n">
-        <v>771966386</v>
+        <v>836909590</v>
       </c>
       <c r="G22" t="n">
-        <v>18900</v>
+        <v>20490</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2059,59 +2059,59 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>798439765.897283</v>
+        <v>870767702.5803556</v>
       </c>
       <c r="J22" t="n">
-        <v>1120165077.361747</v>
+        <v>902575900.0881163</v>
       </c>
       <c r="K22" t="n">
-        <v>1636791918.822593</v>
+        <v>1109808438.380666</v>
       </c>
       <c r="L22" t="n">
-        <v>74.84183982059385</v>
+        <v>26.48428079865346</v>
       </c>
       <c r="M22" t="n">
-        <v>-31.08458729867184</v>
+        <v>-7.275433576467691</v>
       </c>
       <c r="N22" t="n">
-        <v>1200</v>
+        <v>950</v>
       </c>
       <c r="O22" t="n">
-        <v>300</v>
+        <v>234</v>
       </c>
       <c r="P22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q22" t="n">
         <v>5</v>
       </c>
       <c r="R22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="T22" t="n">
-        <v>-33.4220764</v>
+        <v>-33.3446935</v>
       </c>
       <c r="U22" t="n">
-        <v>-70.5238011</v>
+        <v>-70.5094564</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3819933524-casa-en-pie-andinolos-litres-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1943852377-casa-en-venta-de-4-dorm-amplia-sector-tabancura-_JM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>La Llavería</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1.959190031594937</v>
+        <v>3.415558755318286</v>
       </c>
       <c r="F23" t="n">
-        <v>806684451</v>
+        <v>530982170</v>
       </c>
       <c r="G23" t="n">
-        <v>19750</v>
+        <v>13000</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2134,25 +2134,25 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>823692988.6379058</v>
+        <v>551184638.4746212</v>
       </c>
       <c r="J23" t="n">
-        <v>868141291.2283721</v>
+        <v>591483558.6758503</v>
       </c>
       <c r="K23" t="n">
-        <v>1381646136.367141</v>
+        <v>681514442.6273643</v>
       </c>
       <c r="L23" t="n">
-        <v>64.26985484583525</v>
+        <v>22.0343916988177</v>
       </c>
       <c r="M23" t="n">
-        <v>-7.079128806488868</v>
+        <v>-10.22875239529807</v>
       </c>
       <c r="N23" t="n">
-        <v>831</v>
+        <v>248</v>
       </c>
       <c r="O23" t="n">
-        <v>258</v>
+        <v>112</v>
       </c>
       <c r="P23" t="n">
         <v>4</v>
@@ -2164,29 +2164,29 @@
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="T23" t="n">
-        <v>-33.3145823</v>
+        <v>-33.3846327</v>
       </c>
       <c r="U23" t="n">
-        <v>-70.5465047</v>
+        <v>-70.54068580000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3762939998-amplia-casa-en-san-carlos-de-apoquindo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1909455733-los-litres-sta-martina-370-m2-construidos-en-680-m2-_JM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1.595831270821897</v>
+        <v>3.114137308495647</v>
       </c>
       <c r="F24" t="n">
-        <v>774008625</v>
+        <v>894500733</v>
       </c>
       <c r="G24" t="n">
-        <v>18950</v>
+        <v>21900</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2209,49 +2209,49 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>789473034.6072816</v>
+        <v>928993815.9342552</v>
       </c>
       <c r="J24" t="n">
-        <v>969050418.4265652</v>
+        <v>1107628839.619724</v>
       </c>
       <c r="K24" t="n">
-        <v>1180906345.504298</v>
+        <v>1569785379.327997</v>
       </c>
       <c r="L24" t="n">
-        <v>40.39349278983669</v>
+        <v>57.85255317239131</v>
       </c>
       <c r="M24" t="n">
-        <v>-20.12710481496433</v>
+        <v>-19.24183435787895</v>
       </c>
       <c r="N24" t="n">
-        <v>524</v>
+        <v>680</v>
       </c>
       <c r="O24" t="n">
-        <v>250</v>
+        <v>370</v>
       </c>
       <c r="P24" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q24" t="n">
         <v>5</v>
       </c>
-      <c r="Q24" t="n">
-        <v>4</v>
-      </c>
       <c r="R24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S24" t="n">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="T24" t="n">
-        <v>-33.4013109</v>
+        <v>-33.3164187</v>
       </c>
       <c r="U24" t="n">
-        <v>-70.5172651</v>
+        <v>-70.5500026</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3763892940-las-condes-abadia-c423752-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4201709018-oportunidad-venta-de-casa-en-las-condes-_JM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Alto Las Condes</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2270,73 +2270,73 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1.466679864660099</v>
+        <v>2.989365320366729</v>
       </c>
       <c r="F25" t="n">
-        <v>490137388</v>
+        <v>544900000</v>
       </c>
       <c r="G25" t="n">
-        <v>12000</v>
+        <v>544900000</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>UF</t>
+          <t>CLP</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>498270162.5187379</v>
+        <v>567736420.3343048</v>
       </c>
       <c r="J25" t="n">
-        <v>554502363.7876567</v>
+        <v>763922033.17269</v>
       </c>
       <c r="K25" t="n">
-        <v>757460279.1723225</v>
+        <v>918519176.6651314</v>
       </c>
       <c r="L25" t="n">
-        <v>46.74283349905429</v>
+        <v>45.91865937862401</v>
       </c>
       <c r="M25" t="n">
-        <v>-11.6077008848072</v>
+        <v>-28.67073126076186</v>
       </c>
       <c r="N25" t="n">
-        <v>338</v>
+        <v>456</v>
       </c>
       <c r="O25" t="n">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="P25" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q25" t="n">
         <v>5</v>
       </c>
-      <c r="Q25" t="n">
-        <v>4</v>
-      </c>
       <c r="R25" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S25" t="n">
-        <v>57</v>
+        <v>38</v>
       </c>
       <c r="T25" t="n">
-        <v>-33.392259</v>
+        <v>-33.4131876</v>
       </c>
       <c r="U25" t="n">
-        <v>-70.541263</v>
+        <v>-70.53248859999999</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4080762354-nuevo-valor-casa-remodelada-cerro-mirador-los-dominicos-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4050080372-casa-en-venta-de-5-dorm-en-santa-maria-manquehue-_JM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>Santa María De Manquehue</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1.142186185748493</v>
+        <v>2.934522477883208</v>
       </c>
       <c r="F26" t="n">
-        <v>1057879862</v>
+        <v>1037457471</v>
       </c>
       <c r="G26" t="n">
-        <v>25900</v>
+        <v>25400</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2359,49 +2359,49 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1074292081.093807</v>
+        <v>1148676633.770634</v>
       </c>
       <c r="J26" t="n">
-        <v>1436912764.187526</v>
+        <v>3790025927.859347</v>
       </c>
       <c r="K26" t="n">
-        <v>2297208478.88182</v>
+        <v>5439576117.710694</v>
       </c>
       <c r="L26" t="n">
-        <v>85.10721236995118</v>
+        <v>113.2155707009533</v>
       </c>
       <c r="M26" t="n">
-        <v>-26.37828208046036</v>
+        <v>-72.62663921705757</v>
       </c>
       <c r="N26" t="n">
-        <v>1000</v>
+        <v>400000</v>
       </c>
       <c r="O26" t="n">
-        <v>463.94</v>
+        <v>250000</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>-33.4102389</v>
+        <v>-33.3784956</v>
       </c>
       <c r="U26" t="n">
-        <v>-70.5278795</v>
+        <v>-70.578636</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1593441569-cercana-a-colegios-en-condominio-el-huinganal-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4146264354-casa-en-venta-de-3-dorm-en-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>El Huinganal</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2420,13 +2420,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>0.7191276547594285</v>
+        <v>2.673378228474488</v>
       </c>
       <c r="F27" t="n">
-        <v>796473255</v>
+        <v>633094126</v>
       </c>
       <c r="G27" t="n">
-        <v>19500</v>
+        <v>15500</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -2434,59 +2434,59 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>803057835.2355198</v>
+        <v>650689063.167962</v>
       </c>
       <c r="J27" t="n">
-        <v>915634406.7622489</v>
+        <v>658153679.1373575</v>
       </c>
       <c r="K27" t="n">
-        <v>1448838189.22385</v>
+        <v>786270173.8758413</v>
       </c>
       <c r="L27" t="n">
-        <v>70.52818780279978</v>
+        <v>20.60022073956733</v>
       </c>
       <c r="M27" t="n">
-        <v>-13.0140535220396</v>
+        <v>-3.807553453200026</v>
       </c>
       <c r="N27" t="n">
-        <v>1153</v>
+        <v>390</v>
       </c>
       <c r="O27" t="n">
-        <v>315</v>
+        <v>140</v>
       </c>
       <c r="P27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R27" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S27" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="T27" t="n">
-        <v>-33.3386649</v>
+        <v>-33.3330308</v>
       </c>
       <c r="U27" t="n">
-        <v>-70.5036473</v>
+        <v>-70.50358439999999</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4201707858-casa-con-gran-frente-a-blaise-cendrars-para-remodelar-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3152801196-venta-casa-425-mts-en-las-condes-_JM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Nuestra Señora Del Rosario</t>
+          <t>Metro Hernando De Magallanes</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>0.6767429057910912</v>
+        <v>2.667794865584999</v>
       </c>
       <c r="F28" t="n">
-        <v>510559779</v>
+        <v>649432039</v>
       </c>
       <c r="G28" t="n">
-        <v>12500</v>
+        <v>15900</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2509,59 +2509,59 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>515257468.1204659</v>
+        <v>668997000.1642915</v>
       </c>
       <c r="J28" t="n">
-        <v>694161561.2467313</v>
+        <v>733375771.0040894</v>
       </c>
       <c r="K28" t="n">
-        <v>872535484.9977365</v>
+        <v>951841477.3938806</v>
       </c>
       <c r="L28" t="n">
-        <v>51.46900042053473</v>
+        <v>38.56746955825078</v>
       </c>
       <c r="M28" t="n">
-        <v>-26.44943086692642</v>
+        <v>-11.44621015896928</v>
       </c>
       <c r="N28" t="n">
-        <v>350</v>
+        <v>429</v>
       </c>
       <c r="O28" t="n">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S28" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="T28" t="n">
-        <v>-33.3925691</v>
+        <v>-33.4116124</v>
       </c>
       <c r="U28" t="n">
-        <v>-70.5680502</v>
+        <v>-70.55844020000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2057119567-bajo-precio-ideal-remodelar-ubicacion-colegios-terreno-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4201707858-casa-con-gran-frente-a-blaise-cendrars-para-remodelar-_JM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sebastián Elcano</t>
+          <t>Nuestra Señora Del Rosario</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>0.631608749328788</v>
+        <v>2.126736767206013</v>
       </c>
       <c r="F29" t="n">
-        <v>551404561</v>
+        <v>510559779</v>
       </c>
       <c r="G29" t="n">
-        <v>13500</v>
+        <v>12500</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2584,59 +2584,59 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>555649938.1142727</v>
+        <v>525322768.1468455</v>
       </c>
       <c r="J29" t="n">
-        <v>672152993.2548093</v>
+        <v>694161561.2467313</v>
       </c>
       <c r="K29" t="n">
-        <v>933884674.522019</v>
+        <v>851587346.6210884</v>
       </c>
       <c r="L29" t="n">
-        <v>56.2721196220813</v>
+        <v>47.00124534240467</v>
       </c>
       <c r="M29" t="n">
-        <v>-17.9644267698789</v>
+        <v>-26.44943086692642</v>
       </c>
       <c r="N29" t="n">
-        <v>420</v>
+        <v>350</v>
       </c>
       <c r="O29" t="n">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R29" t="n">
         <v>2</v>
       </c>
       <c r="S29" t="n">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="T29" t="n">
-        <v>-33.4266283</v>
+        <v>-33.3925691</v>
       </c>
       <c r="U29" t="n">
-        <v>-70.56975559999999</v>
+        <v>-70.5680502</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4105686464-casa-para-remodelar-barrio-residencial-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3853061210-excelente-casa-condominio-el-arrayan-_JM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Alto Las Condes</t>
+          <t>Camino A Farellones</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>0.3883868676365134</v>
+        <v>1.632282615948746</v>
       </c>
       <c r="F30" t="n">
-        <v>324716019</v>
+        <v>694361299</v>
       </c>
       <c r="G30" t="n">
-        <v>7950</v>
+        <v>17000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2659,49 +2659,49 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>326473951.9184968</v>
+        <v>710249548.2945311</v>
       </c>
       <c r="J30" t="n">
-        <v>452624191.2334729</v>
+        <v>973376126.1248401</v>
       </c>
       <c r="K30" t="n">
-        <v>752293983.4561238</v>
+        <v>1311124325.043917</v>
       </c>
       <c r="L30" t="n">
-        <v>94.07805410868556</v>
+        <v>61.73099592462378</v>
       </c>
       <c r="M30" t="n">
-        <v>-28.25924347633801</v>
+        <v>-28.66464664955787</v>
       </c>
       <c r="N30" t="n">
-        <v>212</v>
+        <v>1600</v>
       </c>
       <c r="O30" t="n">
-        <v>82</v>
+        <v>240</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>-33.3917603</v>
+        <v>-33.3617057</v>
       </c>
       <c r="U30" t="n">
-        <v>-70.5398996</v>
+        <v>-70.47811590000001</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3815592662-casa-en-venta-la-fragua-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4152912686-casa-en-venta-en-el-huinganal-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2711,7 +2711,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>El Huinganal</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2720,63 +2720,63 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>0.0703859623125454</v>
+        <v>1.45377093067777</v>
       </c>
       <c r="F31" t="n">
-        <v>972105819</v>
+        <v>785000000</v>
       </c>
       <c r="G31" t="n">
-        <v>23800</v>
+        <v>785000000</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>UF</t>
+          <t>CLP</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>973156050.9324774</v>
+        <v>799723984.0874234</v>
       </c>
       <c r="J31" t="n">
-        <v>1492104246.318111</v>
+        <v>1012813214.015697</v>
       </c>
       <c r="K31" t="n">
-        <v>2585771850.504198</v>
+        <v>1680335636.098593</v>
       </c>
       <c r="L31" t="n">
-        <v>108.0766175386862</v>
+        <v>86.94709348426031</v>
       </c>
       <c r="M31" t="n">
-        <v>-34.85000653280422</v>
+        <v>-22.49311233928733</v>
       </c>
       <c r="N31" t="n">
-        <v>778</v>
+        <v>900</v>
       </c>
       <c r="O31" t="n">
-        <v>778</v>
+        <v>375</v>
       </c>
       <c r="P31" t="n">
         <v>4</v>
       </c>
       <c r="Q31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="T31" t="n">
-        <v>-33.3503046</v>
+        <v>-33.3382633</v>
       </c>
       <c r="U31" t="n">
-        <v>-70.53169939999999</v>
+        <v>-70.49861850000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4139251760-unica-casa-th-4d-condominio-los-trapenses-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1986959355-estupenda-casa-en-venta-en-condominio-los-trapenses-_JM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2795,13 +2795,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>0.04516879313014872</v>
+        <v>1.410226505129124</v>
       </c>
       <c r="F32" t="n">
-        <v>714783691</v>
+        <v>816895646</v>
       </c>
       <c r="G32" t="n">
-        <v>17500</v>
+        <v>20000</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -2809,74 +2809,74 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>715233012.1709107</v>
+        <v>830340240.9083152</v>
       </c>
       <c r="J32" t="n">
-        <v>994760186.7865905</v>
+        <v>953364219.1106143</v>
       </c>
       <c r="K32" t="n">
-        <v>1184387322.137912</v>
+        <v>1449352340.870064</v>
       </c>
       <c r="L32" t="n">
-        <v>47.16255397017115</v>
+        <v>64.92923560097732</v>
       </c>
       <c r="M32" t="n">
-        <v>-28.14512477534998</v>
+        <v>-14.31442153743978</v>
       </c>
       <c r="N32" t="n">
-        <v>500</v>
+        <v>680</v>
       </c>
       <c r="O32" t="n">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="P32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T32" t="n">
-        <v>-33.3246571</v>
+        <v>-33.336787</v>
       </c>
       <c r="U32" t="n">
-        <v>-70.55433600000001</v>
+        <v>-70.56188539999999</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1858517657-casa-en-venta-en-la-dehesa-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3915799524-venta-de-hermosa-casa-las-condes-_JM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>-0.1489122214132169</v>
+        <v>0.7713096669800797</v>
       </c>
       <c r="F33" t="n">
-        <v>1919296321</v>
+        <v>436630723</v>
       </c>
       <c r="G33" t="n">
-        <v>46990</v>
+        <v>10690</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2884,74 +2884,74 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1116466840.654515</v>
+        <v>440550386.0672882</v>
       </c>
       <c r="J33" t="n">
-        <v>1517509062.750676</v>
+        <v>508182800.6428178</v>
       </c>
       <c r="K33" t="n">
-        <v>1917036564.544511</v>
+        <v>672732451.5180762</v>
       </c>
       <c r="L33" t="n">
-        <v>52.75551517556425</v>
+        <v>45.68869020303186</v>
       </c>
       <c r="M33" t="n">
-        <v>26.47676169531624</v>
+        <v>-14.07998805790143</v>
       </c>
       <c r="N33" t="n">
-        <v>1000</v>
+        <v>221</v>
       </c>
       <c r="O33" t="n">
-        <v>393</v>
+        <v>133.3</v>
       </c>
       <c r="P33" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q33" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S33" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="T33" t="n">
-        <v>-33.343515</v>
+        <v>-33.3900576</v>
       </c>
       <c r="U33" t="n">
-        <v>-70.5262723</v>
+        <v>-70.5403834</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1960121903-exclusivo-proyecto-izquierdo-lehmann-el-golf-sin-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4188212420-casa-en-venta-de-6-dorm-en-lo-barnechea-imperdible-_JM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Barrio El Golf</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>-0.3820980432548965</v>
+        <v>0.5487967310330348</v>
       </c>
       <c r="F34" t="n">
-        <v>995183121</v>
+        <v>1123231514</v>
       </c>
       <c r="G34" t="n">
-        <v>24365</v>
+        <v>27500</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2959,74 +2959,74 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>600193585.492065</v>
+        <v>1131920214.219915</v>
       </c>
       <c r="J34" t="n">
-        <v>845297043.2404426</v>
+        <v>1583227400.709801</v>
       </c>
       <c r="K34" t="n">
-        <v>991953257.5380868</v>
+        <v>2229606744.262478</v>
       </c>
       <c r="L34" t="n">
-        <v>46.34579940611324</v>
+        <v>69.3322089770833</v>
       </c>
       <c r="M34" t="n">
-        <v>17.73176411276322</v>
+        <v>-29.05431566580853</v>
       </c>
       <c r="N34" t="n">
-        <v>235</v>
+        <v>1300</v>
       </c>
       <c r="O34" t="n">
-        <v>160</v>
+        <v>475</v>
       </c>
       <c r="P34" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q34" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R34" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S34" t="n">
-        <v>2</v>
+        <v>33</v>
       </c>
       <c r="T34" t="n">
-        <v>-33.418302</v>
+        <v>-33.3504593</v>
       </c>
       <c r="U34" t="n">
-        <v>-70.58902</v>
+        <v>-70.53181840000001</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3854955990-sta-maria-de-manquehue-antilhue-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3527137746-casa-en-venta-en-sebastian-elcano-las-condes-_JM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Santa María De Manquehue</t>
+          <t>Sebastián Elcano</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>-0.6596594765739846</v>
+        <v>0.4718782176411309</v>
       </c>
       <c r="F35" t="n">
-        <v>2246463027</v>
+        <v>639220843</v>
       </c>
       <c r="G35" t="n">
-        <v>55000</v>
+        <v>15650</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3034,49 +3034,49 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1170319177.726994</v>
+        <v>642544614.1979997</v>
       </c>
       <c r="J35" t="n">
-        <v>1662539200.21128</v>
+        <v>704370550.2268987</v>
       </c>
       <c r="K35" t="n">
-        <v>2235495929.614049</v>
+        <v>1182982215.942188</v>
       </c>
       <c r="L35" t="n">
-        <v>64.06927137427432</v>
+        <v>76.72631991358772</v>
       </c>
       <c r="M35" t="n">
-        <v>35.12240954766738</v>
+        <v>-9.249351382722065</v>
       </c>
       <c r="N35" t="n">
-        <v>1000</v>
+        <v>369</v>
       </c>
       <c r="O35" t="n">
-        <v>560</v>
+        <v>190</v>
       </c>
       <c r="P35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R35" t="n">
         <v>3</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="T35" t="n">
-        <v>-33.3725774</v>
+        <v>-33.4283312</v>
       </c>
       <c r="U35" t="n">
-        <v>-70.5744251</v>
+        <v>-70.57098999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3927242992-casa-en-condominio-san-carlos-de-apoquindo-5d-5b-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3583745698-casa-en-venta-san-carlos-de-apoquindo-_JM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3091,17 +3091,17 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>-0.6851820658076324</v>
+        <v>0.156677500839355</v>
       </c>
       <c r="F36" t="n">
-        <v>894500733</v>
+        <v>755628473</v>
       </c>
       <c r="G36" t="n">
-        <v>21900</v>
+        <v>18500</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3109,74 +3109,74 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>640122682.8136743</v>
+        <v>756994078.2264291</v>
       </c>
       <c r="J36" t="n">
-        <v>738515965.9174603</v>
+        <v>871602635.4219749</v>
       </c>
       <c r="K36" t="n">
-        <v>889440554.0484076</v>
+        <v>941589122.9923725</v>
       </c>
       <c r="L36" t="n">
-        <v>33.75930687226308</v>
+        <v>21.17880755105498</v>
       </c>
       <c r="M36" t="n">
-        <v>21.12138048210771</v>
+        <v>-13.30585265679326</v>
       </c>
       <c r="N36" t="n">
-        <v>372</v>
+        <v>497</v>
       </c>
       <c r="O36" t="n">
-        <v>180</v>
+        <v>185.85</v>
       </c>
       <c r="P36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R36" t="n">
         <v>2</v>
       </c>
       <c r="S36" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="T36" t="n">
-        <v>-33.3883239</v>
+        <v>-33.38872</v>
       </c>
       <c r="U36" t="n">
-        <v>-70.49293419999999</v>
+        <v>-70.50438</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4099822016-casa-en-venta-en-los-trapenses-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1978119201-colegio-aleman-_JM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>Estadio Manquehue</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>-1.115212294355993</v>
+        <v>0.05037357321248355</v>
       </c>
       <c r="F37" t="n">
-        <v>1838015204</v>
+        <v>449292605</v>
       </c>
       <c r="G37" t="n">
-        <v>45000</v>
+        <v>11000</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3184,59 +3184,59 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1025774050.912396</v>
+        <v>449554327.3519086</v>
       </c>
       <c r="J37" t="n">
-        <v>1482025497.788356</v>
+        <v>519562808.8652339</v>
       </c>
       <c r="K37" t="n">
-        <v>1821487473.443174</v>
+        <v>735593008.258764</v>
       </c>
       <c r="L37" t="n">
-        <v>53.69094011663294</v>
+        <v>55.05372517551563</v>
       </c>
       <c r="M37" t="n">
-        <v>24.02048458295026</v>
+        <v>-13.52487180880201</v>
       </c>
       <c r="N37" t="n">
-        <v>1062</v>
+        <v>194</v>
       </c>
       <c r="O37" t="n">
-        <v>410</v>
+        <v>96</v>
       </c>
       <c r="P37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R37" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S37" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>-33.3438006</v>
+        <v>-33.3971055</v>
       </c>
       <c r="U37" t="n">
-        <v>-70.5455882</v>
+        <v>-70.57425310000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1797087177-casa-con-5-dorm-y-4-banos-en-santuario-del-valle-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1955676239-casa-de-lujo-en-venta-en-cerro-san-luis-_JM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>Barrio El Golf</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3245,13 +3245,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-1.380160075332888</v>
+        <v>-0.4773337327212747</v>
       </c>
       <c r="F38" t="n">
-        <v>1878859987</v>
+        <v>1307033034</v>
       </c>
       <c r="G38" t="n">
-        <v>46000</v>
+        <v>32000</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3259,59 +3259,59 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>1166245562.648281</v>
+        <v>658159871.2906245</v>
       </c>
       <c r="J38" t="n">
-        <v>1647064110.101618</v>
+        <v>820690047.7590786</v>
       </c>
       <c r="K38" t="n">
-        <v>1856127865.737241</v>
+        <v>1303115603.56096</v>
       </c>
       <c r="L38" t="n">
-        <v>41.88557681864587</v>
+        <v>78.58700541470049</v>
       </c>
       <c r="M38" t="n">
-        <v>14.07327592634393</v>
+        <v>59.26025148823201</v>
       </c>
       <c r="N38" t="n">
-        <v>1434</v>
+        <v>317</v>
       </c>
       <c r="O38" t="n">
-        <v>479</v>
+        <v>173</v>
       </c>
       <c r="P38" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S38" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="T38" t="n">
-        <v>-33.3236865</v>
+        <v>-33.4115008</v>
       </c>
       <c r="U38" t="n">
-        <v>-70.5503396</v>
+        <v>-70.59783849999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3990910568-casa-en-venta-con-gran-ubicacion-en-vitacura-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4143696762-condominio-nueva-3-dorm-estar-family-room-servicios-_JM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Jardín Del Este</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3320,13 +3320,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-1.406507801607911</v>
+        <v>-0.5706967295539646</v>
       </c>
       <c r="F39" t="n">
-        <v>1021119558</v>
+        <v>898585211</v>
       </c>
       <c r="G39" t="n">
-        <v>25000</v>
+        <v>22000</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3334,59 +3334,59 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>583149139.4418882</v>
+        <v>639411175.3669966</v>
       </c>
       <c r="J39" t="n">
-        <v>828490005.0917866</v>
+        <v>773624728.6491828</v>
       </c>
       <c r="K39" t="n">
-        <v>1009466781.442842</v>
+        <v>894170159.9745784</v>
       </c>
       <c r="L39" t="n">
-        <v>51.45718589009691</v>
+        <v>32.93056376990604</v>
       </c>
       <c r="M39" t="n">
-        <v>23.25067915416462</v>
+        <v>16.15259669491295</v>
       </c>
       <c r="N39" t="n">
-        <v>288</v>
+        <v>325</v>
       </c>
       <c r="O39" t="n">
-        <v>200</v>
+        <v>168</v>
       </c>
       <c r="P39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R39" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="T39" t="n">
-        <v>-33.3848883</v>
+        <v>-33.3868028</v>
       </c>
       <c r="U39" t="n">
-        <v>-70.5770651</v>
+        <v>-70.518474</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4100162976-casa-en-venta-en-vitacura-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1709323389-venta-casa-san-carlos-de-apoquindo-_JM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3395,13 +3395,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.797165704537034</v>
+        <v>-1.171603518302364</v>
       </c>
       <c r="F40" t="n">
-        <v>3063358674</v>
+        <v>916965363</v>
       </c>
       <c r="G40" t="n">
-        <v>75000</v>
+        <v>22450</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3409,28 +3409,28 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>1045175861.755335</v>
+        <v>608402379.8034436</v>
       </c>
       <c r="J40" t="n">
-        <v>2583416419.910332</v>
+        <v>744587637.4853662</v>
       </c>
       <c r="K40" t="n">
-        <v>3016930400.095993</v>
+        <v>908241748.042377</v>
       </c>
       <c r="L40" t="n">
-        <v>76.32352737036081</v>
+        <v>40.2691843302094</v>
       </c>
       <c r="M40" t="n">
-        <v>18.57781232598677</v>
+        <v>23.15076383712073</v>
       </c>
       <c r="N40" t="n">
-        <v>5500</v>
+        <v>400</v>
       </c>
       <c r="O40" t="n">
-        <v>650</v>
+        <v>160</v>
       </c>
       <c r="P40" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q40" t="n">
         <v>3</v>
@@ -3439,19 +3439,19 @@
         <v>2</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="T40" t="n">
-        <v>-33.3616399</v>
+        <v>-33.3970927</v>
       </c>
       <c r="U40" t="n">
-        <v>-70.5605438</v>
+        <v>-70.50746479999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4179281400-moderna-elegante-a-estrenar-gran-vista-desde-cada-rincon-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3968105340-mediterranea-cerca-de-santiago-college-en-golf-de-manquehue-_JM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3470,13 +3470,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-2.250273884383382</v>
+        <v>-1.704475891532858</v>
       </c>
       <c r="F41" t="n">
-        <v>2446602461</v>
+        <v>1552101728</v>
       </c>
       <c r="G41" t="n">
-        <v>59900</v>
+        <v>38000</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3484,49 +3484,49 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1194386714.560243</v>
+        <v>1062673616.468726</v>
       </c>
       <c r="J41" t="n">
-        <v>1942687588.326237</v>
+        <v>1267219195.058656</v>
       </c>
       <c r="K41" t="n">
-        <v>2402886669.544737</v>
+        <v>1530502282.327348</v>
       </c>
       <c r="L41" t="n">
-        <v>62.20763246990748</v>
+        <v>36.9177382794433</v>
       </c>
       <c r="M41" t="n">
-        <v>25.93905863721101</v>
+        <v>22.48091995861522</v>
       </c>
       <c r="N41" t="n">
-        <v>1400</v>
+        <v>840</v>
       </c>
       <c r="O41" t="n">
-        <v>492</v>
+        <v>325</v>
       </c>
       <c r="P41" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q41" t="n">
         <v>5</v>
       </c>
       <c r="R41" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S41" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="T41" t="n">
-        <v>-33.3377104</v>
+        <v>-33.33126</v>
       </c>
       <c r="U41" t="n">
-        <v>-70.555567</v>
+        <v>-70.54414</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4088013424-oportunidad-completamente-remodelada-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3894147344-club-manquehue-_JM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>La Llavería</t>
+          <t>Estadio Manquehue</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3545,7 +3545,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.993964662866813</v>
+        <v>-2.143453602299109</v>
       </c>
       <c r="F42" t="n">
         <v>771966386</v>
@@ -3559,59 +3559,59 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>525151759.0133949</v>
+        <v>599299294.9065548</v>
       </c>
       <c r="J42" t="n">
-        <v>647147478.5854679</v>
+        <v>647462843.6281235</v>
       </c>
       <c r="K42" t="n">
-        <v>752591019.1745175</v>
+        <v>758088320.3547047</v>
       </c>
       <c r="L42" t="n">
-        <v>35.14488855898169</v>
+        <v>24.5248089540335</v>
       </c>
       <c r="M42" t="n">
-        <v>19.28755214921963</v>
+        <v>19.22944978189147</v>
       </c>
       <c r="N42" t="n">
-        <v>286</v>
+        <v>239</v>
       </c>
       <c r="O42" t="n">
-        <v>140</v>
+        <v>128</v>
       </c>
       <c r="P42" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R42" t="n">
         <v>2</v>
       </c>
       <c r="S42" t="n">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>-33.3856938</v>
+        <v>-33.3907923</v>
       </c>
       <c r="U42" t="n">
-        <v>-70.5441996</v>
+        <v>-70.576588</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3926363292-casa-en-venta-jardin-del-este-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3824790288-casa-en-venta-condominio4d4bestarpiscinasan-carlos-_JM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jardín Del Este</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3620,13 +3620,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-3.133235493314933</v>
+        <v>-2.197173716850572</v>
       </c>
       <c r="F43" t="n">
-        <v>1797170422</v>
+        <v>894500733</v>
       </c>
       <c r="G43" t="n">
-        <v>44000</v>
+        <v>21900</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3634,59 +3634,59 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>964561106.9678024</v>
+        <v>686914781.8727839</v>
       </c>
       <c r="J43" t="n">
-        <v>1576153207.625419</v>
+        <v>760830326.7250018</v>
       </c>
       <c r="K43" t="n">
-        <v>1747785830.269659</v>
+        <v>877783969.0313699</v>
       </c>
       <c r="L43" t="n">
-        <v>49.69216948660956</v>
+        <v>25.0869583472288</v>
       </c>
       <c r="M43" t="n">
-        <v>14.02257174653463</v>
+        <v>17.56901658355065</v>
       </c>
       <c r="N43" t="n">
-        <v>843</v>
+        <v>375</v>
       </c>
       <c r="O43" t="n">
-        <v>308</v>
+        <v>178</v>
       </c>
       <c r="P43" t="n">
         <v>4</v>
       </c>
       <c r="Q43" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="T43" t="n">
-        <v>-33.3876211</v>
+        <v>-33.3871246</v>
       </c>
       <c r="U43" t="n">
-        <v>-70.58274590000001</v>
+        <v>-70.4957548</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4155491174-casa-jardin-la-dehesa-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2031477993-townhouses-alonso-camargo-6276-_JM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Rotonda Atenas</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3695,13 +3695,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-3.781310931172527</v>
+        <v>-2.356125897747323</v>
       </c>
       <c r="F44" t="n">
-        <v>1235554665</v>
+        <v>635136365</v>
       </c>
       <c r="G44" t="n">
-        <v>30250</v>
+        <v>15550</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3709,49 +3709,49 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>742611877.201777</v>
+        <v>332967591.2042384</v>
       </c>
       <c r="J44" t="n">
-        <v>951786563.6592499</v>
+        <v>512535598.1219028</v>
       </c>
       <c r="K44" t="n">
-        <v>1199564655.626921</v>
+        <v>623060381.0374757</v>
       </c>
       <c r="L44" t="n">
-        <v>48.01000517052251</v>
+        <v>56.59953979708565</v>
       </c>
       <c r="M44" t="n">
-        <v>29.81425796239147</v>
+        <v>23.92043934652467</v>
       </c>
       <c r="N44" t="n">
-        <v>737</v>
+        <v>159</v>
       </c>
       <c r="O44" t="n">
-        <v>168</v>
+        <v>109</v>
       </c>
       <c r="P44" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q44" t="n">
         <v>3</v>
       </c>
       <c r="R44" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S44" t="n">
-        <v>44</v>
+        <v>176</v>
       </c>
       <c r="T44" t="n">
-        <v>-33.360967</v>
+        <v>-33.4206685</v>
       </c>
       <c r="U44" t="n">
-        <v>-70.5284477</v>
+        <v>-70.5625969</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4054786240-preciosa-casa-en-los-bravos-con-maravillosa-vista-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3543533266-estupenda-casa-con-gran-vista-en-el-arrayan-_JM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>El Arrayán</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3770,13 +3770,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-3.890184569803377</v>
+        <v>-2.452997356240638</v>
       </c>
       <c r="F45" t="n">
-        <v>1631749054</v>
+        <v>1221258991</v>
       </c>
       <c r="G45" t="n">
-        <v>39950</v>
+        <v>29900</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3784,49 +3784,49 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>992386182.1903177</v>
+        <v>564740811.6916066</v>
       </c>
       <c r="J45" t="n">
-        <v>1166961509.212906</v>
+        <v>886931368.6594583</v>
       </c>
       <c r="K45" t="n">
-        <v>1586352097.433055</v>
+        <v>1199502587.975115</v>
       </c>
       <c r="L45" t="n">
-        <v>50.89850098340916</v>
+        <v>71.5683082945765</v>
       </c>
       <c r="M45" t="n">
-        <v>39.82886677218555</v>
+        <v>37.69486954169376</v>
       </c>
       <c r="N45" t="n">
-        <v>1170</v>
+        <v>5172</v>
       </c>
       <c r="O45" t="n">
-        <v>315</v>
+        <v>248</v>
       </c>
       <c r="P45" t="n">
         <v>5</v>
       </c>
       <c r="Q45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R45" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S45" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T45" t="n">
-        <v>-33.3165239</v>
+        <v>-33.346985</v>
       </c>
       <c r="U45" t="n">
-        <v>-70.56922299999999</v>
+        <v>-70.4776525</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2039833029-borderio-comoda-casa-5d-3-b-piscina-168236-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4170217018-se-vende-casa-remodelada-en-vitacura-95640-_JM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Borde Río - Casa Piedra</t>
+          <t>Estadio Croata</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3845,13 +3845,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-4.522999631259394</v>
+        <v>-2.487237264009662</v>
       </c>
       <c r="F46" t="n">
-        <v>1102809123</v>
+        <v>894500733</v>
       </c>
       <c r="G46" t="n">
-        <v>27000</v>
+        <v>21900</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3859,28 +3859,28 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>615530427.2878411</v>
+        <v>619529051.6985533</v>
       </c>
       <c r="J46" t="n">
-        <v>869565037.7893066</v>
+        <v>716297882.1734375</v>
       </c>
       <c r="K46" t="n">
-        <v>1063478699.547229</v>
+        <v>876684705.1532702</v>
       </c>
       <c r="L46" t="n">
-        <v>51.51406194966231</v>
+        <v>35.90065807181205</v>
       </c>
       <c r="M46" t="n">
-        <v>26.82307533932934</v>
+        <v>24.87831602766266</v>
       </c>
       <c r="N46" t="n">
-        <v>480</v>
+        <v>395</v>
       </c>
       <c r="O46" t="n">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="n">
         <v>3</v>
@@ -3889,19 +3889,19 @@
         <v>2</v>
       </c>
       <c r="S46" t="n">
-        <v>49</v>
+        <v>4</v>
       </c>
       <c r="T46" t="n">
-        <v>-33.3819761</v>
+        <v>-33.3826607</v>
       </c>
       <c r="U46" t="n">
-        <v>-70.57844969999999</v>
+        <v>-70.559969</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4198327852-espectacular-casa-remodelada-con-salida-al-sport-frances-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1859517231-22205-las-hualtatas-colegio-tabancura-_JM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Juan Xxiii</t>
+          <t>Tabancura</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3920,13 +3920,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-5.11094373045514</v>
+        <v>-3.064400413608777</v>
       </c>
       <c r="F47" t="n">
-        <v>1470412163</v>
+        <v>2777445198</v>
       </c>
       <c r="G47" t="n">
-        <v>36000</v>
+        <v>68000</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3934,28 +3934,28 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>755662774.3091938</v>
+        <v>816942506.1206945</v>
       </c>
       <c r="J47" t="n">
-        <v>1200593375.699747</v>
+        <v>1859773848.374941</v>
       </c>
       <c r="K47" t="n">
-        <v>1409050511.136414</v>
+        <v>2720454280.49821</v>
       </c>
       <c r="L47" t="n">
-        <v>54.42206745863506</v>
+        <v>102.3517873445092</v>
       </c>
       <c r="M47" t="n">
-        <v>22.47378610955547</v>
+        <v>49.34316881737607</v>
       </c>
       <c r="N47" t="n">
-        <v>640</v>
+        <v>2665</v>
       </c>
       <c r="O47" t="n">
-        <v>240</v>
+        <v>508</v>
       </c>
       <c r="P47" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q47" t="n">
         <v>4</v>
@@ -3964,29 +3964,29 @@
         <v>3</v>
       </c>
       <c r="S47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="T47" t="n">
-        <v>-33.3838555</v>
+        <v>-33.3780395</v>
       </c>
       <c r="U47" t="n">
-        <v>-70.56662470000001</v>
+        <v>-70.52854859999999</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1859517231-22205-las-hualtatas-colegio-tabancura-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1946224879-sector-los-trapenses-comercial-_JM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Tabancura</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3995,13 +3995,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-5.483707032066924</v>
+        <v>-3.077760508074324</v>
       </c>
       <c r="F48" t="n">
-        <v>2777445198</v>
+        <v>2001394334</v>
       </c>
       <c r="G48" t="n">
-        <v>68000</v>
+        <v>49000</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4009,59 +4009,59 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>567016748.6547259</v>
+        <v>1087283687.053744</v>
       </c>
       <c r="J48" t="n">
-        <v>1859773848.374941</v>
+        <v>1497198576.268294</v>
       </c>
       <c r="K48" t="n">
-        <v>2675460648.696122</v>
+        <v>1955314147.492163</v>
       </c>
       <c r="L48" t="n">
-        <v>113.3709833528276</v>
+        <v>57.9769760803507</v>
       </c>
       <c r="M48" t="n">
-        <v>49.34316881737607</v>
+        <v>33.67594424170465</v>
       </c>
       <c r="N48" t="n">
-        <v>2665</v>
+        <v>1062</v>
       </c>
       <c r="O48" t="n">
-        <v>508</v>
+        <v>410</v>
       </c>
       <c r="P48" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q48" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R48" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>-33.3780395</v>
+        <v>-33.3474949</v>
       </c>
       <c r="U48" t="n">
-        <v>-70.52854859999999</v>
+        <v>-70.5421845</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4109151200-casa-en-venta-en-vitacura-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4021085782-luminosa-casa-en-venta-_JM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4070,13 +4070,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-5.823806270093908</v>
+        <v>-3.278274915740692</v>
       </c>
       <c r="F49" t="n">
-        <v>4043633449</v>
+        <v>976190297</v>
       </c>
       <c r="G49" t="n">
-        <v>99000</v>
+        <v>23900</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4084,59 +4084,59 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>1260433021.824693</v>
+        <v>614566902.9499044</v>
       </c>
       <c r="J49" t="n">
-        <v>2507747160.220189</v>
+        <v>907831013.8166518</v>
       </c>
       <c r="K49" t="n">
-        <v>3897587112.644995</v>
+        <v>946429100.5967343</v>
       </c>
       <c r="L49" t="n">
-        <v>105.16028619842</v>
+        <v>36.55550345781133</v>
       </c>
       <c r="M49" t="n">
-        <v>61.2456595761813</v>
+        <v>7.529956802858711</v>
       </c>
       <c r="N49" t="n">
-        <v>11200</v>
+        <v>563</v>
       </c>
       <c r="O49" t="n">
-        <v>750</v>
+        <v>153</v>
       </c>
       <c r="P49" t="n">
         <v>6</v>
       </c>
       <c r="Q49" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R49" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="S49" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="T49" t="n">
-        <v>-33.3678391</v>
+        <v>-33.4060449</v>
       </c>
       <c r="U49" t="n">
-        <v>-70.55428089999999</v>
+        <v>-70.5114827</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4084847464-condominio-el-golf-la-dehesa-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4164770646-casa-impecable-y-amplia-bien-emplazada-club-de-polo-_JM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Borde Río - Casa Piedra</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4145,13 +4145,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-7.097894807809473</v>
+        <v>-3.599381391866206</v>
       </c>
       <c r="F50" t="n">
-        <v>1196752122</v>
+        <v>1039499710</v>
       </c>
       <c r="G50" t="n">
-        <v>29300</v>
+        <v>25450</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4159,25 +4159,25 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>549343975.1459272</v>
+        <v>792169095.6728661</v>
       </c>
       <c r="J50" t="n">
-        <v>964592273.3350897</v>
+        <v>871216704.8094535</v>
       </c>
       <c r="K50" t="n">
-        <v>1128286377.114417</v>
+        <v>1008141298.044259</v>
       </c>
       <c r="L50" t="n">
-        <v>60.01939036550537</v>
+        <v>24.78972237092589</v>
       </c>
       <c r="M50" t="n">
-        <v>24.06818456695851</v>
+        <v>19.31586071083798</v>
       </c>
       <c r="N50" t="n">
-        <v>281</v>
+        <v>354</v>
       </c>
       <c r="O50" t="n">
-        <v>235</v>
+        <v>195</v>
       </c>
       <c r="P50" t="n">
         <v>4</v>
@@ -4189,29 +4189,29 @@
         <v>3</v>
       </c>
       <c r="S50" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>-33.3393451</v>
+        <v>-33.3845621</v>
       </c>
       <c r="U50" t="n">
-        <v>-70.51458239999999</v>
+        <v>-70.5819789</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1946224879-sector-los-trapenses-comercial-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4198328642-casa-en-venta-de-5-dorm-en-vitacura-_JM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>Santa María De Manquehue</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4220,13 +4220,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-7.139286976727352</v>
+        <v>-4.085309844173856</v>
       </c>
       <c r="F51" t="n">
-        <v>2001394334</v>
+        <v>1960549551</v>
       </c>
       <c r="G51" t="n">
-        <v>49000</v>
+        <v>48000</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4234,49 +4234,49 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1045540343.784035</v>
+        <v>1049194578.441455</v>
       </c>
       <c r="J51" t="n">
-        <v>1497198576.268294</v>
+        <v>1417513188.88171</v>
       </c>
       <c r="K51" t="n">
-        <v>1894505031.02873</v>
+        <v>1902639745.152153</v>
       </c>
       <c r="L51" t="n">
-        <v>56.70354625641612</v>
+        <v>60.20721171448074</v>
       </c>
       <c r="M51" t="n">
-        <v>33.67594424170465</v>
+        <v>38.30908709545745</v>
       </c>
       <c r="N51" t="n">
-        <v>1062</v>
+        <v>1000</v>
       </c>
       <c r="O51" t="n">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="P51" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q51" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R51" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="T51" t="n">
-        <v>-33.3474949</v>
+        <v>-33.3736513</v>
       </c>
       <c r="U51" t="n">
-        <v>-70.5421845</v>
+        <v>-70.57956590000001</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4054604630-san-rafael-mall-vivo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4138226282-exclusiva-mediterranea-valle-escondido-arquitecto-mardones-_JM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Valle Escondido</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4295,13 +4295,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-7.26528529885178</v>
+        <v>-4.664980279104539</v>
       </c>
       <c r="F52" t="n">
-        <v>1629706814</v>
+        <v>2797867589</v>
       </c>
       <c r="G52" t="n">
-        <v>39900</v>
+        <v>68500</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -4309,28 +4309,28 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1050270856.753262</v>
+        <v>1126249065.835708</v>
       </c>
       <c r="J52" t="n">
-        <v>1381863090.376708</v>
+        <v>1813378999.567022</v>
       </c>
       <c r="K52" t="n">
-        <v>1529310518.044602</v>
+        <v>2713273816.284775</v>
       </c>
       <c r="L52" t="n">
-        <v>34.66621727053656</v>
+        <v>87.51754326194356</v>
       </c>
       <c r="M52" t="n">
-        <v>17.93547605036096</v>
+        <v>54.29028292861248</v>
       </c>
       <c r="N52" t="n">
-        <v>980</v>
+        <v>2000</v>
       </c>
       <c r="O52" t="n">
-        <v>360</v>
+        <v>580</v>
       </c>
       <c r="P52" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q52" t="n">
         <v>5</v>
@@ -4339,19 +4339,19 @@
         <v>4</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="T52" t="n">
-        <v>-33.3583692</v>
+        <v>-33.3448698</v>
       </c>
       <c r="U52" t="n">
-        <v>-70.5388037</v>
+        <v>-70.4937958</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3798064784-espectacular-casa-en-gran-vista-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4155491174-casa-jardin-la-dehesa-_JM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-7.268269296762019</v>
+        <v>-4.67632771801618</v>
       </c>
       <c r="F53" t="n">
-        <v>1960549551</v>
+        <v>1235554665</v>
       </c>
       <c r="G53" t="n">
-        <v>48000</v>
+        <v>30250</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4384,59 +4384,59 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>1084575857.275928</v>
+        <v>747601427.4900656</v>
       </c>
       <c r="J53" t="n">
-        <v>1471463890.370267</v>
+        <v>951786563.6592499</v>
       </c>
       <c r="K53" t="n">
-        <v>1853599592.843278</v>
+        <v>1191046006.107249</v>
       </c>
       <c r="L53" t="n">
-        <v>52.26249455389894</v>
+        <v>46.59075842721617</v>
       </c>
       <c r="M53" t="n">
-        <v>33.23803348695586</v>
+        <v>29.81425796239147</v>
       </c>
       <c r="N53" t="n">
-        <v>1088</v>
+        <v>737</v>
       </c>
       <c r="O53" t="n">
-        <v>409</v>
+        <v>168</v>
       </c>
       <c r="P53" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S53" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="T53" t="n">
-        <v>-33.3388513</v>
+        <v>-33.360967</v>
       </c>
       <c r="U53" t="n">
-        <v>-70.56431689999999</v>
+        <v>-70.5284477</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4084770850-mediterranea-el-arrayan-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3854828116-espectacular-vista-camino-del-condor-_JM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>El Arrayán</t>
+          <t>Lo Curro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4445,13 +4445,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>-7.569506853046779</v>
+        <v>-4.781796626820063</v>
       </c>
       <c r="F54" t="n">
-        <v>2246258803</v>
+        <v>5105597790</v>
       </c>
       <c r="G54" t="n">
-        <v>54995</v>
+        <v>125000</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -4459,59 +4459,59 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>931266665.1103389</v>
+        <v>1385941292.189607</v>
       </c>
       <c r="J54" t="n">
-        <v>1779082741.057906</v>
+        <v>3310421103.623775</v>
       </c>
       <c r="K54" t="n">
-        <v>2111591012.994249</v>
+        <v>4947300185.333379</v>
       </c>
       <c r="L54" t="n">
-        <v>66.3445448963238</v>
+        <v>107.580237730037</v>
       </c>
       <c r="M54" t="n">
-        <v>26.25937800196379</v>
+        <v>54.22804622684171</v>
       </c>
       <c r="N54" t="n">
-        <v>6138</v>
+        <v>3125</v>
       </c>
       <c r="O54" t="n">
-        <v>575</v>
+        <v>1200</v>
       </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R54" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S54" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="T54" t="n">
-        <v>-33.3607481</v>
+        <v>-33.3656426</v>
       </c>
       <c r="U54" t="n">
-        <v>-70.4790017</v>
+        <v>-70.5665712</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2039819565-casa-en-venta-de-6-dorm-en-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2016678475-luis-pasteur-las-rosas-chicas-_JM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>Juan Xxiii</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4520,13 +4520,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-7.925905168622435</v>
+        <v>-4.905488290367124</v>
       </c>
       <c r="F55" t="n">
-        <v>1552101728</v>
+        <v>980274776</v>
       </c>
       <c r="G55" t="n">
-        <v>38000</v>
+        <v>24000</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -4534,49 +4534,49 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>972455779.7986553</v>
+        <v>740713790.3985107</v>
       </c>
       <c r="J55" t="n">
-        <v>1403868818.687348</v>
+        <v>849968330.43574</v>
       </c>
       <c r="K55" t="n">
-        <v>1440832416.738981</v>
+        <v>938579679.0786458</v>
       </c>
       <c r="L55" t="n">
-        <v>33.36327659006411</v>
+        <v>23.27920718866058</v>
       </c>
       <c r="M55" t="n">
-        <v>10.55888608247981</v>
+        <v>15.33074126390778</v>
       </c>
       <c r="N55" t="n">
-        <v>840</v>
+        <v>390</v>
       </c>
       <c r="O55" t="n">
-        <v>325</v>
+        <v>190</v>
       </c>
       <c r="P55" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q55" t="n">
+        <v>4</v>
+      </c>
+      <c r="R55" t="n">
+        <v>2</v>
+      </c>
+      <c r="S55" t="n">
         <v>5</v>
       </c>
-      <c r="R55" t="n">
-        <v>3</v>
-      </c>
-      <c r="S55" t="n">
-        <v>16</v>
-      </c>
       <c r="T55" t="n">
-        <v>-33.3323566</v>
+        <v>-33.383201</v>
       </c>
       <c r="U55" t="n">
-        <v>-70.5436206</v>
+        <v>-70.5719739</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3979989580-gran-casa-remodelada-con-amplios-y-luminosos-espa-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3927242992-casa-en-condominio-san-carlos-de-apoquindo-5d-5b-_JM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Quinchamalí</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4595,13 +4595,13 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>-8.775715178962619</v>
+        <v>-5.25465351191651</v>
       </c>
       <c r="F56" t="n">
-        <v>2246463027</v>
+        <v>894500733</v>
       </c>
       <c r="G56" t="n">
-        <v>55000</v>
+        <v>21900</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -4609,49 +4609,49 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>1112960628.372801</v>
+        <v>667151987.0166159</v>
       </c>
       <c r="J56" t="n">
-        <v>1549896083.820508</v>
+        <v>738515965.9174603</v>
       </c>
       <c r="K56" t="n">
-        <v>2110448561.114017</v>
+        <v>855694277.860854</v>
       </c>
       <c r="L56" t="n">
-        <v>64.35837493584722</v>
+        <v>25.52988690095706</v>
       </c>
       <c r="M56" t="n">
-        <v>44.94281587333577</v>
+        <v>21.12138048210771</v>
       </c>
       <c r="N56" t="n">
-        <v>1230</v>
+        <v>372</v>
       </c>
       <c r="O56" t="n">
-        <v>530</v>
+        <v>180</v>
       </c>
       <c r="P56" t="n">
         <v>5</v>
       </c>
       <c r="Q56" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R56" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="S56" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T56" t="n">
-        <v>-33.3772917</v>
+        <v>-33.3883239</v>
       </c>
       <c r="U56" t="n">
-        <v>-70.49907279999999</v>
+        <v>-70.49293419999999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4146245022-moderna-casa-sanfuentes-jardin-del-este-174047-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4198327852-espectacular-casa-remodelada-con-salida-al-sport-frances-_JM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Jardín Del Este</t>
+          <t>Juan Xxiii</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -4670,13 +4670,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>-8.917987702112834</v>
+        <v>-5.653542228248217</v>
       </c>
       <c r="F57" t="n">
-        <v>2197449289</v>
+        <v>1470412163</v>
       </c>
       <c r="G57" t="n">
-        <v>53800</v>
+        <v>36000</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -4684,59 +4684,59 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>1073543831.543072</v>
+        <v>811306107.1896869</v>
       </c>
       <c r="J57" t="n">
-        <v>1603288556.125255</v>
+        <v>1200593375.699747</v>
       </c>
       <c r="K57" t="n">
-        <v>2054468212.735367</v>
+        <v>1402536109.515264</v>
       </c>
       <c r="L57" t="n">
-        <v>61.18202350068178</v>
+        <v>49.24481629602428</v>
       </c>
       <c r="M57" t="n">
-        <v>37.05887693171599</v>
+        <v>22.47378610955547</v>
       </c>
       <c r="N57" t="n">
-        <v>1126</v>
+        <v>640</v>
       </c>
       <c r="O57" t="n">
-        <v>410</v>
+        <v>240</v>
       </c>
       <c r="P57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q57" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R57" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S57" t="n">
-        <v>61</v>
+        <v>3</v>
       </c>
       <c r="T57" t="n">
-        <v>-33.3906175</v>
+        <v>-33.3838555</v>
       </c>
       <c r="U57" t="n">
-        <v>-70.5854102</v>
+        <v>-70.56662470000001</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4179336334-casa-comercial-venta-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4054604630-san-rafael-mall-vivo-_JM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rotonda Atenas</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4745,39 +4745,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>-9.105612333921504</v>
+        <v>-5.684950541444155</v>
       </c>
       <c r="F58" t="n">
-        <v>780000000</v>
+        <v>1629706814</v>
       </c>
       <c r="G58" t="n">
-        <v>780000000</v>
+        <v>39900</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>UF</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>360268692.9646396</v>
+        <v>1083010865.631332</v>
       </c>
       <c r="J58" t="n">
-        <v>495858183.8982863</v>
+        <v>1381863090.376708</v>
       </c>
       <c r="K58" t="n">
-        <v>734849076.0481985</v>
+        <v>1551148580.761612</v>
       </c>
       <c r="L58" t="n">
-        <v>75.54183741381895</v>
+        <v>33.87728628041305</v>
       </c>
       <c r="M58" t="n">
-        <v>57.30304053224998</v>
+        <v>17.93547605036096</v>
       </c>
       <c r="N58" t="n">
-        <v>200</v>
+        <v>980</v>
       </c>
       <c r="O58" t="n">
-        <v>140</v>
+        <v>360</v>
       </c>
       <c r="P58" t="n">
         <v>5</v>
@@ -4789,19 +4789,19 @@
         <v>4</v>
       </c>
       <c r="S58" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="T58" t="n">
-        <v>-33.4184886</v>
+        <v>-33.3583692</v>
       </c>
       <c r="U58" t="n">
-        <v>-70.5638072</v>
+        <v>-70.5388037</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2059445027-grandes-espacios-y-exquisita-luz-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1946991437-venta-casa-en-condominio-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>El Huinganal</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>-9.337952246914583</v>
+        <v>-5.821901389581974</v>
       </c>
       <c r="F59" t="n">
-        <v>1752241161</v>
+        <v>935345515</v>
       </c>
       <c r="G59" t="n">
-        <v>42900</v>
+        <v>22900</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4834,59 +4834,59 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>1046161808.847322</v>
+        <v>661840388.1612519</v>
       </c>
       <c r="J59" t="n">
-        <v>1359408698.969573</v>
+        <v>750417699.9380925</v>
       </c>
       <c r="K59" t="n">
-        <v>1625300225.849818</v>
+        <v>891656936.4996351</v>
       </c>
       <c r="L59" t="n">
-        <v>42.60222973719981</v>
+        <v>30.62515028061604</v>
       </c>
       <c r="M59" t="n">
-        <v>28.8973038298337</v>
+        <v>24.64331732542604</v>
       </c>
       <c r="N59" t="n">
-        <v>1000</v>
+        <v>445</v>
       </c>
       <c r="O59" t="n">
-        <v>491</v>
+        <v>200</v>
       </c>
       <c r="P59" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q59" t="n">
         <v>4</v>
       </c>
       <c r="R59" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S59" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="T59" t="n">
-        <v>-33.3630342</v>
+        <v>-33.3406188</v>
       </c>
       <c r="U59" t="n">
-        <v>-70.53728580000001</v>
+        <v>-70.4960912</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3798822532-venta-casa-colegio-cordillera-s-carlos-apoq-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1777531091-casa-mediterranea-remodelada-_JM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>La Llavería</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4895,13 +4895,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>-10.37879194018612</v>
+        <v>-5.900895524851315</v>
       </c>
       <c r="F60" t="n">
-        <v>976190297</v>
+        <v>776050864</v>
       </c>
       <c r="G60" t="n">
-        <v>23900</v>
+        <v>19000</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4909,59 +4909,59 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>584924757.6864979</v>
+        <v>499474658.3460681</v>
       </c>
       <c r="J60" t="n">
-        <v>817585586.016544</v>
+        <v>683228372.552276</v>
       </c>
       <c r="K60" t="n">
-        <v>891334790.0943915</v>
+        <v>735734271.5395483</v>
       </c>
       <c r="L60" t="n">
-        <v>37.47742592928898</v>
+        <v>34.57988905099271</v>
       </c>
       <c r="M60" t="n">
-        <v>19.39915694407149</v>
+        <v>13.58586604080495</v>
       </c>
       <c r="N60" t="n">
-        <v>234</v>
+        <v>273</v>
       </c>
       <c r="O60" t="n">
-        <v>234</v>
+        <v>118</v>
       </c>
       <c r="P60" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q60" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R60" t="n">
         <v>2</v>
       </c>
       <c r="S60" t="n">
-        <v>28</v>
+        <v>2</v>
       </c>
       <c r="T60" t="n">
-        <v>-33.3989457</v>
+        <v>-33.3873026</v>
       </c>
       <c r="U60" t="n">
-        <v>-70.5146483</v>
+        <v>-70.54762890000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3979989636-espectacular-casa-estilo-mediterraneo-condominio-l-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4164888756-moderna-mediterranea-remodelada-luminosa-_JM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Borde Río - Casa Piedra</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>-11.56309839348152</v>
+        <v>-6.140452483460727</v>
       </c>
       <c r="F61" t="n">
-        <v>2123928680</v>
+        <v>1041541949</v>
       </c>
       <c r="G61" t="n">
-        <v>52000</v>
+        <v>25500</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4984,43 +4984,43 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>1069666870.185503</v>
+        <v>777165051.7413801</v>
       </c>
       <c r="J61" t="n">
-        <v>1558942639.793951</v>
+        <v>846041647.2677914</v>
       </c>
       <c r="K61" t="n">
-        <v>1943666608.662687</v>
+        <v>989591163.6592329</v>
       </c>
       <c r="L61" t="n">
-        <v>56.06362390554045</v>
+        <v>25.10823345444779</v>
       </c>
       <c r="M61" t="n">
-        <v>36.2416182471425</v>
+        <v>23.10764515713354</v>
       </c>
       <c r="N61" t="n">
-        <v>959</v>
+        <v>355</v>
       </c>
       <c r="O61" t="n">
-        <v>600</v>
+        <v>195</v>
       </c>
       <c r="P61" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q61" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R61" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S61" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T61" t="n">
-        <v>-33.3362961</v>
+        <v>-33.3845184</v>
       </c>
       <c r="U61" t="n">
-        <v>-70.5317232</v>
+        <v>-70.5803214</v>
       </c>
     </row>
     <row r="62">
@@ -5045,7 +5045,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>-11.87189368186282</v>
+        <v>-7.022638872194742</v>
       </c>
       <c r="F62" t="n">
         <v>1037457471</v>
@@ -5059,16 +5059,16 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>510089140.9028462</v>
+        <v>580605792.4508977</v>
       </c>
       <c r="J62" t="n">
         <v>816072620.1648812</v>
       </c>
       <c r="K62" t="n">
-        <v>940574197.1672331</v>
+        <v>980147637.9509629</v>
       </c>
       <c r="L62" t="n">
-        <v>52.75082702534619</v>
+        <v>48.95910432815904</v>
       </c>
       <c r="M62" t="n">
         <v>27.12808215405997</v>
@@ -5101,7 +5101,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1698236219-casa-siete-dormitorios-mas-estar-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2039833029-borderio-comoda-casa-5d-3-b-piscina-168236-_JM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Jardín Del Este</t>
+          <t>Borde Río - Casa Piedra</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5120,13 +5120,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>-12.53397410046966</v>
+        <v>-7.315097105256737</v>
       </c>
       <c r="F63" t="n">
-        <v>2201533767</v>
+        <v>1102809123</v>
       </c>
       <c r="G63" t="n">
-        <v>53900</v>
+        <v>27000</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -5134,49 +5134,49 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>1070062195.143353</v>
+        <v>661363780.4092292</v>
       </c>
       <c r="J63" t="n">
-        <v>1592431088.999179</v>
+        <v>869565037.7893066</v>
       </c>
       <c r="K63" t="n">
-        <v>2001938866.737016</v>
+        <v>1039199596.09235</v>
       </c>
       <c r="L63" t="n">
-        <v>58.51912073503509</v>
+        <v>43.45112777805463</v>
       </c>
       <c r="M63" t="n">
-        <v>38.24986099609711</v>
+        <v>26.82307533932934</v>
       </c>
       <c r="N63" t="n">
-        <v>1126</v>
+        <v>480</v>
       </c>
       <c r="O63" t="n">
-        <v>397</v>
+        <v>146</v>
       </c>
       <c r="P63" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S63" t="n">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="T63" t="n">
-        <v>-33.3918257</v>
+        <v>-33.3819761</v>
       </c>
       <c r="U63" t="n">
-        <v>-70.5825452</v>
+        <v>-70.57844969999999</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3847765376-gran-casa-sector-jardin-del-este-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4088013424-oportunidad-completamente-remodelada-_JM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Estadio Manquehue</t>
+          <t>La Llavería</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5195,13 +5195,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>-14.52678116152314</v>
+        <v>-7.375507267128762</v>
       </c>
       <c r="F64" t="n">
-        <v>1838015204</v>
+        <v>771966386</v>
       </c>
       <c r="G64" t="n">
-        <v>45000</v>
+        <v>18900</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -5209,59 +5209,59 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>890561045.322926</v>
+        <v>544162365.519313</v>
       </c>
       <c r="J64" t="n">
-        <v>1385402402.756366</v>
+        <v>647147478.5854679</v>
       </c>
       <c r="K64" t="n">
-        <v>1636760828.745099</v>
+        <v>724235976.6878883</v>
       </c>
       <c r="L64" t="n">
-        <v>53.86159154463358</v>
+        <v>27.82574561863076</v>
       </c>
       <c r="M64" t="n">
-        <v>32.67013254366569</v>
+        <v>19.28755214921963</v>
       </c>
       <c r="N64" t="n">
-        <v>842</v>
+        <v>286</v>
       </c>
       <c r="O64" t="n">
-        <v>293</v>
+        <v>140</v>
       </c>
       <c r="P64" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S64" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="T64" t="n">
-        <v>-33.3916065</v>
+        <v>-33.3856938</v>
       </c>
       <c r="U64" t="n">
-        <v>-70.57754749999999</v>
+        <v>-70.5441996</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1872579401-casa-en-venta-de-5-dorm-en-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3876586078-casa-en-venta-en-santa-teresita-con-piscina-_JM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Lo Curro</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>-15.68558808540965</v>
+        <v>-7.801585576992902</v>
       </c>
       <c r="F65" t="n">
-        <v>1572524119</v>
+        <v>919007602</v>
       </c>
       <c r="G65" t="n">
-        <v>38500</v>
+        <v>22500</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -5284,59 +5284,59 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>964845522.2533094</v>
+        <v>484614270.514893</v>
       </c>
       <c r="J65" t="n">
-        <v>1289932781.316407</v>
+        <v>754705600.8309665</v>
       </c>
       <c r="K65" t="n">
-        <v>1370190576.34404</v>
+        <v>860128598.6968137</v>
       </c>
       <c r="L65" t="n">
-        <v>31.42373462879723</v>
+        <v>49.75639875581442</v>
       </c>
       <c r="M65" t="n">
-        <v>21.90744678921968</v>
+        <v>21.77034342770602</v>
       </c>
       <c r="N65" t="n">
-        <v>1011</v>
+        <v>280</v>
       </c>
       <c r="O65" t="n">
-        <v>280</v>
+        <v>74</v>
       </c>
       <c r="P65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S65" t="n">
         <v>4</v>
       </c>
       <c r="T65" t="n">
-        <v>-33.3581657</v>
+        <v>-33.3725014</v>
       </c>
       <c r="U65" t="n">
-        <v>-70.5400722</v>
+        <v>-70.5423126</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4198328642-casa-en-venta-de-5-dorm-en-vitacura-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3838783300-increible-casa-con-gran-jardin-mirador-san-damian-_JM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Santa María De Manquehue</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>-15.89199488861268</v>
+        <v>-8.667313701796298</v>
       </c>
       <c r="F66" t="n">
-        <v>1960549551</v>
+        <v>3676030408</v>
       </c>
       <c r="G66" t="n">
-        <v>48000</v>
+        <v>90000</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5359,59 +5359,59 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1085369482.271106</v>
+        <v>1045022405.495147</v>
       </c>
       <c r="J66" t="n">
-        <v>1417513188.88171</v>
+        <v>2144397506.223563</v>
       </c>
       <c r="K66" t="n">
-        <v>1735278427.477508</v>
+        <v>3490168749.122107</v>
       </c>
       <c r="L66" t="n">
-        <v>45.8485289804691</v>
+        <v>114.0248641649019</v>
       </c>
       <c r="M66" t="n">
-        <v>38.30908709545745</v>
+        <v>71.42485930576146</v>
       </c>
       <c r="N66" t="n">
-        <v>1000</v>
+        <v>2577</v>
       </c>
       <c r="O66" t="n">
-        <v>403</v>
+        <v>652</v>
       </c>
       <c r="P66" t="n">
         <v>5</v>
       </c>
       <c r="Q66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="S66" t="n">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="T66" t="n">
-        <v>-33.3736513</v>
+        <v>-33.3806006</v>
       </c>
       <c r="U66" t="n">
-        <v>-70.57956590000001</v>
+        <v>-70.5017314</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3569364732-casa-en-venta-de-4-dorm-en-las-condes-el-golf-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4054786240-preciosa-casa-en-los-bravos-con-maravillosa-vista-_JM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Barrio El Golf</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5420,13 +5420,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>-18.34016548713291</v>
+        <v>-9.738385844327247</v>
       </c>
       <c r="F67" t="n">
-        <v>1633791293</v>
+        <v>1631749054</v>
       </c>
       <c r="G67" t="n">
-        <v>40000</v>
+        <v>39950</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -5434,59 +5434,59 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>748741960.2808802</v>
+        <v>927484737.5132129</v>
       </c>
       <c r="J67" t="n">
-        <v>1227762900.570667</v>
+        <v>1166961509.212906</v>
       </c>
       <c r="K67" t="n">
-        <v>1408617545.245717</v>
+        <v>1518105839.578063</v>
       </c>
       <c r="L67" t="n">
-        <v>53.74617400950334</v>
+        <v>50.61187514772556</v>
       </c>
       <c r="M67" t="n">
-        <v>33.07058653104844</v>
+        <v>39.82886677218555</v>
       </c>
       <c r="N67" t="n">
-        <v>399</v>
+        <v>1170</v>
       </c>
       <c r="O67" t="n">
-        <v>271</v>
+        <v>315</v>
       </c>
       <c r="P67" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q67" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R67" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T67" t="n">
-        <v>-33.4210698</v>
+        <v>-33.3165239</v>
       </c>
       <c r="U67" t="n">
-        <v>-70.5918738</v>
+        <v>-70.56922299999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3541049788-casa-en-venta-en-lo-curro-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1872579401-casa-en-venta-de-5-dorm-en-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>-18.8323877803089</v>
+        <v>-10.40141042474583</v>
       </c>
       <c r="F68" t="n">
-        <v>3063358674</v>
+        <v>1572524119</v>
       </c>
       <c r="G68" t="n">
-        <v>75000</v>
+        <v>38500</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5509,59 +5509,59 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1223482770.074514</v>
+        <v>1020592416.770405</v>
       </c>
       <c r="J68" t="n">
-        <v>2028028621.442431</v>
+        <v>1289932781.316407</v>
       </c>
       <c r="K68" t="n">
-        <v>2681432459.714309</v>
+        <v>1438352916.211941</v>
       </c>
       <c r="L68" t="n">
-        <v>71.88999574388802</v>
+        <v>32.38622240572893</v>
       </c>
       <c r="M68" t="n">
-        <v>51.05105724894518</v>
+        <v>21.90744678921968</v>
       </c>
       <c r="N68" t="n">
-        <v>3476</v>
+        <v>1011</v>
       </c>
       <c r="O68" t="n">
-        <v>614</v>
+        <v>280</v>
       </c>
       <c r="P68" t="n">
         <v>5</v>
       </c>
       <c r="Q68" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R68" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="T68" t="n">
-        <v>-33.367236</v>
+        <v>-33.3581657</v>
       </c>
       <c r="U68" t="n">
-        <v>-70.55182569999999</v>
+        <v>-70.5400722</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1883257409-casa-san-ramon-oriente-id-167799-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4084847464-condominio-el-golf-la-dehesa-_JM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>-20.51414788829328</v>
+        <v>-11.78427950966704</v>
       </c>
       <c r="F69" t="n">
-        <v>1053795384</v>
+        <v>1196752122</v>
       </c>
       <c r="G69" t="n">
-        <v>25800</v>
+        <v>29300</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -5584,49 +5584,49 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>547235993.7199936</v>
+        <v>584107537.3752755</v>
       </c>
       <c r="J69" t="n">
-        <v>723041599.2892851</v>
+        <v>964592273.3350897</v>
       </c>
       <c r="K69" t="n">
-        <v>905469561.0279151</v>
+        <v>1083081872.381541</v>
       </c>
       <c r="L69" t="n">
-        <v>49.54536055187527</v>
+        <v>51.72904125398559</v>
       </c>
       <c r="M69" t="n">
-        <v>45.74477942013709</v>
+        <v>24.06818456695851</v>
       </c>
       <c r="N69" t="n">
-        <v>300</v>
+        <v>281</v>
       </c>
       <c r="O69" t="n">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="P69" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q69" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S69" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="T69" t="n">
-        <v>-33.3925902</v>
+        <v>-33.3393451</v>
       </c>
       <c r="U69" t="n">
-        <v>-70.51186079999999</v>
+        <v>-70.51458239999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3979950470-gran-casa-mediterranea-con-excelente-ubicacion-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1938489451-casa-en-condominio-colegios-mayflower-y-nido-de-aguilas-_JM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5636,7 +5636,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>El Huinganal</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5645,13 +5645,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>-20.53782054681183</v>
+        <v>-12.72734632057789</v>
       </c>
       <c r="F70" t="n">
-        <v>1838015204</v>
+        <v>894500733</v>
       </c>
       <c r="G70" t="n">
-        <v>45000</v>
+        <v>21900</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5659,59 +5659,59 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>1018153988.773446</v>
+        <v>611756561.9932473</v>
       </c>
       <c r="J70" t="n">
-        <v>1327452260.210802</v>
+        <v>709567235.0425349</v>
       </c>
       <c r="K70" t="n">
-        <v>1565385440.953308</v>
+        <v>804191653.6187876</v>
       </c>
       <c r="L70" t="n">
-        <v>41.22419077375788</v>
+        <v>27.12006447338354</v>
       </c>
       <c r="M70" t="n">
-        <v>38.4618685803525</v>
+        <v>26.0628575876082</v>
       </c>
       <c r="N70" t="n">
-        <v>864</v>
+        <v>445</v>
       </c>
       <c r="O70" t="n">
-        <v>373</v>
+        <v>140</v>
       </c>
       <c r="P70" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q70" t="n">
         <v>5</v>
       </c>
-      <c r="Q70" t="n">
-        <v>3</v>
-      </c>
       <c r="R70" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S70" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="T70" t="n">
-        <v>-33.327</v>
+        <v>-33.3405638</v>
       </c>
       <c r="U70" t="n">
-        <v>-70.54795799999999</v>
+        <v>-70.49693000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1949405103-entorno-natural-en-el-arrayan-para-desarrollo-inmobiliario-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1883257409-casa-san-ramon-oriente-id-167799-_JM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>El Arrayán</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5720,13 +5720,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>-20.93666146312801</v>
+        <v>-13.15582650002811</v>
       </c>
       <c r="F71" t="n">
-        <v>1960549551</v>
+        <v>1053795384</v>
       </c>
       <c r="G71" t="n">
-        <v>48000</v>
+        <v>25800</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -5734,59 +5734,59 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>552871206.9084212</v>
+        <v>610949516.5052081</v>
       </c>
       <c r="J71" t="n">
-        <v>856905672.4415878</v>
+        <v>723041599.2892851</v>
       </c>
       <c r="K71" t="n">
-        <v>1781142111.302564</v>
+        <v>958673285.6744732</v>
       </c>
       <c r="L71" t="n">
-        <v>143.3379360057708</v>
+        <v>48.09180682149695</v>
       </c>
       <c r="M71" t="n">
-        <v>128.79409181804</v>
+        <v>45.74477942013709</v>
       </c>
       <c r="N71" t="n">
-        <v>10385</v>
+        <v>300</v>
       </c>
       <c r="O71" t="n">
-        <v>305</v>
+        <v>200</v>
       </c>
       <c r="P71" t="n">
         <v>7</v>
       </c>
       <c r="Q71" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="R71" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="S71" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="T71" t="n">
-        <v>-33.3443566</v>
+        <v>-33.3925902</v>
       </c>
       <c r="U71" t="n">
-        <v>-70.4699251</v>
+        <v>-70.51186079999999</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3941848806-casa-de-diseno-en-sector-exclusivo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3798822532-venta-casa-colegio-cordillera-s-carlos-apoq-las-condes-_JM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5795,13 +5795,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>-22.34187284325871</v>
+        <v>-13.36740055884638</v>
       </c>
       <c r="F72" t="n">
-        <v>2940824327</v>
+        <v>976190297</v>
       </c>
       <c r="G72" t="n">
-        <v>72000</v>
+        <v>23900</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -5809,59 +5809,59 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>1152557176.229172</v>
+        <v>624202650.4259667</v>
       </c>
       <c r="J72" t="n">
-        <v>1784060267.889923</v>
+        <v>817585586.016544</v>
       </c>
       <c r="K72" t="n">
-        <v>2542231850.500933</v>
+        <v>866900356.8057771</v>
       </c>
       <c r="L72" t="n">
-        <v>77.89393101138803</v>
+        <v>29.68468506915426</v>
       </c>
       <c r="M72" t="n">
-        <v>64.83884428849633</v>
+        <v>19.39915694407149</v>
       </c>
       <c r="N72" t="n">
-        <v>2118</v>
+        <v>234</v>
       </c>
       <c r="O72" t="n">
-        <v>308</v>
+        <v>234</v>
       </c>
       <c r="P72" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q72" t="n">
         <v>4</v>
       </c>
       <c r="R72" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S72" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="T72" t="n">
-        <v>-33.3724038</v>
+        <v>-33.3989457</v>
       </c>
       <c r="U72" t="n">
-        <v>-70.5645356</v>
+        <v>-70.5146483</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3538444870-casa-en-venta-en-el-arrayan-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3847765376-gran-casa-sector-jardin-del-este-_JM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>El Arrayán</t>
+          <t>Estadio Manquehue</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5870,13 +5870,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>-22.36589738876757</v>
+        <v>-13.94975602677535</v>
       </c>
       <c r="F73" t="n">
-        <v>2246463027</v>
+        <v>1838015204</v>
       </c>
       <c r="G73" t="n">
-        <v>55000</v>
+        <v>45000</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -5884,49 +5884,49 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>682308800.0591381</v>
+        <v>869099831.3496712</v>
       </c>
       <c r="J73" t="n">
-        <v>1292335492.300017</v>
+        <v>1385402402.756366</v>
       </c>
       <c r="K73" t="n">
-        <v>1957420596.873554</v>
+        <v>1644754948.826403</v>
       </c>
       <c r="L73" t="n">
-        <v>98.66724270994467</v>
+        <v>55.98771273483472</v>
       </c>
       <c r="M73" t="n">
-        <v>73.82970911074239</v>
+        <v>32.67013254366569</v>
       </c>
       <c r="N73" t="n">
-        <v>6138</v>
+        <v>842</v>
       </c>
       <c r="O73" t="n">
-        <v>575</v>
+        <v>293</v>
       </c>
       <c r="P73" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q73" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R73" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S73" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="T73" t="n">
-        <v>-33.3432917</v>
+        <v>-33.3916065</v>
       </c>
       <c r="U73" t="n">
-        <v>-70.4699641</v>
+        <v>-70.57754749999999</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4170191126-moderno-y-exclusivo-departamento-90781-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2983249392-club-de-polo-_JM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>Jardín Del Este</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5945,13 +5945,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>-24.08871875248119</v>
+        <v>-14.42660555932013</v>
       </c>
       <c r="F74" t="n">
-        <v>2654910851</v>
+        <v>1429567381</v>
       </c>
       <c r="G74" t="n">
-        <v>65000</v>
+        <v>35000</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5959,59 +5959,59 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>1035140319.147453</v>
+        <v>822658220.310781</v>
       </c>
       <c r="J74" t="n">
-        <v>1637331824.610674</v>
+        <v>948225657.2453243</v>
       </c>
       <c r="K74" t="n">
-        <v>2260498592.724666</v>
+        <v>1292770605.616946</v>
       </c>
       <c r="L74" t="n">
-        <v>74.83872573408144</v>
+        <v>49.57811273235123</v>
       </c>
       <c r="M74" t="n">
-        <v>62.14861343889696</v>
+        <v>50.76236021212652</v>
       </c>
       <c r="N74" t="n">
-        <v>500</v>
+        <v>337</v>
       </c>
       <c r="O74" t="n">
-        <v>450</v>
+        <v>268</v>
       </c>
       <c r="P74" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q74" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R74" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S74" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="T74" t="n">
-        <v>-33.3669086</v>
+        <v>-33.3912484</v>
       </c>
       <c r="U74" t="n">
-        <v>-70.545604</v>
+        <v>-70.58727399999999</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3854828116-espectacular-vista-camino-del-condor-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4164894878-a-estrenar-nueva-oxford-los-dominicos-_JM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>-24.63710022538149</v>
+        <v>-14.50884871374012</v>
       </c>
       <c r="F75" t="n">
-        <v>5105597790</v>
+        <v>1347469369</v>
       </c>
       <c r="G75" t="n">
-        <v>125000</v>
+        <v>32990</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -6034,59 +6034,59 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>1221486163.042739</v>
+        <v>759961270.8312922</v>
       </c>
       <c r="J75" t="n">
-        <v>3310421103.623775</v>
+        <v>984756043.4639397</v>
       </c>
       <c r="K75" t="n">
-        <v>4290006024.81803</v>
+        <v>1204592604.454404</v>
       </c>
       <c r="L75" t="n">
-        <v>92.69273502444491</v>
+        <v>45.15141964085785</v>
       </c>
       <c r="M75" t="n">
-        <v>54.22804622684171</v>
+        <v>36.83281031312019</v>
       </c>
       <c r="N75" t="n">
-        <v>3125</v>
+        <v>500</v>
       </c>
       <c r="O75" t="n">
-        <v>1200</v>
+        <v>280</v>
       </c>
       <c r="P75" t="n">
         <v>5</v>
       </c>
       <c r="Q75" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R75" t="n">
         <v>4</v>
       </c>
       <c r="S75" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>-33.3656426</v>
+        <v>-33.4029151</v>
       </c>
       <c r="U75" t="n">
-        <v>-70.5665712</v>
+        <v>-70.5424204</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3795283994-casa-en-venta-de-3-dorm-en-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3979950470-gran-casa-mediterranea-con-excelente-ubicacion-_JM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6095,13 +6095,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-25.50312232476499</v>
+        <v>-16.68427651323841</v>
       </c>
       <c r="F76" t="n">
-        <v>1633791293</v>
+        <v>1838015204</v>
       </c>
       <c r="G76" t="n">
-        <v>40000</v>
+        <v>45000</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -6109,49 +6109,49 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>756211635.8200498</v>
+        <v>1014723104.521324</v>
       </c>
       <c r="J76" t="n">
-        <v>811224515.5150867</v>
+        <v>1327452260.210802</v>
       </c>
       <c r="K76" t="n">
-        <v>1426903712.479705</v>
+        <v>1616539398.325197</v>
       </c>
       <c r="L76" t="n">
-        <v>82.67650494189022</v>
+        <v>45.33619112662497</v>
       </c>
       <c r="M76" t="n">
-        <v>101.3981655821416</v>
+        <v>38.4618685803525</v>
       </c>
       <c r="N76" t="n">
-        <v>501</v>
+        <v>864</v>
       </c>
       <c r="O76" t="n">
-        <v>200</v>
+        <v>373</v>
       </c>
       <c r="P76" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q76" t="n">
         <v>3</v>
       </c>
       <c r="R76" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S76" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="T76" t="n">
-        <v>-33.4005536</v>
+        <v>-33.327</v>
       </c>
       <c r="U76" t="n">
-        <v>-70.5314422</v>
+        <v>-70.54795799999999</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2983249392-club-de-polo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3941848806-casa-de-diseno-en-sector-exclusivo-_JM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Jardín Del Este</t>
+          <t>Lo Curro</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6170,13 +6170,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>-25.9439798772486</v>
+        <v>-17.74660746003439</v>
       </c>
       <c r="F77" t="n">
-        <v>1429567381</v>
+        <v>2940824327</v>
       </c>
       <c r="G77" t="n">
-        <v>35000</v>
+        <v>72000</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -6184,49 +6184,49 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>696646662.1712186</v>
+        <v>1156716869.862871</v>
       </c>
       <c r="J77" t="n">
-        <v>948225657.2453243</v>
+        <v>1784060267.889923</v>
       </c>
       <c r="K77" t="n">
-        <v>1183559907.293365</v>
+        <v>2624214154.407137</v>
       </c>
       <c r="L77" t="n">
-        <v>51.34993357347768</v>
+        <v>82.25603758778466</v>
       </c>
       <c r="M77" t="n">
-        <v>50.76236021212652</v>
+        <v>64.83884428849633</v>
       </c>
       <c r="N77" t="n">
-        <v>337</v>
+        <v>2118</v>
       </c>
       <c r="O77" t="n">
-        <v>268</v>
+        <v>308</v>
       </c>
       <c r="P77" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q77" t="n">
         <v>4</v>
       </c>
       <c r="R77" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S77" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="T77" t="n">
-        <v>-33.3912484</v>
+        <v>-33.3724038</v>
       </c>
       <c r="U77" t="n">
-        <v>-70.58727399999999</v>
+        <v>-70.5645356</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2005730735-pano-barrio-estadio-espanol-verbo-divino-vma-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3795283994-casa-en-venta-de-3-dorm-en-las-condes-_JM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6236,7 +6236,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Metro Escuela Militar</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>-26.00469875819209</v>
+        <v>-23.02008662815424</v>
       </c>
       <c r="F78" t="n">
-        <v>2351638342</v>
+        <v>1633791293</v>
       </c>
       <c r="G78" t="n">
-        <v>57575</v>
+        <v>40000</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -6259,59 +6259,59 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>977146151.026263</v>
+        <v>731023191.6933835</v>
       </c>
       <c r="J78" t="n">
-        <v>1533713390.112091</v>
+        <v>811224515.5150867</v>
       </c>
       <c r="K78" t="n">
-        <v>1952800795.087295</v>
+        <v>1447046706.779603</v>
       </c>
       <c r="L78" t="n">
-        <v>63.61388316429362</v>
+        <v>88.26453113680623</v>
       </c>
       <c r="M78" t="n">
-        <v>53.32971317594948</v>
+        <v>101.3981655821416</v>
       </c>
       <c r="N78" t="n">
-        <v>1225</v>
+        <v>501</v>
       </c>
       <c r="O78" t="n">
-        <v>497</v>
+        <v>200</v>
       </c>
       <c r="P78" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Q78" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R78" t="n">
+        <v>7</v>
+      </c>
+      <c r="S78" t="n">
         <v>0</v>
       </c>
-      <c r="S78" t="n">
-        <v>69</v>
-      </c>
       <c r="T78" t="n">
-        <v>-33.4163346</v>
+        <v>-33.4005536</v>
       </c>
       <c r="U78" t="n">
-        <v>-70.5808174</v>
+        <v>-70.5314422</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1960135633-espectacular-casa-en-el-golf-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4170191126-moderno-y-exclusivo-departamento-90781-_JM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Barrio El Golf</t>
+          <t>Lo Curro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6320,7 +6320,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>-26.60509848430851</v>
+        <v>-23.57320048526929</v>
       </c>
       <c r="F79" t="n">
         <v>2654910851</v>
@@ -6334,49 +6334,49 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>951013307.2627529</v>
+        <v>890712832.6979307</v>
       </c>
       <c r="J79" t="n">
-        <v>1541938228.686142</v>
+        <v>1637331824.610674</v>
       </c>
       <c r="K79" t="n">
-        <v>2244676666.69085</v>
+        <v>2268939337.375408</v>
       </c>
       <c r="L79" t="n">
-        <v>83.89852040508809</v>
+        <v>84.17514910303494</v>
       </c>
       <c r="M79" t="n">
-        <v>72.18010433934194</v>
+        <v>62.14861343889696</v>
       </c>
       <c r="N79" t="n">
-        <v>892</v>
+        <v>500</v>
       </c>
       <c r="O79" t="n">
-        <v>871</v>
+        <v>450</v>
       </c>
       <c r="P79" t="n">
         <v>4</v>
       </c>
       <c r="Q79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R79" t="n">
         <v>4</v>
       </c>
       <c r="S79" t="n">
-        <v>75</v>
+        <v>13</v>
       </c>
       <c r="T79" t="n">
-        <v>-33.418827</v>
+        <v>-33.3669086</v>
       </c>
       <c r="U79" t="n">
-        <v>-70.588898</v>
+        <v>-70.545604</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3838783300-increible-casa-con-gran-jardin-mirador-san-damian-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4179336334-casa-comercial-venta-las-condes-_JM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>Rotonda Atenas</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6395,63 +6395,63 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>-33.05113837251504</v>
+        <v>-29.37244195097637</v>
       </c>
       <c r="F80" t="n">
-        <v>3676030408</v>
+        <v>780000000</v>
       </c>
       <c r="G80" t="n">
-        <v>90000</v>
+        <v>780000000</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>UF</t>
+          <t>CLP</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1070537832.863456</v>
+        <v>369395409.6714396</v>
       </c>
       <c r="J80" t="n">
-        <v>2144397506.223563</v>
+        <v>495858183.8982863</v>
       </c>
       <c r="K80" t="n">
-        <v>2967282620.961288</v>
+        <v>634354342.7753102</v>
       </c>
       <c r="L80" t="n">
-        <v>88.45117486813982</v>
+        <v>53.4344176838716</v>
       </c>
       <c r="M80" t="n">
-        <v>71.42485930576146</v>
+        <v>57.30304053224998</v>
       </c>
       <c r="N80" t="n">
-        <v>2577</v>
+        <v>200</v>
       </c>
       <c r="O80" t="n">
-        <v>652</v>
+        <v>140</v>
       </c>
       <c r="P80" t="n">
         <v>5</v>
       </c>
       <c r="Q80" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R80" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S80" t="n">
-        <v>16</v>
+        <v>77</v>
       </c>
       <c r="T80" t="n">
-        <v>-33.3806006</v>
+        <v>-33.4184886</v>
       </c>
       <c r="U80" t="n">
-        <v>-70.5017314</v>
+        <v>-70.5638072</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4138226282-exclusiva-mediterranea-valle-escondido-arquitecto-mardones-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1949405103-entorno-natural-en-el-arrayan-para-desarrollo-inmobiliario-_JM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Valle Escondido</t>
+          <t>El Arrayán</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>-33.77822879951345</v>
+        <v>-39.96734705957697</v>
       </c>
       <c r="F81" t="n">
-        <v>2797867589</v>
+        <v>1960549551</v>
       </c>
       <c r="G81" t="n">
-        <v>68500</v>
+        <v>48000</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -6484,43 +6484,43 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>1104731771.88972</v>
+        <v>617782023.1138905</v>
       </c>
       <c r="J81" t="n">
-        <v>1813378999.567022</v>
+        <v>856905672.4415878</v>
       </c>
       <c r="K81" t="n">
-        <v>2185340281.523923</v>
+        <v>1618067086.922069</v>
       </c>
       <c r="L81" t="n">
-        <v>59.59088033401837</v>
+        <v>116.7322257253892</v>
       </c>
       <c r="M81" t="n">
-        <v>54.29028292861248</v>
+        <v>128.79409181804</v>
       </c>
       <c r="N81" t="n">
-        <v>2000</v>
+        <v>10385</v>
       </c>
       <c r="O81" t="n">
-        <v>580</v>
+        <v>305</v>
       </c>
       <c r="P81" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q81" t="n">
         <v>5</v>
       </c>
       <c r="R81" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="S81" t="n">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="T81" t="n">
-        <v>-33.3448698</v>
+        <v>-33.3443566</v>
       </c>
       <c r="U81" t="n">
-        <v>-70.4937958</v>
+        <v>-70.4699251</v>
       </c>
     </row>
     <row r="82">
@@ -6545,7 +6545,7 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>-37.49707360559454</v>
+        <v>-42.97831305724794</v>
       </c>
       <c r="F82" t="n">
         <v>1143653905</v>
@@ -6559,16 +6559,16 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>553359329.3743249</v>
+        <v>619074280.6158991</v>
       </c>
       <c r="J82" t="n">
         <v>708858468.0830567</v>
       </c>
       <c r="K82" t="n">
-        <v>877852723.4634063</v>
+        <v>838998493.4544519</v>
       </c>
       <c r="L82" t="n">
-        <v>45.77689464112611</v>
+        <v>31.02512317208919</v>
       </c>
       <c r="M82" t="n">
         <v>61.33741169697059</v>
@@ -6601,7 +6601,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4125912720-casa-via-aurora-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4029221140-espectacular-casa-en-santa-maria-de-manquehue-_JM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>Santa María De Manquehue</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>-39.55068017484409</v>
+        <v>-45.97738450630628</v>
       </c>
       <c r="F83" t="n">
-        <v>3063358674</v>
+        <v>4901373878</v>
       </c>
       <c r="G83" t="n">
-        <v>75000</v>
+        <v>120000</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -6634,59 +6634,59 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1059070367.921236</v>
+        <v>1360095591.869593</v>
       </c>
       <c r="J83" t="n">
-        <v>1662503353.452482</v>
+        <v>2424391676.054841</v>
       </c>
       <c r="K83" t="n">
-        <v>2405827289.779951</v>
+        <v>3786701995.161383</v>
       </c>
       <c r="L83" t="n">
-        <v>81.00777174746361</v>
+        <v>100.0913518743206</v>
       </c>
       <c r="M83" t="n">
-        <v>84.26180420258368</v>
+        <v>102.1692256416215</v>
       </c>
       <c r="N83" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="O83" t="n">
-        <v>900</v>
+        <v>850</v>
       </c>
       <c r="P83" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>7</v>
+      </c>
+      <c r="R83" t="n">
         <v>6</v>
       </c>
-      <c r="Q83" t="n">
-        <v>6</v>
-      </c>
-      <c r="R83" t="n">
-        <v>5</v>
-      </c>
       <c r="S83" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="T83" t="n">
-        <v>-33.3673321</v>
+        <v>-33.367176</v>
       </c>
       <c r="U83" t="n">
-        <v>-70.5469629</v>
+        <v>-70.5778047</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4029221140-espectacular-casa-en-santa-maria-de-manquehue-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4018720458-espectacularpaseo-pie-andino-_JM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Santa María De Manquehue</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-58.50431455706118</v>
+        <v>-47.72914926635305</v>
       </c>
       <c r="F84" t="n">
-        <v>4901373878</v>
+        <v>1756325640</v>
       </c>
       <c r="G84" t="n">
-        <v>120000</v>
+        <v>43000</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6709,59 +6709,59 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>1219550801.170683</v>
+        <v>771867064.6165577</v>
       </c>
       <c r="J84" t="n">
-        <v>2424391676.054841</v>
+        <v>951937590.5782057</v>
       </c>
       <c r="K84" t="n">
-        <v>3483000145.745668</v>
+        <v>1301973926.470403</v>
       </c>
       <c r="L84" t="n">
-        <v>93.36153753250986</v>
+        <v>55.68714452507958</v>
       </c>
       <c r="M84" t="n">
-        <v>102.1692256416215</v>
+        <v>84.50008250364502</v>
       </c>
       <c r="N84" t="n">
-        <v>2000</v>
+        <v>450</v>
       </c>
       <c r="O84" t="n">
-        <v>850</v>
+        <v>280</v>
       </c>
       <c r="P84" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q84" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="R84" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S84" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="T84" t="n">
-        <v>-33.367176</v>
+        <v>-33.3245489</v>
       </c>
       <c r="U84" t="n">
-        <v>-70.5778047</v>
+        <v>-70.53096650000001</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4018720458-espectacularpaseo-pie-andino-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1868286737-casa-con-espectacular-terreno-lo-curro-_JM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>Lo Curro</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6770,13 +6770,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>-58.96365273537021</v>
+        <v>-57.45612747439884</v>
       </c>
       <c r="F85" t="n">
-        <v>1756325640</v>
+        <v>4901373878</v>
       </c>
       <c r="G85" t="n">
-        <v>43000</v>
+        <v>120000</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6784,59 +6784,59 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>775158423.3242766</v>
+        <v>1366728469.998903</v>
       </c>
       <c r="J85" t="n">
-        <v>951937590.5782057</v>
+        <v>1966890648.122933</v>
       </c>
       <c r="K85" t="n">
-        <v>1195028464.834017</v>
+        <v>3771274679.932458</v>
       </c>
       <c r="L85" t="n">
-        <v>44.10688743310488</v>
+        <v>122.251138477286</v>
       </c>
       <c r="M85" t="n">
-        <v>84.50008250364502</v>
+        <v>149.1940201493936</v>
       </c>
       <c r="N85" t="n">
+        <v>5440</v>
+      </c>
+      <c r="O85" t="n">
         <v>450</v>
       </c>
-      <c r="O85" t="n">
-        <v>280</v>
-      </c>
       <c r="P85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q85" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R85" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S85" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="T85" t="n">
-        <v>-33.3245489</v>
+        <v>-33.367545</v>
       </c>
       <c r="U85" t="n">
-        <v>-70.53096650000001</v>
+        <v>-70.5564964</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2035145623-casa-comercial-esquina-venta-en-las-condes-mla-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1967132999-casa-en-venta-con-gran-terreno-en-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Alto Las Condes</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6845,13 +6845,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>-81.27784072181485</v>
+        <v>-69.26804911943888</v>
       </c>
       <c r="F86" t="n">
-        <v>1552101728</v>
+        <v>4697149966</v>
       </c>
       <c r="G86" t="n">
-        <v>38000</v>
+        <v>115000</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -6859,59 +6859,59 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>531688259.9808438</v>
+        <v>1144028527.283284</v>
       </c>
       <c r="J86" t="n">
-        <v>669493630.0509378</v>
+        <v>1950449243.969325</v>
       </c>
       <c r="K86" t="n">
-        <v>1007951761.724502</v>
+        <v>3346111825.637604</v>
       </c>
       <c r="L86" t="n">
-        <v>71.13786903505303</v>
+        <v>112.9013382513301</v>
       </c>
       <c r="M86" t="n">
-        <v>131.8321875417859</v>
+        <v>140.8240040351377</v>
       </c>
       <c r="N86" t="n">
-        <v>403</v>
+        <v>2700</v>
       </c>
       <c r="O86" t="n">
-        <v>184</v>
+        <v>500</v>
       </c>
       <c r="P86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q86" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="S86" t="n">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="T86" t="n">
-        <v>-33.3937675</v>
+        <v>-33.352549</v>
       </c>
       <c r="U86" t="n">
-        <v>-70.5463814</v>
+        <v>-70.5198627</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1967132999-casa-en-venta-con-gran-terreno-en-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2035145623-casa-comercial-esquina-venta-en-las-condes-mla-_JM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Alto Las Condes</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6920,13 +6920,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>-97.16400609743698</v>
+        <v>-100.6274037375979</v>
       </c>
       <c r="F87" t="n">
-        <v>4697149966</v>
+        <v>1552101728</v>
       </c>
       <c r="G87" t="n">
-        <v>115000</v>
+        <v>38000</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -6934,43 +6934,43 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>1140556658.457362</v>
+        <v>515866137.4838958</v>
       </c>
       <c r="J87" t="n">
-        <v>1950449243.969325</v>
+        <v>669493630.0509378</v>
       </c>
       <c r="K87" t="n">
-        <v>2802015343.662231</v>
+        <v>878407669.8911431</v>
       </c>
       <c r="L87" t="n">
-        <v>85.18338481977948</v>
+        <v>54.15160296292343</v>
       </c>
       <c r="M87" t="n">
-        <v>140.8240040351377</v>
+        <v>131.8321875417859</v>
       </c>
       <c r="N87" t="n">
-        <v>2700</v>
+        <v>403</v>
       </c>
       <c r="O87" t="n">
-        <v>500</v>
+        <v>184</v>
       </c>
       <c r="P87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q87" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R87" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="T87" t="n">
-        <v>-33.352549</v>
+        <v>-33.3937675</v>
       </c>
       <c r="U87" t="n">
-        <v>-70.5198627</v>
+        <v>-70.5463814</v>
       </c>
     </row>
     <row r="88">
@@ -6995,7 +6995,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>-104.5390489392995</v>
+        <v>-114.3860034321664</v>
       </c>
       <c r="F88" t="n">
         <v>1470412163</v>
@@ -7009,16 +7009,16 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>408095437.4525639</v>
+        <v>435823513.3491086</v>
       </c>
       <c r="J88" t="n">
         <v>563035695.3352805</v>
       </c>
       <c r="K88" t="n">
-        <v>881820001.9077258</v>
+        <v>826378133.2094641</v>
       </c>
       <c r="L88" t="n">
-        <v>84.13757216104479</v>
+        <v>69.36587202127303</v>
       </c>
       <c r="M88" t="n">
         <v>161.1578937503045</v>
@@ -7046,81 +7046,6 @@
       </c>
       <c r="U88" t="n">
         <v>-70.56255350000001</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>https://www.portalinmobiliario.com/MLC-1868286737-casa-con-espectacular-terreno-lo-curro-_JM</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Vitacura</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Lo Curro</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>sobrevalorada</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>-113.9090505016377</v>
-      </c>
-      <c r="F89" t="n">
-        <v>4901373878</v>
-      </c>
-      <c r="G89" t="n">
-        <v>120000</v>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>UF</t>
-        </is>
-      </c>
-      <c r="I89" t="n">
-        <v>1288917079.441762</v>
-      </c>
-      <c r="J89" t="n">
-        <v>1966890648.122933</v>
-      </c>
-      <c r="K89" t="n">
-        <v>2660907416.317658</v>
-      </c>
-      <c r="L89" t="n">
-        <v>69.75427628298658</v>
-      </c>
-      <c r="M89" t="n">
-        <v>149.1940201493936</v>
-      </c>
-      <c r="N89" t="n">
-        <v>5440</v>
-      </c>
-      <c r="O89" t="n">
-        <v>450</v>
-      </c>
-      <c r="P89" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>4</v>
-      </c>
-      <c r="R89" t="n">
-        <v>6</v>
-      </c>
-      <c r="S89" t="n">
-        <v>10</v>
-      </c>
-      <c r="T89" t="n">
-        <v>-33.367545</v>
-      </c>
-      <c r="U89" t="n">
-        <v>-70.5564964</v>
       </c>
     </row>
   </sheetData>

--- a/casas_candidatas.xlsx
+++ b/casas_candidatas.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U88"/>
+  <dimension ref="A1:U116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -526,7 +526,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2059394253-solida-cercana-al-metro-los-dominicos-bajo-valor-tasacion-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4201744792-vive-a-minutos-de-mall-los-dominicos-excelente-ubicacion-y-_JM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -536,7 +536,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>Rotonda Atenas</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>22.73443282500916</v>
+        <v>24.5931819398397</v>
       </c>
       <c r="F2" t="n">
-        <v>592249344</v>
+        <v>173181877</v>
       </c>
       <c r="G2" t="n">
-        <v>14500</v>
+        <v>4240</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -559,49 +559,49 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>816844224.6119645</v>
+        <v>263621181.0834101</v>
       </c>
       <c r="J2" t="n">
-        <v>987906240.4622535</v>
+        <v>367741369.5578082</v>
       </c>
       <c r="K2" t="n">
-        <v>1249752218.579044</v>
+        <v>573508198.5736868</v>
       </c>
       <c r="L2" t="n">
-        <v>43.82075709578638</v>
+        <v>84.26765198130998</v>
       </c>
       <c r="M2" t="n">
-        <v>-40.0500452631133</v>
+        <v>-52.90661009713344</v>
       </c>
       <c r="N2" t="n">
-        <v>530</v>
+        <v>153</v>
       </c>
       <c r="O2" t="n">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="P2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="R2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="T2" t="n">
-        <v>-33.4119286</v>
+        <v>-33.4131298</v>
       </c>
       <c r="U2" t="n">
-        <v>-70.54692420000001</v>
+        <v>-70.54787109999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4201744792-vive-a-minutos-de-mall-los-dominicos-excelente-ubicacion-y-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2059394253-solida-cercana-al-metro-los-dominicos-bajo-valor-tasacion-_JM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -611,7 +611,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rotonda Atenas</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -620,13 +620,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>18.99475869940124</v>
+        <v>18.08394167149637</v>
       </c>
       <c r="F3" t="n">
-        <v>173181877</v>
+        <v>592249344</v>
       </c>
       <c r="G3" t="n">
-        <v>4240</v>
+        <v>14500</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -634,49 +634,49 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>243792239.458679</v>
+        <v>771177591.382915</v>
       </c>
       <c r="J3" t="n">
-        <v>371736032.95579</v>
+        <v>989431677.1931365</v>
       </c>
       <c r="K3" t="n">
-        <v>583142164.3818694</v>
+        <v>1239007624.784108</v>
       </c>
       <c r="L3" t="n">
-        <v>91.28787495387859</v>
+        <v>47.28270220015131</v>
       </c>
       <c r="M3" t="n">
-        <v>-53.41267414326868</v>
+        <v>-40.14247192083852</v>
       </c>
       <c r="N3" t="n">
-        <v>153</v>
+        <v>530</v>
       </c>
       <c r="O3" t="n">
-        <v>40</v>
+        <v>250</v>
       </c>
       <c r="P3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="R3" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S3" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-33.4131298</v>
+        <v>-33.4119286</v>
       </c>
       <c r="U3" t="n">
-        <v>-70.54787109999999</v>
+        <v>-70.54692420000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2059405379-gran-potencial-para-remodelar-las-tranqueras-con-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4201733452-excelente-oportunidad-las-condes-ureta-bravo-propiedades-_JM</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -686,7 +686,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Metro Hernando De Magallanes</t>
+          <t>Colón Oriente - Vital Apoquindo</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -695,13 +695,13 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>12.84014173976164</v>
+        <v>17.97847892629181</v>
       </c>
       <c r="F4" t="n">
-        <v>540000000</v>
+        <v>175000000</v>
       </c>
       <c r="G4" t="n">
-        <v>540000000</v>
+        <v>175000000</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -709,59 +709,59 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>629142024.8129748</v>
+        <v>226797075.185349</v>
       </c>
       <c r="J4" t="n">
-        <v>694244865.9809703</v>
+        <v>288105992.7133255</v>
       </c>
       <c r="K4" t="n">
-        <v>899928762.4531304</v>
+        <v>579356802.0363342</v>
       </c>
       <c r="L4" t="n">
-        <v>39.00449983991355</v>
+        <v>122.3715353959309</v>
       </c>
       <c r="M4" t="n">
-        <v>-22.21764589688708</v>
+        <v>-39.25846583339539</v>
       </c>
       <c r="N4" t="n">
-        <v>444</v>
+        <v>160</v>
       </c>
       <c r="O4" t="n">
-        <v>138</v>
+        <v>60</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R4" t="n">
         <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="T4" t="n">
-        <v>-33.4006389</v>
+        <v>-33.4130798</v>
       </c>
       <c r="U4" t="n">
-        <v>-70.5579754</v>
+        <v>-70.5363143</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1913092679-casa-en-venta-de-5-dorm-en-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3915739572-terreno-en-valle-escondido-precio-unico-_JM</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>Valle Escondido</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -770,13 +770,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12.57283472142889</v>
+        <v>13.44784934115178</v>
       </c>
       <c r="F5" t="n">
-        <v>448884158</v>
+        <v>693952852</v>
       </c>
       <c r="G5" t="n">
-        <v>10990</v>
+        <v>16990</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -784,43 +784,43 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>519235879.5224249</v>
+        <v>1009614809.376689</v>
       </c>
       <c r="J5" t="n">
-        <v>559553379.0205544</v>
+        <v>2347304385.77068</v>
       </c>
       <c r="K5" t="n">
-        <v>747423212.0288947</v>
+        <v>4352602510.7773</v>
       </c>
       <c r="L5" t="n">
-        <v>40.78026173407982</v>
+        <v>142.418159385964</v>
       </c>
       <c r="M5" t="n">
-        <v>-19.77813469990486</v>
+        <v>-70.43617963623591</v>
       </c>
       <c r="N5" t="n">
-        <v>224</v>
+        <v>2040</v>
       </c>
       <c r="O5" t="n">
-        <v>140</v>
+        <v>2040</v>
       </c>
       <c r="P5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="Q5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R5" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>-33.3891264</v>
+        <v>-33.3448698</v>
       </c>
       <c r="U5" t="n">
-        <v>-70.5402646</v>
+        <v>-70.4937958</v>
       </c>
     </row>
     <row r="6">
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>10.73430695296489</v>
+        <v>12.97932308821565</v>
       </c>
       <c r="F6" t="n">
         <v>420292810</v>
@@ -859,19 +859,19 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>477362322.1141524</v>
+        <v>485031565.1518294</v>
       </c>
       <c r="J6" t="n">
-        <v>531655302.6126143</v>
+        <v>498783755.6074695</v>
       </c>
       <c r="K6" t="n">
-        <v>757803290.6873889</v>
+        <v>744299740.2543846</v>
       </c>
       <c r="L6" t="n">
-        <v>52.74864507042775</v>
+        <v>51.98007597236043</v>
       </c>
       <c r="M6" t="n">
-        <v>-20.94637109145088</v>
+        <v>-15.73646790318487</v>
       </c>
       <c r="N6" t="n">
         <v>240</v>
@@ -901,7 +901,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4201733452-excelente-oportunidad-las-condes-ureta-bravo-propiedades-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2059405379-gran-potencial-para-remodelar-las-tranqueras-con-las-condes-_JM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Colón Oriente - Vital Apoquindo</t>
+          <t>Metro Hernando De Magallanes</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -920,13 +920,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>10.23783523159774</v>
+        <v>10.43100639837898</v>
       </c>
       <c r="F7" t="n">
-        <v>175000000</v>
+        <v>540000000</v>
       </c>
       <c r="G7" t="n">
-        <v>175000000</v>
+        <v>540000000</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -934,59 +934,59 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>207900497.4138709</v>
+        <v>614994900.0862293</v>
       </c>
       <c r="J7" t="n">
-        <v>321361856.9707766</v>
+        <v>718961308.4494308</v>
       </c>
       <c r="K7" t="n">
-        <v>584071925.9789529</v>
+        <v>881169442.1959238</v>
       </c>
       <c r="L7" t="n">
-        <v>117.0554066717661</v>
+        <v>37.02209548435196</v>
       </c>
       <c r="M7" t="n">
-        <v>-45.54425293356647</v>
+        <v>-24.89164664999748</v>
       </c>
       <c r="N7" t="n">
-        <v>160</v>
+        <v>444</v>
       </c>
       <c r="O7" t="n">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
         <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="T7" t="n">
-        <v>-33.4130798</v>
+        <v>-33.4006389</v>
       </c>
       <c r="U7" t="n">
-        <v>-70.5363143</v>
+        <v>-70.5579754</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3915739572-terreno-en-valle-escondido-precio-unico-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1913092679-casa-en-venta-de-5-dorm-en-las-condes-_JM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Valle Escondido</t>
+          <t>Estoril</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -995,13 +995,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8.784736699381178</v>
+        <v>9.04212142528484</v>
       </c>
       <c r="F8" t="n">
-        <v>693952852</v>
+        <v>448884158</v>
       </c>
       <c r="G8" t="n">
-        <v>16990</v>
+        <v>10990</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1009,49 +1009,49 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>896043099.1862906</v>
+        <v>494541495.3681083</v>
       </c>
       <c r="J8" t="n">
-        <v>2300470168.907014</v>
+        <v>504940546.8105628</v>
       </c>
       <c r="K8" t="n">
-        <v>4650360596.862105</v>
+        <v>694725756.9828374</v>
       </c>
       <c r="L8" t="n">
-        <v>163.1978344435366</v>
+        <v>39.64511522776001</v>
       </c>
       <c r="M8" t="n">
-        <v>-69.83430337939541</v>
+        <v>-11.10158199111575</v>
       </c>
       <c r="N8" t="n">
-        <v>2040</v>
+        <v>224</v>
       </c>
       <c r="O8" t="n">
-        <v>2040</v>
+        <v>140</v>
       </c>
       <c r="P8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>-33.3448698</v>
+        <v>-33.3891264</v>
       </c>
       <c r="U8" t="n">
-        <v>-70.4937958</v>
+        <v>-70.5402646</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1918940429-dehesa-central-a-pasos-del-portal-condominio-cerrado-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3851356140-casa-en-venta-de-4-dorm-en-lo-barnechea-las-lomas-_JM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1070,13 +1070,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8.461613750963808</v>
+        <v>9.040184823932867</v>
       </c>
       <c r="F9" t="n">
-        <v>653516517</v>
+        <v>1135484948</v>
       </c>
       <c r="G9" t="n">
-        <v>16000</v>
+        <v>27800</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1084,59 +1084,59 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>714022291.6463907</v>
+        <v>1286426738.742129</v>
       </c>
       <c r="J9" t="n">
-        <v>715061883.313911</v>
+        <v>1669675937.847288</v>
       </c>
       <c r="K9" t="n">
-        <v>956923020.5890279</v>
+        <v>2323547188.023273</v>
       </c>
       <c r="L9" t="n">
-        <v>33.96918988562619</v>
+        <v>62.11507429509355</v>
       </c>
       <c r="M9" t="n">
-        <v>-8.606998603908615</v>
+        <v>-31.99369277226456</v>
       </c>
       <c r="N9" t="n">
-        <v>412</v>
+        <v>2158</v>
       </c>
       <c r="O9" t="n">
-        <v>152</v>
+        <v>460</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="T9" t="n">
-        <v>-33.3554101</v>
+        <v>-33.341676</v>
       </c>
       <c r="U9" t="n">
-        <v>-70.5156223</v>
+        <v>-70.5324222</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2057119567-bajo-precio-ideal-remodelar-ubicacion-colegios-terreno-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1926980767-colegio-aleman-_JM</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sebastián Elcano</t>
+          <t>Nuestra Señora Del Rosario</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>7.768761615388793</v>
+        <v>7.908548438613347</v>
       </c>
       <c r="F10" t="n">
-        <v>551404561</v>
+        <v>518728735</v>
       </c>
       <c r="G10" t="n">
-        <v>13500</v>
+        <v>12700</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1159,59 +1159,59 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>603622524.7366664</v>
+        <v>564056808.9383899</v>
       </c>
       <c r="J10" t="n">
-        <v>672152993.2548093</v>
+        <v>573152890.0686299</v>
       </c>
       <c r="K10" t="n">
-        <v>1045314597.480842</v>
+        <v>887080322.9194871</v>
       </c>
       <c r="L10" t="n">
-        <v>65.71302622716024</v>
+        <v>56.35904827111978</v>
       </c>
       <c r="M10" t="n">
-        <v>-17.9644267698789</v>
+        <v>-9.495573696245877</v>
       </c>
       <c r="N10" t="n">
-        <v>420</v>
+        <v>241</v>
       </c>
       <c r="O10" t="n">
-        <v>160</v>
+        <v>119</v>
       </c>
       <c r="P10" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R10" t="n">
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>-33.4266283</v>
+        <v>-33.3895733</v>
       </c>
       <c r="U10" t="n">
-        <v>-70.56975559999999</v>
+        <v>-70.56936159999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3851356140-casa-en-venta-de-4-dorm-en-lo-barnechea-las-lomas-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3762939998-amplia-casa-en-san-carlos-de-apoquindo-_JM</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>7.621723872489305</v>
+        <v>7.899688245038343</v>
       </c>
       <c r="F11" t="n">
-        <v>1135484948</v>
+        <v>774008625</v>
       </c>
       <c r="G11" t="n">
-        <v>27800</v>
+        <v>18950</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1234,59 +1234,59 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1271574560.305465</v>
+        <v>848816308.9860973</v>
       </c>
       <c r="J11" t="n">
-        <v>1785548972.6764</v>
+        <v>946970078.6367455</v>
       </c>
       <c r="K11" t="n">
-        <v>2468145616.618157</v>
+        <v>1013506632.935233</v>
       </c>
       <c r="L11" t="n">
-        <v>67.01418301168881</v>
+        <v>17.39129119963573</v>
       </c>
       <c r="M11" t="n">
-        <v>-36.40695576677487</v>
+        <v>-18.26472214261934</v>
       </c>
       <c r="N11" t="n">
-        <v>2158</v>
+        <v>524</v>
       </c>
       <c r="O11" t="n">
-        <v>460</v>
+        <v>250</v>
       </c>
       <c r="P11" t="n">
         <v>5</v>
       </c>
       <c r="Q11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R11" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="T11" t="n">
-        <v>-33.341676</v>
+        <v>-33.4013109</v>
       </c>
       <c r="U11" t="n">
-        <v>-70.5324222</v>
+        <v>-70.5172651</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1999203389-en-condominio-con-piscina-y-vistas-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4050080372-casa-en-venta-de-5-dorm-en-santa-maria-manquehue-_JM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Santa María De Manquehue</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1295,13 +1295,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>7.368471554592512</v>
+        <v>7.768525762997385</v>
       </c>
       <c r="F12" t="n">
-        <v>673938908</v>
+        <v>1037457471</v>
       </c>
       <c r="G12" t="n">
-        <v>16500</v>
+        <v>25400</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1309,49 +1309,49 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>733985863.6822748</v>
+        <v>1321487480.303295</v>
       </c>
       <c r="J12" t="n">
-        <v>814917384.6623542</v>
+        <v>3656163575.541852</v>
       </c>
       <c r="K12" t="n">
-        <v>1051674085.690798</v>
+        <v>5718416600.453251</v>
       </c>
       <c r="L12" t="n">
-        <v>38.98410170009461</v>
+        <v>120.2607331237449</v>
       </c>
       <c r="M12" t="n">
-        <v>-17.29972624412302</v>
+        <v>-71.62442408375433</v>
       </c>
       <c r="N12" t="n">
-        <v>392</v>
+        <v>400000</v>
       </c>
       <c r="O12" t="n">
-        <v>190</v>
+        <v>250000</v>
       </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R12" t="n">
         <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-33.3333379</v>
+        <v>-33.3784956</v>
       </c>
       <c r="U12" t="n">
-        <v>-70.5110471</v>
+        <v>-70.578636</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3762939998-amplia-casa-en-san-carlos-de-apoquindo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2057119567-bajo-precio-ideal-remodelar-ubicacion-colegios-terreno-_JM</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>Sebastián Elcano</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1370,13 +1370,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>7.353637492009218</v>
+        <v>6.371164292764016</v>
       </c>
       <c r="F13" t="n">
-        <v>774008625</v>
+        <v>551404561</v>
       </c>
       <c r="G13" t="n">
-        <v>18950</v>
+        <v>13500</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1384,49 +1384,49 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>845269079.8858881</v>
+        <v>596097158.8147789</v>
       </c>
       <c r="J13" t="n">
-        <v>969050418.4265652</v>
+        <v>701482425.5205297</v>
       </c>
       <c r="K13" t="n">
-        <v>1086138660.46817</v>
+        <v>995991896.6105222</v>
       </c>
       <c r="L13" t="n">
-        <v>24.85624855034676</v>
+        <v>57.00709287178568</v>
       </c>
       <c r="M13" t="n">
-        <v>-20.12710481496433</v>
+        <v>-21.39438695262616</v>
       </c>
       <c r="N13" t="n">
-        <v>524</v>
+        <v>420</v>
       </c>
       <c r="O13" t="n">
-        <v>250</v>
+        <v>160</v>
       </c>
       <c r="P13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
         <v>2</v>
       </c>
       <c r="S13" t="n">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="T13" t="n">
-        <v>-33.4013109</v>
+        <v>-33.4266283</v>
       </c>
       <c r="U13" t="n">
-        <v>-70.5172651</v>
+        <v>-70.56975559999999</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4179308246-exclusiva-casa-en-venta-en-las-condes-con-gran-terreno-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3994610292-se-liquida-casa-gran-terreno-y-construcion-_JM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sebastián Elcano</t>
+          <t>Metro Hernando De Magallanes</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1445,13 +1445,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>7.167052683256014</v>
+        <v>5.612454791254674</v>
       </c>
       <c r="F14" t="n">
-        <v>445208127</v>
+        <v>653108069</v>
       </c>
       <c r="G14" t="n">
-        <v>10900</v>
+        <v>15990</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1459,49 +1459,49 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>498447751.0819235</v>
+        <v>692476391.5110631</v>
       </c>
       <c r="J14" t="n">
-        <v>742838464.2170169</v>
+        <v>701445694.8928447</v>
       </c>
       <c r="K14" t="n">
-        <v>1481077544.650872</v>
+        <v>1078829195.940165</v>
       </c>
       <c r="L14" t="n">
-        <v>132.2804136973012</v>
+        <v>55.07950326619694</v>
       </c>
       <c r="M14" t="n">
-        <v>-40.06662976596559</v>
+        <v>-6.891142998636396</v>
       </c>
       <c r="N14" t="n">
-        <v>368</v>
+        <v>576</v>
       </c>
       <c r="O14" t="n">
-        <v>368</v>
+        <v>180</v>
       </c>
       <c r="P14" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3</v>
       </c>
-      <c r="Q14" t="n">
-        <v>2</v>
-      </c>
       <c r="R14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S14" t="n">
-        <v>70</v>
+        <v>10</v>
       </c>
       <c r="T14" t="n">
-        <v>-33.4258973</v>
+        <v>-33.4095851</v>
       </c>
       <c r="U14" t="n">
-        <v>-70.57036069999999</v>
+        <v>-70.5599108</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1698705917-casa-en-venta-los-dominicos-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4105686464-casa-para-remodelar-barrio-residencial-las-condes-_JM</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>Alto Las Condes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6.890160576531251</v>
+        <v>5.567514311939378</v>
       </c>
       <c r="F15" t="n">
-        <v>735206082</v>
+        <v>324716019</v>
       </c>
       <c r="G15" t="n">
-        <v>18000</v>
+        <v>7950</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1534,59 +1534,59 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>789806255.1590754</v>
+        <v>348311542.8408611</v>
       </c>
       <c r="J15" t="n">
-        <v>792436875.0570254</v>
+        <v>423807151.9683594</v>
       </c>
       <c r="K15" t="n">
-        <v>914314798.7013974</v>
+        <v>645416274.0226049</v>
       </c>
       <c r="L15" t="n">
-        <v>15.71210874473278</v>
+        <v>70.10375587147362</v>
       </c>
       <c r="M15" t="n">
-        <v>-7.222126437882763</v>
+        <v>-23.38118469877954</v>
       </c>
       <c r="N15" t="n">
-        <v>507</v>
+        <v>212</v>
       </c>
       <c r="O15" t="n">
-        <v>184</v>
+        <v>82</v>
       </c>
       <c r="P15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S15" t="n">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="T15" t="n">
-        <v>-33.4149605</v>
+        <v>-33.3917603</v>
       </c>
       <c r="U15" t="n">
-        <v>-70.53007049999999</v>
+        <v>-70.5398996</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4034196578-casa-en-venta-de-5-dorm-espectacular-vista-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1909455733-los-litres-sta-martina-370-m2-construidos-en-680-m2-_JM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1595,13 +1595,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5.556951655170388</v>
+        <v>5.409540615631936</v>
       </c>
       <c r="F16" t="n">
-        <v>853655950</v>
+        <v>894500733</v>
       </c>
       <c r="G16" t="n">
-        <v>20900</v>
+        <v>21900</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1609,49 +1609,49 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>912819417.7471167</v>
+        <v>955661192.2720538</v>
       </c>
       <c r="J16" t="n">
-        <v>1064674868.85672</v>
+        <v>1130603569.096396</v>
       </c>
       <c r="K16" t="n">
-        <v>1183409571.735484</v>
+        <v>1565408110.530171</v>
       </c>
       <c r="L16" t="n">
-        <v>25.41528516390505</v>
+        <v>53.93109794845604</v>
       </c>
       <c r="M16" t="n">
-        <v>-19.82003379898681</v>
+        <v>-20.88290206664524</v>
       </c>
       <c r="N16" t="n">
-        <v>900</v>
+        <v>680</v>
       </c>
       <c r="O16" t="n">
-        <v>300</v>
+        <v>370</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
         <v>5</v>
       </c>
       <c r="R16" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="T16" t="n">
-        <v>-33.4042302</v>
+        <v>-33.3164187</v>
       </c>
       <c r="U16" t="n">
-        <v>-70.52972269999999</v>
+        <v>-70.5500026</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2046359361-casa-en-venta-los-dominicosseguridad-247-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2045838433-amplia-casa-para-remodelar-en-las-condes-con-terreno-434-mt2-_JM</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1670,13 +1670,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4.90252759964082</v>
+        <v>5.026750640211171</v>
       </c>
       <c r="F17" t="n">
-        <v>608587257</v>
+        <v>550587666</v>
       </c>
       <c r="G17" t="n">
-        <v>14900</v>
+        <v>13480</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1684,49 +1684,49 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>643279335.7706861</v>
+        <v>584041815.0274228</v>
       </c>
       <c r="J17" t="n">
-        <v>707636582.6727388</v>
+        <v>665522350.7569374</v>
       </c>
       <c r="K17" t="n">
-        <v>936345925.1473588</v>
+        <v>949541402.0205666</v>
       </c>
       <c r="L17" t="n">
-        <v>41.4148443640042</v>
+        <v>54.91920542975601</v>
       </c>
       <c r="M17" t="n">
-        <v>-13.99720253277892</v>
+        <v>-17.26984595276409</v>
       </c>
       <c r="N17" t="n">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="O17" t="n">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="P17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
       <c r="R17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="S17" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="T17" t="n">
-        <v>-33.4095244</v>
+        <v>-33.4031717</v>
       </c>
       <c r="U17" t="n">
-        <v>-70.5351452</v>
+        <v>-70.54493549999999</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1904332139-casa-sector-el-monasterio-la-dehesa-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4096296848-casa-estilo-colonial-en-calle-tranquila-en-el-arrayan-_JM</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1736,7 +1736,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Camino A Farellones</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1745,13 +1745,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4.464948680290737</v>
+        <v>4.364983549069128</v>
       </c>
       <c r="F18" t="n">
-        <v>1061555892</v>
+        <v>702530256</v>
       </c>
       <c r="G18" t="n">
-        <v>25990</v>
+        <v>17200</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -1759,59 +1759,59 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1121600032.29404</v>
+        <v>740827342.1383229</v>
       </c>
       <c r="J18" t="n">
-        <v>1344789035.517647</v>
+        <v>877370686.6888454</v>
       </c>
       <c r="K18" t="n">
-        <v>1714780605.121176</v>
+        <v>1405587026.959661</v>
       </c>
       <c r="L18" t="n">
-        <v>44.10956344530312</v>
+        <v>75.76725492506586</v>
       </c>
       <c r="M18" t="n">
-        <v>-21.06152980408729</v>
+        <v>-19.92777207415998</v>
       </c>
       <c r="N18" t="n">
-        <v>1100</v>
+        <v>1760</v>
       </c>
       <c r="O18" t="n">
-        <v>470</v>
+        <v>348</v>
       </c>
       <c r="P18" t="n">
         <v>6</v>
       </c>
       <c r="Q18" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="R18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="T18" t="n">
-        <v>-33.3499985</v>
+        <v>-33.3609338</v>
       </c>
       <c r="U18" t="n">
-        <v>-70.51667019999999</v>
+        <v>-70.47830380000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3806992554-casa-cercana-metro-colon-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1971319439-colegio-aleman-_JM</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Barrio El Golf</t>
+          <t>Estadio Croata</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4.382564037673125</v>
+        <v>4.341437205068405</v>
       </c>
       <c r="F19" t="n">
-        <v>608587257</v>
+        <v>520770975</v>
       </c>
       <c r="G19" t="n">
-        <v>14900</v>
+        <v>12750</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -1834,49 +1834,49 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>645829490.2166635</v>
+        <v>552089877.4964927</v>
       </c>
       <c r="J19" t="n">
-        <v>849781837.6759381</v>
+        <v>721394805.847463</v>
       </c>
       <c r="K19" t="n">
-        <v>1083888542.157176</v>
+        <v>878223367.3576334</v>
       </c>
       <c r="L19" t="n">
-        <v>51.54958984985569</v>
+        <v>45.20873829664095</v>
       </c>
       <c r="M19" t="n">
-        <v>-28.38311787594559</v>
+        <v>-27.81054551838351</v>
       </c>
       <c r="N19" t="n">
-        <v>375</v>
+        <v>220</v>
       </c>
       <c r="O19" t="n">
         <v>170</v>
       </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
         <v>2</v>
       </c>
       <c r="S19" t="n">
-        <v>45</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>-33.4241535</v>
+        <v>-33.3885668</v>
       </c>
       <c r="U19" t="n">
-        <v>-70.5920527</v>
+        <v>-70.5579899</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1997594621-gran-terreno-potencial-de-remodelacion-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1698705917-casa-en-venta-los-dominicos-_JM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1895,13 +1895,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.334237393219198</v>
+        <v>4.150747805144098</v>
       </c>
       <c r="F20" t="n">
-        <v>673530460</v>
+        <v>735206082</v>
       </c>
       <c r="G20" t="n">
-        <v>16490</v>
+        <v>18000</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -1909,59 +1909,59 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>708008655.8721253</v>
+        <v>769184346.4019855</v>
       </c>
       <c r="J20" t="n">
-        <v>795484712.629389</v>
+        <v>818605851.2125367</v>
       </c>
       <c r="K20" t="n">
-        <v>947648623.4418827</v>
+        <v>937330127.8671547</v>
       </c>
       <c r="L20" t="n">
-        <v>30.12502487667593</v>
+        <v>20.54050569222148</v>
       </c>
       <c r="M20" t="n">
-        <v>-15.33081034659766</v>
+        <v>-10.18802505369381</v>
       </c>
       <c r="N20" t="n">
-        <v>385</v>
+        <v>507</v>
       </c>
       <c r="O20" t="n">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="P20" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q20" t="n">
         <v>4</v>
       </c>
       <c r="R20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S20" t="n">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="T20" t="n">
-        <v>-33.3996367</v>
+        <v>-33.4149605</v>
       </c>
       <c r="U20" t="n">
-        <v>-70.5496942</v>
+        <v>-70.53007049999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3741540074-condominio-camino-la-laguna-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4201709018-oportunidad-venta-de-casa-en-las-condes-_JM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>El Huinganal</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1970,63 +1970,63 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.061434387716982</v>
+        <v>3.881731708597933</v>
       </c>
       <c r="F21" t="n">
-        <v>755220025</v>
+        <v>544900000</v>
       </c>
       <c r="G21" t="n">
-        <v>18490</v>
+        <v>544900000</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>UF</t>
+          <t>CLP</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>791367514.2885705</v>
+        <v>572720090.8075279</v>
       </c>
       <c r="J21" t="n">
-        <v>890017807.4497908</v>
+        <v>716692777.7596564</v>
       </c>
       <c r="K21" t="n">
-        <v>1025459338.564049</v>
+        <v>944160499.5038462</v>
       </c>
       <c r="L21" t="n">
-        <v>26.30192590710438</v>
+        <v>51.827005967246</v>
       </c>
       <c r="M21" t="n">
-        <v>-15.14551521570486</v>
+        <v>-23.97021193609227</v>
       </c>
       <c r="N21" t="n">
-        <v>831</v>
+        <v>456</v>
       </c>
       <c r="O21" t="n">
-        <v>242</v>
+        <v>168</v>
       </c>
       <c r="P21" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q21" t="n">
         <v>5</v>
       </c>
       <c r="R21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S21" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="T21" t="n">
-        <v>-33.3421149</v>
+        <v>-33.4131876</v>
       </c>
       <c r="U21" t="n">
-        <v>-70.4964981</v>
+        <v>-70.53248859999999</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4191864430-amplia-casa-de-4-dorm-mas-servicio-piscina-en-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4182508496-linda-casa-en-exelente-sector-del-arrayan-175378-_JM</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>El Huinganal</t>
+          <t>El Arrayán</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>3.751275940012375</v>
+        <v>3.754577445657583</v>
       </c>
       <c r="F22" t="n">
-        <v>836909590</v>
+        <v>702530256</v>
       </c>
       <c r="G22" t="n">
-        <v>20490</v>
+        <v>17200</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2059,59 +2059,59 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>870767702.5803556</v>
+        <v>732570925.0154493</v>
       </c>
       <c r="J22" t="n">
-        <v>902575900.0881163</v>
+        <v>800107853.6865262</v>
       </c>
       <c r="K22" t="n">
-        <v>1109808438.380666</v>
+        <v>1433357470.393094</v>
       </c>
       <c r="L22" t="n">
-        <v>26.48428079865346</v>
+        <v>87.58651001221213</v>
       </c>
       <c r="M22" t="n">
-        <v>-7.275433576467691</v>
+        <v>-12.19555554128532</v>
       </c>
       <c r="N22" t="n">
-        <v>950</v>
+        <v>1770</v>
       </c>
       <c r="O22" t="n">
-        <v>234</v>
+        <v>284</v>
       </c>
       <c r="P22" t="n">
         <v>5</v>
       </c>
       <c r="Q22" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
         <v>3</v>
       </c>
       <c r="S22" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="T22" t="n">
-        <v>-33.3446935</v>
+        <v>-33.3617083</v>
       </c>
       <c r="U22" t="n">
-        <v>-70.5094564</v>
+        <v>-70.48556809999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1943852377-casa-en-venta-de-4-dorm-amplia-sector-tabancura-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3793872376-amplia-casa-en-condominio-_JM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>La Llavería</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2120,13 +2120,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3.415558755318286</v>
+        <v>3.399419829068307</v>
       </c>
       <c r="F23" t="n">
-        <v>530982170</v>
+        <v>592249344</v>
       </c>
       <c r="G23" t="n">
-        <v>13000</v>
+        <v>14500</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2134,49 +2134,49 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>551184638.4746212</v>
+        <v>616079111.389401</v>
       </c>
       <c r="J23" t="n">
-        <v>591483558.6758503</v>
+        <v>700995128.2166898</v>
       </c>
       <c r="K23" t="n">
-        <v>681514442.6273643</v>
+        <v>941482900.3548892</v>
       </c>
       <c r="L23" t="n">
-        <v>22.0343916988177</v>
+        <v>46.42026397434537</v>
       </c>
       <c r="M23" t="n">
-        <v>-10.22875239529807</v>
+        <v>-15.51305848491926</v>
       </c>
       <c r="N23" t="n">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="O23" t="n">
-        <v>112</v>
+        <v>190</v>
       </c>
       <c r="P23" t="n">
         <v>4</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R23" t="n">
         <v>2</v>
       </c>
       <c r="S23" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="T23" t="n">
-        <v>-33.3846327</v>
+        <v>-33.3317871</v>
       </c>
       <c r="U23" t="n">
-        <v>-70.54068580000001</v>
+        <v>-70.5238346</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1909455733-los-litres-sta-martina-370-m2-construidos-en-680-m2-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3853061210-excelente-casa-condominio-el-arrayan-_JM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>Camino A Farellones</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2195,13 +2195,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>3.114137308495647</v>
+        <v>3.246776748877398</v>
       </c>
       <c r="F24" t="n">
-        <v>894500733</v>
+        <v>694361299</v>
       </c>
       <c r="G24" t="n">
-        <v>21900</v>
+        <v>17000</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2209,49 +2209,49 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>928993815.9342552</v>
+        <v>725269181.1144109</v>
       </c>
       <c r="J24" t="n">
-        <v>1107628839.619724</v>
+        <v>951955878.2444019</v>
       </c>
       <c r="K24" t="n">
-        <v>1569785379.327997</v>
+        <v>1343689693.510168</v>
       </c>
       <c r="L24" t="n">
-        <v>57.85255317239131</v>
+        <v>64.96314866359657</v>
       </c>
       <c r="M24" t="n">
-        <v>-19.24183435787895</v>
+        <v>-27.05950823261453</v>
       </c>
       <c r="N24" t="n">
-        <v>680</v>
+        <v>1600</v>
       </c>
       <c r="O24" t="n">
-        <v>370</v>
+        <v>240</v>
       </c>
       <c r="P24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R24" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S24" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-33.3164187</v>
+        <v>-33.3617057</v>
       </c>
       <c r="U24" t="n">
-        <v>-70.5500026</v>
+        <v>-70.47811590000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4201709018-oportunidad-venta-de-casa-en-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2025082337-vendo-casa-cercana-a-hernando-de-magallanes-_JM</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2261,7 +2261,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>Metro Hernando De Magallanes</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2270,73 +2270,73 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2.989365320366729</v>
+        <v>2.990451473828742</v>
       </c>
       <c r="F25" t="n">
-        <v>544900000</v>
+        <v>649432039</v>
       </c>
       <c r="G25" t="n">
-        <v>544900000</v>
+        <v>15900</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>UF</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>567736420.3343048</v>
+        <v>671065820.5639592</v>
       </c>
       <c r="J25" t="n">
-        <v>763922033.17269</v>
+        <v>723428611.140813</v>
       </c>
       <c r="K25" t="n">
-        <v>918519176.6651314</v>
+        <v>1041712086.172741</v>
       </c>
       <c r="L25" t="n">
-        <v>45.91865937862401</v>
+        <v>51.23467055364181</v>
       </c>
       <c r="M25" t="n">
-        <v>-28.67073126076186</v>
+        <v>-10.22859353380064</v>
       </c>
       <c r="N25" t="n">
-        <v>456</v>
+        <v>425</v>
       </c>
       <c r="O25" t="n">
-        <v>168</v>
+        <v>190</v>
       </c>
       <c r="P25" t="n">
         <v>4</v>
       </c>
       <c r="Q25" t="n">
+        <v>3</v>
+      </c>
+      <c r="R25" t="n">
         <v>5</v>
       </c>
-      <c r="R25" t="n">
-        <v>3</v>
-      </c>
       <c r="S25" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="T25" t="n">
-        <v>-33.4131876</v>
+        <v>-33.4112393</v>
       </c>
       <c r="U25" t="n">
-        <v>-70.53248859999999</v>
+        <v>-70.5586484</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4050080372-casa-en-venta-de-5-dorm-en-santa-maria-manquehue-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3863197110-casa-en-exclusivo-condominio-ubicado-en-buen-sector-_JM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Santa María De Manquehue</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2345,13 +2345,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2.934522477883208</v>
+        <v>2.972991046628121</v>
       </c>
       <c r="F26" t="n">
-        <v>1037457471</v>
+        <v>980274776</v>
       </c>
       <c r="G26" t="n">
-        <v>25400</v>
+        <v>24000</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -2359,43 +2359,43 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1148676633.770634</v>
+        <v>1018085543.329853</v>
       </c>
       <c r="J26" t="n">
-        <v>3790025927.859347</v>
+        <v>1271808987.542601</v>
       </c>
       <c r="K26" t="n">
-        <v>5439576117.710694</v>
+        <v>1457377998.578704</v>
       </c>
       <c r="L26" t="n">
-        <v>113.2155707009533</v>
+        <v>34.54075726400194</v>
       </c>
       <c r="M26" t="n">
-        <v>-72.62663921705757</v>
+        <v>-22.92279850183366</v>
       </c>
       <c r="N26" t="n">
-        <v>400000</v>
+        <v>900</v>
       </c>
       <c r="O26" t="n">
-        <v>250000</v>
+        <v>320</v>
       </c>
       <c r="P26" t="n">
         <v>5</v>
       </c>
       <c r="Q26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="T26" t="n">
-        <v>-33.3784956</v>
+        <v>-33.3190125</v>
       </c>
       <c r="U26" t="n">
-        <v>-70.578636</v>
+        <v>-70.5664357</v>
       </c>
     </row>
     <row r="27">
@@ -2420,7 +2420,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2.673378228474488</v>
+        <v>2.870972793534543</v>
       </c>
       <c r="F27" t="n">
         <v>633094126</v>
@@ -2434,19 +2434,19 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>650689063.167962</v>
+        <v>652591360.1419528</v>
       </c>
       <c r="J27" t="n">
-        <v>658153679.1373575</v>
+        <v>679115949.334689</v>
       </c>
       <c r="K27" t="n">
-        <v>786270173.8758413</v>
+        <v>817465362.8759106</v>
       </c>
       <c r="L27" t="n">
-        <v>20.60022073956733</v>
+        <v>24.27773974318824</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.807553453200026</v>
+        <v>-6.776725444274327</v>
       </c>
       <c r="N27" t="n">
         <v>390</v>
@@ -2476,17 +2476,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3152801196-venta-casa-425-mts-en-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3816280262-casa-en-venta-4-dor-cerca-de-colegio-huinganal-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Metro Hernando De Magallanes</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2495,13 +2495,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2.667794865584999</v>
+        <v>2.711128322881763</v>
       </c>
       <c r="F28" t="n">
-        <v>649432039</v>
+        <v>571418505</v>
       </c>
       <c r="G28" t="n">
-        <v>15900</v>
+        <v>13990</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -2509,59 +2509,59 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>668997000.1642915</v>
+        <v>588950427.4438114</v>
       </c>
       <c r="J28" t="n">
-        <v>733375771.0040894</v>
+        <v>646665165.0474464</v>
       </c>
       <c r="K28" t="n">
-        <v>951841477.3938806</v>
+        <v>776366747.7080895</v>
       </c>
       <c r="L28" t="n">
-        <v>38.56746955825078</v>
+        <v>28.98197249430115</v>
       </c>
       <c r="M28" t="n">
-        <v>-11.44621015896928</v>
+        <v>-11.63610847074551</v>
       </c>
       <c r="N28" t="n">
-        <v>429</v>
+        <v>317</v>
       </c>
       <c r="O28" t="n">
-        <v>191</v>
+        <v>154</v>
       </c>
       <c r="P28" t="n">
         <v>4</v>
       </c>
       <c r="Q28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="S28" t="n">
-        <v>63</v>
+        <v>22</v>
       </c>
       <c r="T28" t="n">
-        <v>-33.4116124</v>
+        <v>-33.3258909</v>
       </c>
       <c r="U28" t="n">
-        <v>-70.55844020000001</v>
+        <v>-70.51562149999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4201707858-casa-con-gran-frente-a-blaise-cendrars-para-remodelar-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3152801196-venta-casa-425-mts-en-las-condes-_JM</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Nuestra Señora Del Rosario</t>
+          <t>Metro Hernando De Magallanes</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2570,13 +2570,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2.126736767206013</v>
+        <v>2.496257505430513</v>
       </c>
       <c r="F29" t="n">
-        <v>510559779</v>
+        <v>649432039</v>
       </c>
       <c r="G29" t="n">
-        <v>12500</v>
+        <v>15900</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -2584,49 +2584,49 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>525322768.1468455</v>
+        <v>667796909.5186195</v>
       </c>
       <c r="J29" t="n">
-        <v>694161561.2467313</v>
+        <v>735696156.2926687</v>
       </c>
       <c r="K29" t="n">
-        <v>851587346.6210884</v>
+        <v>1076614295.598468</v>
       </c>
       <c r="L29" t="n">
-        <v>47.00124534240467</v>
+        <v>55.56878102231325</v>
       </c>
       <c r="M29" t="n">
-        <v>-26.44943086692642</v>
+        <v>-11.7255087653811</v>
       </c>
       <c r="N29" t="n">
-        <v>350</v>
+        <v>429</v>
       </c>
       <c r="O29" t="n">
-        <v>120</v>
+        <v>191</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="R29" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S29" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="T29" t="n">
-        <v>-33.3925691</v>
+        <v>-33.4116124</v>
       </c>
       <c r="U29" t="n">
-        <v>-70.5680502</v>
+        <v>-70.55844020000001</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3853061210-excelente-casa-condominio-el-arrayan-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2053114541-casa-mediterranea-6d-5b-5e-los-trapenses-_JM</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2636,7 +2636,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Camino A Farellones</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2645,13 +2645,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1.632282615948746</v>
+        <v>2.44165852643156</v>
       </c>
       <c r="F30" t="n">
-        <v>694361299</v>
+        <v>1021119558</v>
       </c>
       <c r="G30" t="n">
-        <v>17000</v>
+        <v>25000</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -2659,59 +2659,59 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>710249548.2945311</v>
+        <v>1055371051.282784</v>
       </c>
       <c r="J30" t="n">
-        <v>973376126.1248401</v>
+        <v>1402796210.5267</v>
       </c>
       <c r="K30" t="n">
-        <v>1311124325.043917</v>
+        <v>1911282854.915335</v>
       </c>
       <c r="L30" t="n">
-        <v>61.73099592462378</v>
+        <v>61.01469316852422</v>
       </c>
       <c r="M30" t="n">
-        <v>-28.66464664955787</v>
+        <v>-27.20827513380534</v>
       </c>
       <c r="N30" t="n">
-        <v>1600</v>
+        <v>1500</v>
       </c>
       <c r="O30" t="n">
-        <v>240</v>
+        <v>412</v>
       </c>
       <c r="P30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R30" t="n">
         <v>4</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="T30" t="n">
-        <v>-33.3617057</v>
+        <v>-33.3384117</v>
       </c>
       <c r="U30" t="n">
-        <v>-70.47811590000001</v>
+        <v>-70.561412</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4152912686-casa-en-venta-en-el-huinganal-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2046359361-casa-en-venta-los-dominicosseguridad-247-_JM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>El Huinganal</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2720,42 +2720,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1.45377093067777</v>
+        <v>2.264412150237126</v>
       </c>
       <c r="F31" t="n">
-        <v>785000000</v>
+        <v>608587257</v>
       </c>
       <c r="G31" t="n">
-        <v>785000000</v>
+        <v>14900</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>UF</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>799723984.0874234</v>
+        <v>624734485.110985</v>
       </c>
       <c r="J31" t="n">
-        <v>1012813214.015697</v>
+        <v>713086975.323557</v>
       </c>
       <c r="K31" t="n">
-        <v>1680335636.098593</v>
+        <v>925645031.3720046</v>
       </c>
       <c r="L31" t="n">
-        <v>86.94709348426031</v>
+        <v>42.19829511322711</v>
       </c>
       <c r="M31" t="n">
-        <v>-22.49311233928733</v>
+        <v>-14.65455434467039</v>
       </c>
       <c r="N31" t="n">
-        <v>900</v>
+        <v>446</v>
       </c>
       <c r="O31" t="n">
-        <v>375</v>
+        <v>161</v>
       </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
         <v>3</v>
@@ -2764,19 +2764,19 @@
         <v>1</v>
       </c>
       <c r="S31" t="n">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="T31" t="n">
-        <v>-33.3382633</v>
+        <v>-33.4095244</v>
       </c>
       <c r="U31" t="n">
-        <v>-70.49861850000001</v>
+        <v>-70.5351452</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1986959355-estupenda-casa-en-venta-en-condominio-los-trapenses-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4152912686-casa-en-venta-en-el-huinganal-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>El Huinganal</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2795,63 +2795,63 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1.410226505129124</v>
+        <v>2.225067845787626</v>
       </c>
       <c r="F32" t="n">
-        <v>816895646</v>
+        <v>785000000</v>
       </c>
       <c r="G32" t="n">
-        <v>20000</v>
+        <v>785000000</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>UF</t>
+          <t>CLP</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>830340240.9083152</v>
+        <v>811495003.6564882</v>
       </c>
       <c r="J32" t="n">
-        <v>953364219.1106143</v>
+        <v>1190750372.248066</v>
       </c>
       <c r="K32" t="n">
-        <v>1449352340.870064</v>
+        <v>1637704750.553923</v>
       </c>
       <c r="L32" t="n">
-        <v>64.92923560097732</v>
+        <v>69.38563834648235</v>
       </c>
       <c r="M32" t="n">
-        <v>-14.31442153743978</v>
+        <v>-34.07518332175981</v>
       </c>
       <c r="N32" t="n">
-        <v>680</v>
+        <v>900</v>
       </c>
       <c r="O32" t="n">
-        <v>220</v>
+        <v>375</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
       </c>
       <c r="R32" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S32" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T32" t="n">
-        <v>-33.336787</v>
+        <v>-33.3382633</v>
       </c>
       <c r="U32" t="n">
-        <v>-70.56188539999999</v>
+        <v>-70.49861850000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3915799524-venta-de-hermosa-casa-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2004175013-casa-en-venta-tipo-castilo-velasco-con-vista-al-valle-_JM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Estoril</t>
+          <t>El Remanso</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2870,13 +2870,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>0.7713096669800797</v>
+        <v>2.036876878490544</v>
       </c>
       <c r="F33" t="n">
-        <v>436630723</v>
+        <v>771966386</v>
       </c>
       <c r="G33" t="n">
-        <v>10690</v>
+        <v>18900</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -2884,59 +2884,59 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>440550386.0672882</v>
+        <v>792517971.8414869</v>
       </c>
       <c r="J33" t="n">
-        <v>508182800.6428178</v>
+        <v>1008975361.177303</v>
       </c>
       <c r="K33" t="n">
-        <v>672732451.5180762</v>
+        <v>1815499638.026793</v>
       </c>
       <c r="L33" t="n">
-        <v>45.68869020303186</v>
+        <v>101.3881711632343</v>
       </c>
       <c r="M33" t="n">
-        <v>-14.07998805790143</v>
+        <v>-23.49006569404762</v>
       </c>
       <c r="N33" t="n">
-        <v>221</v>
+        <v>1200</v>
       </c>
       <c r="O33" t="n">
-        <v>133.3</v>
+        <v>300</v>
       </c>
       <c r="P33" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q33" t="n">
         <v>5</v>
       </c>
-      <c r="Q33" t="n">
-        <v>3</v>
-      </c>
       <c r="R33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S33" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="T33" t="n">
-        <v>-33.3900576</v>
+        <v>-33.4220764</v>
       </c>
       <c r="U33" t="n">
-        <v>-70.5403834</v>
+        <v>-70.5238011</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4188212420-casa-en-venta-de-6-dorm-en-lo-barnechea-imperdible-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4109455262-2-casas-a-pasos-del-metro-los-dominicos-_JM</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2945,13 +2945,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>0.5487967310330348</v>
+        <v>1.969478574061377</v>
       </c>
       <c r="F34" t="n">
-        <v>1123231514</v>
+        <v>694361299</v>
       </c>
       <c r="G34" t="n">
-        <v>27500</v>
+        <v>17000</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -2959,49 +2959,49 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1131920214.219915</v>
+        <v>717129361.5213426</v>
       </c>
       <c r="J34" t="n">
-        <v>1583227400.709801</v>
+        <v>1156045200.044562</v>
       </c>
       <c r="K34" t="n">
-        <v>2229606744.262478</v>
+        <v>1751618561.484303</v>
       </c>
       <c r="L34" t="n">
-        <v>69.3322089770833</v>
+        <v>89.48518621270901</v>
       </c>
       <c r="M34" t="n">
-        <v>-29.05431566580853</v>
+        <v>-39.936492191375</v>
       </c>
       <c r="N34" t="n">
-        <v>1300</v>
+        <v>526</v>
       </c>
       <c r="O34" t="n">
-        <v>475</v>
+        <v>526</v>
       </c>
       <c r="P34" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R34" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="S34" t="n">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="T34" t="n">
-        <v>-33.3504593</v>
+        <v>-33.4021417</v>
       </c>
       <c r="U34" t="n">
-        <v>-70.53181840000001</v>
+        <v>-70.54351819999999</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3527137746-casa-en-venta-en-sebastian-elcano-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4179309460-manquehue-colon-175368-_JM</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3020,13 +3020,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>0.4718782176411309</v>
+        <v>1.49808677174487</v>
       </c>
       <c r="F35" t="n">
-        <v>639220843</v>
+        <v>424785736</v>
       </c>
       <c r="G35" t="n">
-        <v>15650</v>
+        <v>10400</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -3034,59 +3034,59 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>642544614.1979997</v>
+        <v>432548834.348492</v>
       </c>
       <c r="J35" t="n">
-        <v>704370550.2268987</v>
+        <v>518200847.568398</v>
       </c>
       <c r="K35" t="n">
-        <v>1182982215.942188</v>
+        <v>641054936.8631432</v>
       </c>
       <c r="L35" t="n">
-        <v>76.72631991358772</v>
+        <v>40.23654216179765</v>
       </c>
       <c r="M35" t="n">
-        <v>-9.249351382722065</v>
+        <v>-18.02681566553555</v>
       </c>
       <c r="N35" t="n">
-        <v>369</v>
+        <v>223</v>
       </c>
       <c r="O35" t="n">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="P35" t="n">
         <v>3</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S35" t="n">
-        <v>35</v>
+        <v>61</v>
       </c>
       <c r="T35" t="n">
-        <v>-33.4283312</v>
+        <v>-33.4177771</v>
       </c>
       <c r="U35" t="n">
-        <v>-70.57098999999999</v>
+        <v>-70.5653703</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3583745698-casa-en-venta-san-carlos-de-apoquindo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1986959355-estupenda-casa-en-venta-en-condominio-los-trapenses-_JM</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3095,13 +3095,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>0.156677500839355</v>
+        <v>1.485502558971937</v>
       </c>
       <c r="F36" t="n">
-        <v>755628473</v>
+        <v>816895646</v>
       </c>
       <c r="G36" t="n">
-        <v>18500</v>
+        <v>20000</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
@@ -3109,59 +3109,59 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>756994078.2264291</v>
+        <v>830581629.7566212</v>
       </c>
       <c r="J36" t="n">
-        <v>871602635.4219749</v>
+        <v>921303277.0601766</v>
       </c>
       <c r="K36" t="n">
-        <v>941589122.9923725</v>
+        <v>1401036054.471169</v>
       </c>
       <c r="L36" t="n">
-        <v>21.17880755105498</v>
+        <v>61.91820206423591</v>
       </c>
       <c r="M36" t="n">
-        <v>-13.30585265679326</v>
+        <v>-11.33260172408537</v>
       </c>
       <c r="N36" t="n">
-        <v>497</v>
+        <v>680</v>
       </c>
       <c r="O36" t="n">
-        <v>185.85</v>
+        <v>220</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R36" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S36" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="T36" t="n">
-        <v>-33.38872</v>
+        <v>-33.336787</v>
       </c>
       <c r="U36" t="n">
-        <v>-70.50438</v>
+        <v>-70.56188539999999</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1978119201-colegio-aleman-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3527137746-casa-en-venta-en-sebastian-elcano-las-condes-_JM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Estadio Manquehue</t>
+          <t>Sebastián Elcano</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3170,13 +3170,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>0.05037357321248355</v>
+        <v>1.469187193092278</v>
       </c>
       <c r="F37" t="n">
-        <v>449292605</v>
+        <v>639220843</v>
       </c>
       <c r="G37" t="n">
-        <v>11000</v>
+        <v>15650</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -3184,74 +3184,74 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>449554327.3519086</v>
+        <v>649691113.644027</v>
       </c>
       <c r="J37" t="n">
-        <v>519562808.8652339</v>
+        <v>712657358.6575888</v>
       </c>
       <c r="K37" t="n">
-        <v>735593008.258764</v>
+        <v>980807213.7395022</v>
       </c>
       <c r="L37" t="n">
-        <v>55.05372517551563</v>
+        <v>46.46217373229523</v>
       </c>
       <c r="M37" t="n">
-        <v>-13.52487180880201</v>
+        <v>-10.30460357498013</v>
       </c>
       <c r="N37" t="n">
-        <v>194</v>
+        <v>369</v>
       </c>
       <c r="O37" t="n">
-        <v>96</v>
+        <v>190</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
       </c>
       <c r="Q37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R37" t="n">
         <v>3</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="T37" t="n">
-        <v>-33.3971055</v>
+        <v>-33.4283312</v>
       </c>
       <c r="U37" t="n">
-        <v>-70.57425310000001</v>
+        <v>-70.57098999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1955676239-casa-de-lujo-en-venta-en-cerro-san-luis-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1904332139-casa-sector-el-monasterio-la-dehesa-_JM</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Barrio El Golf</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>-0.4773337327212747</v>
+        <v>1.463874703830868</v>
       </c>
       <c r="F38" t="n">
-        <v>1307033034</v>
+        <v>1061555892</v>
       </c>
       <c r="G38" t="n">
-        <v>32000</v>
+        <v>25990</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -3259,49 +3259,49 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>658159871.2906245</v>
+        <v>1080323736.44457</v>
       </c>
       <c r="J38" t="n">
-        <v>820690047.7590786</v>
+        <v>1282066313.152077</v>
       </c>
       <c r="K38" t="n">
-        <v>1303115603.56096</v>
+        <v>1831537883.630203</v>
       </c>
       <c r="L38" t="n">
-        <v>78.58700541470049</v>
+        <v>58.5940165090762</v>
       </c>
       <c r="M38" t="n">
-        <v>59.26025148823201</v>
+        <v>-17.19961119717218</v>
       </c>
       <c r="N38" t="n">
-        <v>317</v>
+        <v>1100</v>
       </c>
       <c r="O38" t="n">
-        <v>173</v>
+        <v>470</v>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Q38" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S38" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
       <c r="T38" t="n">
-        <v>-33.4115008</v>
+        <v>-33.3499985</v>
       </c>
       <c r="U38" t="n">
-        <v>-70.59783849999999</v>
+        <v>-70.51667019999999</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4143696762-condominio-nueva-3-dorm-estar-family-room-servicios-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1997594621-gran-terreno-potencial-de-remodelacion-_JM</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3316,17 +3316,17 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>-0.5706967295539646</v>
+        <v>1.456766215156459</v>
       </c>
       <c r="F39" t="n">
-        <v>898585211</v>
+        <v>673530460</v>
       </c>
       <c r="G39" t="n">
-        <v>22000</v>
+        <v>16490</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3334,28 +3334,28 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>639411175.3669966</v>
+        <v>684334187.1148677</v>
       </c>
       <c r="J39" t="n">
-        <v>773624728.6491828</v>
+        <v>741623947.7868007</v>
       </c>
       <c r="K39" t="n">
-        <v>894170159.9745784</v>
+        <v>962393765.8778152</v>
       </c>
       <c r="L39" t="n">
-        <v>32.93056376990604</v>
+        <v>37.49333871873338</v>
       </c>
       <c r="M39" t="n">
-        <v>16.15259669491295</v>
+        <v>-9.181673271205639</v>
       </c>
       <c r="N39" t="n">
-        <v>325</v>
+        <v>385</v>
       </c>
       <c r="O39" t="n">
-        <v>168</v>
+        <v>240</v>
       </c>
       <c r="P39" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q39" t="n">
         <v>4</v>
@@ -3364,19 +3364,19 @@
         <v>2</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>56</v>
       </c>
       <c r="T39" t="n">
-        <v>-33.3868028</v>
+        <v>-33.3996367</v>
       </c>
       <c r="U39" t="n">
-        <v>-70.518474</v>
+        <v>-70.5496942</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1709323389-venta-casa-san-carlos-de-apoquindo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4198494308-esplendida-casa-con-gran-potencial-de-inversion-_JM</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3386,22 +3386,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>Metro Hernando De Magallanes</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>-1.171603518302364</v>
+        <v>1.440576161404091</v>
       </c>
       <c r="F40" t="n">
-        <v>916965363</v>
+        <v>541193366</v>
       </c>
       <c r="G40" t="n">
-        <v>22450</v>
+        <v>13250</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -3409,49 +3409,49 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>608402379.8034436</v>
+        <v>549740938.2853037</v>
       </c>
       <c r="J40" t="n">
-        <v>744587637.4853662</v>
+        <v>593344004.5941494</v>
       </c>
       <c r="K40" t="n">
-        <v>908241748.042377</v>
+        <v>799964696.0545819</v>
       </c>
       <c r="L40" t="n">
-        <v>40.2691843302094</v>
+        <v>42.17178497327745</v>
       </c>
       <c r="M40" t="n">
-        <v>23.15076383712073</v>
+        <v>-8.789275393423868</v>
       </c>
       <c r="N40" t="n">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="O40" t="n">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="P40" t="n">
         <v>5</v>
       </c>
       <c r="Q40" t="n">
+        <v>4</v>
+      </c>
+      <c r="R40" t="n">
         <v>3</v>
       </c>
-      <c r="R40" t="n">
-        <v>2</v>
-      </c>
       <c r="S40" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="T40" t="n">
-        <v>-33.3970927</v>
+        <v>-33.4094041</v>
       </c>
       <c r="U40" t="n">
-        <v>-70.50746479999999</v>
+        <v>-70.5522081</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3968105340-mediterranea-cerca-de-santiago-college-en-golf-de-manquehue-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4188212420-casa-en-venta-de-6-dorm-en-lo-barnechea-imperdible-_JM</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3461,22 +3461,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>-1.704475891532858</v>
+        <v>1.224099981258342</v>
       </c>
       <c r="F41" t="n">
-        <v>1552101728</v>
+        <v>1123231514</v>
       </c>
       <c r="G41" t="n">
-        <v>38000</v>
+        <v>27500</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3484,74 +3484,74 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>1062673616.468726</v>
+        <v>1139721572.546841</v>
       </c>
       <c r="J41" t="n">
-        <v>1267219195.058656</v>
+        <v>1347116967.511863</v>
       </c>
       <c r="K41" t="n">
-        <v>1530502282.327348</v>
+        <v>2289115664.130626</v>
       </c>
       <c r="L41" t="n">
-        <v>36.9177382794433</v>
+        <v>85.32251610687722</v>
       </c>
       <c r="M41" t="n">
-        <v>22.48091995861522</v>
+        <v>-16.61960014692576</v>
       </c>
       <c r="N41" t="n">
-        <v>840</v>
+        <v>1300</v>
       </c>
       <c r="O41" t="n">
-        <v>325</v>
+        <v>475</v>
       </c>
       <c r="P41" t="n">
         <v>5</v>
       </c>
       <c r="Q41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="S41" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="T41" t="n">
-        <v>-33.33126</v>
+        <v>-33.3504593</v>
       </c>
       <c r="U41" t="n">
-        <v>-70.54414</v>
+        <v>-70.53181840000001</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3894147344-club-manquehue-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2063339037-casa-en-venta-5d-3b-servicios-san-carlos-de-apoquindo-_JM</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Estadio Manquehue</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>-2.143453602299109</v>
+        <v>1.008771941964469</v>
       </c>
       <c r="F42" t="n">
-        <v>771966386</v>
+        <v>788304299</v>
       </c>
       <c r="G42" t="n">
-        <v>18900</v>
+        <v>19300</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -3559,49 +3559,49 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>599299294.9065548</v>
+        <v>796893429.7294861</v>
       </c>
       <c r="J42" t="n">
-        <v>647462843.6281235</v>
+        <v>851444253.3720509</v>
       </c>
       <c r="K42" t="n">
-        <v>758088320.3547047</v>
+        <v>946471833.1372373</v>
       </c>
       <c r="L42" t="n">
-        <v>24.5248089540335</v>
+        <v>17.56760971905823</v>
       </c>
       <c r="M42" t="n">
-        <v>19.22944978189147</v>
+        <v>-7.415629869130254</v>
       </c>
       <c r="N42" t="n">
-        <v>239</v>
+        <v>530</v>
       </c>
       <c r="O42" t="n">
-        <v>128</v>
+        <v>163</v>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R42" t="n">
         <v>2</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="T42" t="n">
-        <v>-33.3907923</v>
+        <v>-33.4068409</v>
       </c>
       <c r="U42" t="n">
-        <v>-70.576588</v>
+        <v>-70.5086672</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3824790288-casa-en-venta-condominio4d4bestarpiscinasan-carlos-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3583745698-casa-en-venta-san-carlos-de-apoquindo-_JM</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3616,17 +3616,17 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>-2.197173716850572</v>
+        <v>0.9746658145105138</v>
       </c>
       <c r="F43" t="n">
-        <v>894500733</v>
+        <v>755628473</v>
       </c>
       <c r="G43" t="n">
-        <v>21900</v>
+        <v>18500</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -3634,25 +3634,25 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>686914781.8727839</v>
+        <v>763563859.2474345</v>
       </c>
       <c r="J43" t="n">
-        <v>760830326.7250018</v>
+        <v>814164827.5024112</v>
       </c>
       <c r="K43" t="n">
-        <v>877783969.0313699</v>
+        <v>935003458.2909396</v>
       </c>
       <c r="L43" t="n">
-        <v>25.0869583472288</v>
+        <v>21.05711193265682</v>
       </c>
       <c r="M43" t="n">
-        <v>17.56901658355065</v>
+        <v>-7.189742485189571</v>
       </c>
       <c r="N43" t="n">
-        <v>375</v>
+        <v>497</v>
       </c>
       <c r="O43" t="n">
-        <v>178</v>
+        <v>185.85</v>
       </c>
       <c r="P43" t="n">
         <v>4</v>
@@ -3664,19 +3664,19 @@
         <v>2</v>
       </c>
       <c r="S43" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="T43" t="n">
-        <v>-33.3871246</v>
+        <v>-33.38872</v>
       </c>
       <c r="U43" t="n">
-        <v>-70.4957548</v>
+        <v>-70.50438</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2031477993-townhouses-alonso-camargo-6276-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4155493434-ital-apoquindo-la-quebrada-paul-harris-_JM</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3686,22 +3686,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rotonda Atenas</t>
+          <t>Colón Oriente - Vital Apoquindo</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>-2.356125897747323</v>
+        <v>0.9044535684989459</v>
       </c>
       <c r="F44" t="n">
-        <v>635136365</v>
+        <v>236899737</v>
       </c>
       <c r="G44" t="n">
-        <v>15550</v>
+        <v>5800</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -3709,74 +3709,74 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>332967591.2042384</v>
+        <v>239826296.3639584</v>
       </c>
       <c r="J44" t="n">
-        <v>512535598.1219028</v>
+        <v>323572095.449342</v>
       </c>
       <c r="K44" t="n">
-        <v>623060381.0374757</v>
+        <v>575961467.1203578</v>
       </c>
       <c r="L44" t="n">
-        <v>56.59953979708565</v>
+        <v>103.88262012817</v>
       </c>
       <c r="M44" t="n">
-        <v>23.92043934652467</v>
+        <v>-26.78610413823873</v>
       </c>
       <c r="N44" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="O44" t="n">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="P44" t="n">
         <v>3</v>
       </c>
       <c r="Q44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S44" t="n">
-        <v>176</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>-33.4206685</v>
+        <v>-33.4166257</v>
       </c>
       <c r="U44" t="n">
-        <v>-70.5625969</v>
+        <v>-70.5310898</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3543533266-estupenda-casa-con-gran-vista-en-el-arrayan-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4201707858-casa-con-gran-frente-a-blaise-cendrars-para-remodelar-_JM</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>El Arrayán</t>
+          <t>Nuestra Señora Del Rosario</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>-2.452997356240638</v>
+        <v>0.8338608057415077</v>
       </c>
       <c r="F45" t="n">
-        <v>1221258991</v>
+        <v>510559779</v>
       </c>
       <c r="G45" t="n">
-        <v>29900</v>
+        <v>12500</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
@@ -3784,74 +3784,74 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>564740811.6916066</v>
+        <v>516062286.1264538</v>
       </c>
       <c r="J45" t="n">
-        <v>886931368.6594583</v>
+        <v>659883170.9760807</v>
       </c>
       <c r="K45" t="n">
-        <v>1199502587.975115</v>
+        <v>800243909.9749887</v>
       </c>
       <c r="L45" t="n">
-        <v>71.5683082945765</v>
+        <v>43.06544496780869</v>
       </c>
       <c r="M45" t="n">
-        <v>37.69486954169376</v>
+        <v>-22.62876196027331</v>
       </c>
       <c r="N45" t="n">
-        <v>5172</v>
+        <v>350</v>
       </c>
       <c r="O45" t="n">
-        <v>248</v>
+        <v>120</v>
       </c>
       <c r="P45" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R45" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>56</v>
       </c>
       <c r="T45" t="n">
-        <v>-33.346985</v>
+        <v>-33.3925691</v>
       </c>
       <c r="U45" t="n">
-        <v>-70.4776525</v>
+        <v>-70.5680502</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4170217018-se-vende-casa-remodelada-en-vitacura-95640-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4105696724-venta-de-casa-cercana-a-metro-los-dominicos-en-las-condes-_JM</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Estadio Croata</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>-2.487237264009662</v>
+        <v>0.8220391087060617</v>
       </c>
       <c r="F46" t="n">
-        <v>894500733</v>
+        <v>649432039</v>
       </c>
       <c r="G46" t="n">
-        <v>21900</v>
+        <v>15900</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
@@ -3859,28 +3859,28 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>619529051.6985533</v>
+        <v>654830867.1674212</v>
       </c>
       <c r="J46" t="n">
-        <v>716297882.1734375</v>
+        <v>656760500.8378857</v>
       </c>
       <c r="K46" t="n">
-        <v>876684705.1532702</v>
+        <v>874452847.8896065</v>
       </c>
       <c r="L46" t="n">
-        <v>35.90065807181205</v>
+        <v>33.44019325796766</v>
       </c>
       <c r="M46" t="n">
-        <v>24.87831602766266</v>
+        <v>-1.115849967916187</v>
       </c>
       <c r="N46" t="n">
-        <v>395</v>
+        <v>360</v>
       </c>
       <c r="O46" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="P46" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q46" t="n">
         <v>3</v>
@@ -3889,44 +3889,44 @@
         <v>2</v>
       </c>
       <c r="S46" t="n">
-        <v>4</v>
+        <v>44</v>
       </c>
       <c r="T46" t="n">
-        <v>-33.3826607</v>
+        <v>-33.4055405</v>
       </c>
       <c r="U46" t="n">
-        <v>-70.559969</v>
+        <v>-70.54011250000001</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1859517231-22205-las-hualtatas-colegio-tabancura-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3820672742-linda-casa-100-remodelada-hace-tres-anos-estadio-espanol-_JM</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Tabancura</t>
+          <t>Metro Escuela Militar</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>-3.064400413608777</v>
+        <v>0.7775323126710787</v>
       </c>
       <c r="F47" t="n">
-        <v>2777445198</v>
+        <v>731121603</v>
       </c>
       <c r="G47" t="n">
-        <v>68000</v>
+        <v>17900</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -3934,49 +3934,49 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>816942506.1206945</v>
+        <v>737542575.9044847</v>
       </c>
       <c r="J47" t="n">
-        <v>1859773848.374941</v>
+        <v>825814284.4799079</v>
       </c>
       <c r="K47" t="n">
-        <v>2720454280.49821</v>
+        <v>1049979618.694189</v>
       </c>
       <c r="L47" t="n">
-        <v>102.3517873445092</v>
+        <v>37.83381429233508</v>
       </c>
       <c r="M47" t="n">
-        <v>49.34316881737607</v>
+        <v>-11.46658313612784</v>
       </c>
       <c r="N47" t="n">
-        <v>2665</v>
+        <v>395</v>
       </c>
       <c r="O47" t="n">
-        <v>508</v>
+        <v>175</v>
       </c>
       <c r="P47" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R47" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S47" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="T47" t="n">
-        <v>-33.3780395</v>
+        <v>-33.4145458</v>
       </c>
       <c r="U47" t="n">
-        <v>-70.52854859999999</v>
+        <v>-70.57366140000001</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1946224879-sector-los-trapenses-comercial-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3873502872-condominio-los-bravos-no-perimetral-_JM</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3991,17 +3991,17 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>-3.077760508074324</v>
+        <v>0.7168195395943454</v>
       </c>
       <c r="F48" t="n">
-        <v>2001394334</v>
+        <v>857740429</v>
       </c>
       <c r="G48" t="n">
-        <v>49000</v>
+        <v>21000</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4009,49 +4009,49 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>1087283687.053744</v>
+        <v>864888914.245121</v>
       </c>
       <c r="J48" t="n">
-        <v>1497198576.268294</v>
+        <v>997250332.9312694</v>
       </c>
       <c r="K48" t="n">
-        <v>1955314147.492163</v>
+        <v>1109627655.897913</v>
       </c>
       <c r="L48" t="n">
-        <v>57.9769760803507</v>
+        <v>24.54135472017532</v>
       </c>
       <c r="M48" t="n">
-        <v>33.67594424170465</v>
+        <v>-13.98945674163886</v>
       </c>
       <c r="N48" t="n">
-        <v>1062</v>
+        <v>872</v>
       </c>
       <c r="O48" t="n">
-        <v>410</v>
+        <v>200</v>
       </c>
       <c r="P48" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q48" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R48" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="S48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="T48" t="n">
-        <v>-33.3474949</v>
+        <v>-33.3193982</v>
       </c>
       <c r="U48" t="n">
-        <v>-70.5421845</v>
+        <v>-70.5681556</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4021085782-luminosa-casa-en-venta-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4034196578-casa-en-venta-de-5-dorm-espectacular-vista-_JM</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4061,22 +4061,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>-3.278274915740692</v>
+        <v>0.6459017941856643</v>
       </c>
       <c r="F49" t="n">
-        <v>976190297</v>
+        <v>853655950</v>
       </c>
       <c r="G49" t="n">
-        <v>23900</v>
+        <v>20900</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4084,74 +4084,74 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>614566902.9499044</v>
+        <v>860781357.1706355</v>
       </c>
       <c r="J49" t="n">
-        <v>907831013.8166518</v>
+        <v>1103171911.701993</v>
       </c>
       <c r="K49" t="n">
-        <v>946429100.5967343</v>
+        <v>1246578266.004285</v>
       </c>
       <c r="L49" t="n">
-        <v>36.55550345781133</v>
+        <v>34.97160367675021</v>
       </c>
       <c r="M49" t="n">
-        <v>7.529956802858711</v>
+        <v>-22.6180488331175</v>
       </c>
       <c r="N49" t="n">
-        <v>563</v>
+        <v>900</v>
       </c>
       <c r="O49" t="n">
-        <v>153</v>
+        <v>300</v>
       </c>
       <c r="P49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q49" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R49" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="S49" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T49" t="n">
-        <v>-33.4060449</v>
+        <v>-33.4042302</v>
       </c>
       <c r="U49" t="n">
-        <v>-70.5114827</v>
+        <v>-70.52972269999999</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4164770646-casa-impecable-y-amplia-bien-emplazada-club-de-polo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2018153427-oportunidadremodelar-los-dominicos-5d4b-piscina-_JM</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Borde Río - Casa Piedra</t>
+          <t>Los Dominicos</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>-3.599381391866206</v>
+        <v>0.5599585198608685</v>
       </c>
       <c r="F50" t="n">
-        <v>1039499710</v>
+        <v>690276821</v>
       </c>
       <c r="G50" t="n">
-        <v>25450</v>
+        <v>16900</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4159,74 +4159,74 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>792169095.6728661</v>
+        <v>694894719.7908235</v>
       </c>
       <c r="J50" t="n">
-        <v>871216704.8094535</v>
+        <v>824685869.9410195</v>
       </c>
       <c r="K50" t="n">
-        <v>1008141298.044259</v>
+        <v>1121127066.357697</v>
       </c>
       <c r="L50" t="n">
-        <v>24.78972237092589</v>
+        <v>51.68420632662927</v>
       </c>
       <c r="M50" t="n">
-        <v>19.31586071083798</v>
+        <v>-16.298211699763</v>
       </c>
       <c r="N50" t="n">
-        <v>354</v>
+        <v>623</v>
       </c>
       <c r="O50" t="n">
-        <v>195</v>
+        <v>168</v>
       </c>
       <c r="P50" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q50" t="n">
         <v>4</v>
       </c>
       <c r="R50" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>42</v>
       </c>
       <c r="T50" t="n">
-        <v>-33.3845621</v>
+        <v>-33.4032183</v>
       </c>
       <c r="U50" t="n">
-        <v>-70.5819789</v>
+        <v>-70.52516540000001</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4198328642-casa-en-venta-de-5-dorm-en-vitacura-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1918940429-dehesa-central-a-pasos-del-portal-condominio-cerrado-_JM</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa María De Manquehue</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>-4.085309844173856</v>
+        <v>0.4077232914565737</v>
       </c>
       <c r="F51" t="n">
-        <v>1960549551</v>
+        <v>653516517</v>
       </c>
       <c r="G51" t="n">
-        <v>48000</v>
+        <v>16000</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4234,49 +4234,49 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>1049194578.441455</v>
+        <v>656600594.941631</v>
       </c>
       <c r="J51" t="n">
-        <v>1417513188.88171</v>
+        <v>756414462.0272306</v>
       </c>
       <c r="K51" t="n">
-        <v>1902639745.152153</v>
+        <v>954217590.0385821</v>
       </c>
       <c r="L51" t="n">
-        <v>60.20721171448074</v>
+        <v>39.34575686182968</v>
       </c>
       <c r="M51" t="n">
-        <v>38.30908709545745</v>
+        <v>-13.60338150482458</v>
       </c>
       <c r="N51" t="n">
-        <v>1000</v>
+        <v>412</v>
       </c>
       <c r="O51" t="n">
-        <v>403</v>
+        <v>152</v>
       </c>
       <c r="P51" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q51" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S51" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="T51" t="n">
-        <v>-33.3736513</v>
+        <v>-33.3554101</v>
       </c>
       <c r="U51" t="n">
-        <v>-70.57956590000001</v>
+        <v>-70.5156223</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4138226282-exclusiva-mediterranea-valle-escondido-arquitecto-mardones-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1999203389-en-condominio-con-piscina-y-vistas-_JM</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4286,22 +4286,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valle Escondido</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>-4.664980279104539</v>
+        <v>0.3948068373870099</v>
       </c>
       <c r="F52" t="n">
-        <v>2797867589</v>
+        <v>673938908</v>
       </c>
       <c r="G52" t="n">
-        <v>68500</v>
+        <v>16500</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
@@ -4309,74 +4309,74 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>1126249065.835708</v>
+        <v>676970722.5677009</v>
       </c>
       <c r="J52" t="n">
-        <v>1813378999.567022</v>
+        <v>767923521.225374</v>
       </c>
       <c r="K52" t="n">
-        <v>2713273816.284775</v>
+        <v>1069851676.171208</v>
       </c>
       <c r="L52" t="n">
-        <v>87.51754326194356</v>
+        <v>51.16146891510596</v>
       </c>
       <c r="M52" t="n">
-        <v>54.29028292861248</v>
+        <v>-12.23879860788779</v>
       </c>
       <c r="N52" t="n">
-        <v>2000</v>
+        <v>392</v>
       </c>
       <c r="O52" t="n">
-        <v>580</v>
+        <v>190</v>
       </c>
       <c r="P52" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R52" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S52" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="T52" t="n">
-        <v>-33.3448698</v>
+        <v>-33.3333379</v>
       </c>
       <c r="U52" t="n">
-        <v>-70.4937958</v>
+        <v>-70.5110471</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4155491174-casa-jardin-la-dehesa-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3789338736-oportunidad-para-inversionistas-acogedora-casa-d-_JM</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Rotonda Atenas</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>-4.67632771801618</v>
+        <v>0.3628974182209566</v>
       </c>
       <c r="F53" t="n">
-        <v>1235554665</v>
+        <v>326349811</v>
       </c>
       <c r="G53" t="n">
-        <v>30250</v>
+        <v>7990</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4384,25 +4384,25 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>747601427.4900656</v>
+        <v>327910225.8242831</v>
       </c>
       <c r="J53" t="n">
-        <v>951786563.6592499</v>
+        <v>429987854.9516261</v>
       </c>
       <c r="K53" t="n">
-        <v>1191046006.107249</v>
+        <v>633639544.3290203</v>
       </c>
       <c r="L53" t="n">
-        <v>46.59075842721617</v>
+        <v>71.10184973460049</v>
       </c>
       <c r="M53" t="n">
-        <v>29.81425796239147</v>
+        <v>-24.10255144608339</v>
       </c>
       <c r="N53" t="n">
-        <v>737</v>
+        <v>129</v>
       </c>
       <c r="O53" t="n">
-        <v>168</v>
+        <v>108</v>
       </c>
       <c r="P53" t="n">
         <v>4</v>
@@ -4411,47 +4411,47 @@
         <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S53" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="T53" t="n">
-        <v>-33.360967</v>
+        <v>-33.4162203</v>
       </c>
       <c r="U53" t="n">
-        <v>-70.5284477</v>
+        <v>-70.55327339999999</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3854828116-espectacular-vista-camino-del-condor-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4139251760-unica-casa-th-4d-condominio-los-trapenses-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>-4.781796626820063</v>
+        <v>0.2895098563578531</v>
       </c>
       <c r="F54" t="n">
-        <v>5105597790</v>
+        <v>714783691</v>
       </c>
       <c r="G54" t="n">
-        <v>125000</v>
+        <v>17500</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -4459,74 +4459,74 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>1385941292.189607</v>
+        <v>717580574.03729</v>
       </c>
       <c r="J54" t="n">
-        <v>3310421103.623775</v>
+        <v>966075239.1907674</v>
       </c>
       <c r="K54" t="n">
-        <v>4947300185.333379</v>
+        <v>1131519236.196573</v>
       </c>
       <c r="L54" t="n">
-        <v>107.580237730037</v>
+        <v>42.8474559089227</v>
       </c>
       <c r="M54" t="n">
-        <v>54.22804622684171</v>
+        <v>-26.01159185088541</v>
       </c>
       <c r="N54" t="n">
-        <v>3125</v>
+        <v>500</v>
       </c>
       <c r="O54" t="n">
-        <v>1200</v>
+        <v>210</v>
       </c>
       <c r="P54" t="n">
         <v>5</v>
       </c>
       <c r="Q54" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T54" t="n">
-        <v>-33.3656426</v>
+        <v>-33.3246571</v>
       </c>
       <c r="U54" t="n">
-        <v>-70.5665712</v>
+        <v>-70.55433600000001</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2016678475-luis-pasteur-las-rosas-chicas-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3806992554-casa-cercana-metro-colon-_JM</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Juan Xxiii</t>
+          <t>Barrio El Golf</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>-4.905488290367124</v>
+        <v>0.2164305952329084</v>
       </c>
       <c r="F55" t="n">
-        <v>980274776</v>
+        <v>608587257</v>
       </c>
       <c r="G55" t="n">
-        <v>24000</v>
+        <v>14900</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -4534,74 +4534,74 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>740713790.3985107</v>
+        <v>610249225.058606</v>
       </c>
       <c r="J55" t="n">
-        <v>849968330.43574</v>
+        <v>767898853.1254222</v>
       </c>
       <c r="K55" t="n">
-        <v>938579679.0786458</v>
+        <v>1006444763.032305</v>
       </c>
       <c r="L55" t="n">
-        <v>23.27920718866058</v>
+        <v>51.59475578862304</v>
       </c>
       <c r="M55" t="n">
-        <v>15.33074126390778</v>
+        <v>-20.74642975139352</v>
       </c>
       <c r="N55" t="n">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="O55" t="n">
-        <v>190</v>
+        <v>170</v>
       </c>
       <c r="P55" t="n">
         <v>4</v>
       </c>
       <c r="Q55" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R55" t="n">
         <v>2</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="T55" t="n">
-        <v>-33.383201</v>
+        <v>-33.4241535</v>
       </c>
       <c r="U55" t="n">
-        <v>-70.5719739</v>
+        <v>-70.5920527</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3927242992-casa-en-condominio-san-carlos-de-apoquindo-5d-5b-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1938477511-casa-remodelada-de-4-d-jardin-del-este-vitacura-_JM</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>Jardín Del Este</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>-5.25465351191651</v>
+        <v>0.0436890590393463</v>
       </c>
       <c r="F56" t="n">
-        <v>894500733</v>
+        <v>885923328</v>
       </c>
       <c r="G56" t="n">
-        <v>21900</v>
+        <v>21690</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -4609,49 +4609,49 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>667151987.0166159</v>
+        <v>886322860.5264604</v>
       </c>
       <c r="J56" t="n">
-        <v>738515965.9174603</v>
+        <v>914491031.0395808</v>
       </c>
       <c r="K56" t="n">
-        <v>855694277.860854</v>
+        <v>1064933606.988256</v>
       </c>
       <c r="L56" t="n">
-        <v>25.52988690095706</v>
+        <v>19.53116437443381</v>
       </c>
       <c r="M56" t="n">
-        <v>21.12138048210771</v>
+        <v>-3.123891002747774</v>
       </c>
       <c r="N56" t="n">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="O56" t="n">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="P56" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q56" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
         <v>2</v>
       </c>
       <c r="S56" t="n">
-        <v>19</v>
+        <v>64</v>
       </c>
       <c r="T56" t="n">
-        <v>-33.3883239</v>
+        <v>-33.3910353</v>
       </c>
       <c r="U56" t="n">
-        <v>-70.49293419999999</v>
+        <v>-70.5865618</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4198327852-espectacular-casa-remodelada-con-salida-al-sport-frances-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1858353987-vendo-casa-para-remodelar-3d-2b-2e-los-laureles-vitacura-_JM</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4661,22 +4661,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Juan Xxiii</t>
+          <t>Parque Bicentenario</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>sobrevalorada</t>
+          <t>subvalorada</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>-5.653542228248217</v>
+        <v>0.009249806318806097</v>
       </c>
       <c r="F57" t="n">
-        <v>1470412163</v>
+        <v>510559779</v>
       </c>
       <c r="G57" t="n">
-        <v>36000</v>
+        <v>12500</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -4684,59 +4684,59 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>811306107.1896869</v>
+        <v>510619722.7448434</v>
       </c>
       <c r="J57" t="n">
-        <v>1200593375.699747</v>
+        <v>648054054.0777605</v>
       </c>
       <c r="K57" t="n">
-        <v>1402536109.515264</v>
+        <v>890845847.4695154</v>
       </c>
       <c r="L57" t="n">
-        <v>49.24481629602428</v>
+        <v>58.67197687170837</v>
       </c>
       <c r="M57" t="n">
-        <v>22.47378610955547</v>
+        <v>-21.21648251601901</v>
       </c>
       <c r="N57" t="n">
-        <v>640</v>
+        <v>232</v>
       </c>
       <c r="O57" t="n">
-        <v>240</v>
+        <v>95</v>
       </c>
       <c r="P57" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q57" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R57" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S57" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T57" t="n">
-        <v>-33.3838555</v>
+        <v>-33.4043145</v>
       </c>
       <c r="U57" t="n">
-        <v>-70.56662470000001</v>
+        <v>-70.5904373</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4054604630-san-rafael-mall-vivo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4146245022-moderna-casa-sanfuentes-jardin-del-este-174047-_JM</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Jardín Del Este</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -4745,13 +4745,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>-5.684950541444155</v>
+        <v>-0.03836752324471129</v>
       </c>
       <c r="F58" t="n">
-        <v>1629706814</v>
+        <v>2197449289</v>
       </c>
       <c r="G58" t="n">
-        <v>39900</v>
+        <v>53800</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -4759,59 +4759,59 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1083010865.631332</v>
+        <v>1120053653.354236</v>
       </c>
       <c r="J58" t="n">
-        <v>1381863090.376708</v>
+        <v>1570691356.879166</v>
       </c>
       <c r="K58" t="n">
-        <v>1551148580.761612</v>
+        <v>2196846653.628547</v>
       </c>
       <c r="L58" t="n">
-        <v>33.87728628041305</v>
+        <v>68.55535274694638</v>
       </c>
       <c r="M58" t="n">
-        <v>17.93547605036096</v>
+        <v>39.90331578357635</v>
       </c>
       <c r="N58" t="n">
-        <v>980</v>
+        <v>1126</v>
       </c>
       <c r="O58" t="n">
-        <v>360</v>
+        <v>410</v>
       </c>
       <c r="P58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q58" t="n">
         <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>61</v>
       </c>
       <c r="T58" t="n">
-        <v>-33.3583692</v>
+        <v>-33.3906175</v>
       </c>
       <c r="U58" t="n">
-        <v>-70.5388037</v>
+        <v>-70.5854102</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1946991437-venta-casa-en-condominio-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4164897116-casa-en-venta-condominio-san-carlos-de-apoq-las-condes-_JM</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>El Huinganal</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>-5.821901389581974</v>
+        <v>-0.4528739459635967</v>
       </c>
       <c r="F59" t="n">
-        <v>935345515</v>
+        <v>853655950</v>
       </c>
       <c r="G59" t="n">
-        <v>22900</v>
+        <v>20900</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -4834,25 +4834,25 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>661840388.1612519</v>
+        <v>697510884.1495398</v>
       </c>
       <c r="J59" t="n">
-        <v>750417699.9380925</v>
+        <v>765897671.3696853</v>
       </c>
       <c r="K59" t="n">
-        <v>891656936.4996351</v>
+        <v>850187398.9936248</v>
       </c>
       <c r="L59" t="n">
-        <v>30.62515028061604</v>
+        <v>19.93432289342876</v>
       </c>
       <c r="M59" t="n">
-        <v>24.64331732542604</v>
+        <v>11.45822502285104</v>
       </c>
       <c r="N59" t="n">
-        <v>445</v>
+        <v>377</v>
       </c>
       <c r="O59" t="n">
-        <v>200</v>
+        <v>172</v>
       </c>
       <c r="P59" t="n">
         <v>5</v>
@@ -4864,29 +4864,29 @@
         <v>2</v>
       </c>
       <c r="S59" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="T59" t="n">
-        <v>-33.3406188</v>
+        <v>-33.4069938</v>
       </c>
       <c r="U59" t="n">
-        <v>-70.4960912</v>
+        <v>-70.5095711</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1777531091-casa-mediterranea-remodelada-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1872579401-casa-en-venta-de-5-dorm-en-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>La Llavería</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4895,13 +4895,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>-5.900895524851315</v>
+        <v>-0.7887987135359579</v>
       </c>
       <c r="F60" t="n">
-        <v>776050864</v>
+        <v>1572524119</v>
       </c>
       <c r="G60" t="n">
-        <v>19000</v>
+        <v>38500</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
@@ -4909,59 +4909,59 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>499474658.3460681</v>
+        <v>1023588575.560951</v>
       </c>
       <c r="J60" t="n">
-        <v>683228372.552276</v>
+        <v>1216418839.367074</v>
       </c>
       <c r="K60" t="n">
-        <v>735734271.5395483</v>
+        <v>1562929022.843863</v>
       </c>
       <c r="L60" t="n">
-        <v>34.57988905099271</v>
+        <v>44.33838327952417</v>
       </c>
       <c r="M60" t="n">
-        <v>13.58586604080495</v>
+        <v>29.27489020296774</v>
       </c>
       <c r="N60" t="n">
-        <v>273</v>
+        <v>1011</v>
       </c>
       <c r="O60" t="n">
-        <v>118</v>
+        <v>280</v>
       </c>
       <c r="P60" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>5</v>
+      </c>
+      <c r="R60" t="n">
         <v>3</v>
       </c>
-      <c r="Q60" t="n">
-        <v>2</v>
-      </c>
-      <c r="R60" t="n">
-        <v>2</v>
-      </c>
       <c r="S60" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="T60" t="n">
-        <v>-33.3873026</v>
+        <v>-33.3581657</v>
       </c>
       <c r="U60" t="n">
-        <v>-70.54762890000001</v>
+        <v>-70.5400722</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4164888756-moderna-mediterranea-remodelada-luminosa-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3968105340-mediterranea-cerca-de-santiago-college-en-golf-de-manquehue-_JM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Borde Río - Casa Piedra</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4970,13 +4970,13 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>-6.140452483460727</v>
+        <v>-0.9169114648695443</v>
       </c>
       <c r="F61" t="n">
-        <v>1041541949</v>
+        <v>1552101728</v>
       </c>
       <c r="G61" t="n">
-        <v>25500</v>
+        <v>38000</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
@@ -4984,49 +4984,49 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>777165051.7413801</v>
+        <v>1015013355.765565</v>
       </c>
       <c r="J61" t="n">
-        <v>846041647.2677914</v>
+        <v>1397742529.032619</v>
       </c>
       <c r="K61" t="n">
-        <v>989591163.6592329</v>
+        <v>1539285666.501942</v>
       </c>
       <c r="L61" t="n">
-        <v>25.10823345444779</v>
+        <v>37.50850388012641</v>
       </c>
       <c r="M61" t="n">
-        <v>23.10764515713354</v>
+        <v>11.04346442647155</v>
       </c>
       <c r="N61" t="n">
-        <v>355</v>
+        <v>840</v>
       </c>
       <c r="O61" t="n">
-        <v>195</v>
+        <v>325</v>
       </c>
       <c r="P61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q61" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R61" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T61" t="n">
-        <v>-33.3845184</v>
+        <v>-33.33126</v>
       </c>
       <c r="U61" t="n">
-        <v>-70.5803214</v>
+        <v>-70.54414</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4143690828-linda-casa-en-condominio-sta-maria-de-manquehue-plano-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2016678475-luis-pasteur-las-rosas-chicas-_JM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Borde Río - Casa Piedra</t>
+          <t>Juan Xxiii</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5045,13 +5045,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>-7.022638872194742</v>
+        <v>-0.938591393615988</v>
       </c>
       <c r="F62" t="n">
-        <v>1037457471</v>
+        <v>980274776</v>
       </c>
       <c r="G62" t="n">
-        <v>25400</v>
+        <v>24000</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
@@ -5059,59 +5059,59 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>580605792.4508977</v>
+        <v>744753959.6546116</v>
       </c>
       <c r="J62" t="n">
-        <v>816072620.1648812</v>
+        <v>888550735.4001817</v>
       </c>
       <c r="K62" t="n">
-        <v>980147637.9509629</v>
+        <v>971934915.2696223</v>
       </c>
       <c r="L62" t="n">
-        <v>48.95910432815904</v>
+        <v>25.56758399538029</v>
       </c>
       <c r="M62" t="n">
-        <v>27.12808215405997</v>
+        <v>10.32288162571922</v>
       </c>
       <c r="N62" t="n">
-        <v>300</v>
+        <v>390</v>
       </c>
       <c r="O62" t="n">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="P62" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>4</v>
+      </c>
+      <c r="R62" t="n">
+        <v>2</v>
+      </c>
+      <c r="S62" t="n">
         <v>5</v>
       </c>
-      <c r="Q62" t="n">
-        <v>4</v>
-      </c>
-      <c r="R62" t="n">
-        <v>3</v>
-      </c>
-      <c r="S62" t="n">
-        <v>20</v>
-      </c>
       <c r="T62" t="n">
-        <v>-33.3792302</v>
+        <v>-33.383201</v>
       </c>
       <c r="U62" t="n">
-        <v>-70.5761469</v>
+        <v>-70.5719739</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2039833029-borderio-comoda-casa-5d-3-b-piscina-168236-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1903294981-metro-hernando-de-magallanes-_JM</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Borde Río - Casa Piedra</t>
+          <t>Metro Hernando De Magallanes</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5120,13 +5120,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>-7.315097105256737</v>
+        <v>-1.044484610576765</v>
       </c>
       <c r="F63" t="n">
-        <v>1102809123</v>
+        <v>751543995</v>
       </c>
       <c r="G63" t="n">
-        <v>27000</v>
+        <v>18400</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -5134,49 +5134,49 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>661363780.4092292</v>
+        <v>435444538.2634251</v>
       </c>
       <c r="J63" t="n">
-        <v>869565037.7893066</v>
+        <v>606010211.3851582</v>
       </c>
       <c r="K63" t="n">
-        <v>1039199596.09235</v>
+        <v>745214311.6035583</v>
       </c>
       <c r="L63" t="n">
-        <v>43.45112777805463</v>
+        <v>51.11626298046895</v>
       </c>
       <c r="M63" t="n">
-        <v>26.82307533932934</v>
+        <v>24.01507117878346</v>
       </c>
       <c r="N63" t="n">
-        <v>480</v>
+        <v>195</v>
       </c>
       <c r="O63" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="P63" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q63" t="n">
         <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S63" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="T63" t="n">
-        <v>-33.3819761</v>
+        <v>-33.4112168</v>
       </c>
       <c r="U63" t="n">
-        <v>-70.57844969999999</v>
+        <v>-70.5572779</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4088013424-oportunidad-completamente-remodelada-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1698236219-casa-siete-dormitorios-mas-estar-_JM</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>La Llavería</t>
+          <t>Jardín Del Este</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5195,13 +5195,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>-7.375507267128762</v>
+        <v>-1.13321045019504</v>
       </c>
       <c r="F64" t="n">
-        <v>771966386</v>
+        <v>2201533767</v>
       </c>
       <c r="G64" t="n">
-        <v>18900</v>
+        <v>53900</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -5209,49 +5209,49 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>544162365.519313</v>
+        <v>1154060355.028147</v>
       </c>
       <c r="J64" t="n">
-        <v>647147478.5854679</v>
+        <v>1642316296.099054</v>
       </c>
       <c r="K64" t="n">
-        <v>724235976.6878883</v>
+        <v>2182922867.107349</v>
       </c>
       <c r="L64" t="n">
-        <v>27.82574561863076</v>
+        <v>62.64703787711478</v>
       </c>
       <c r="M64" t="n">
-        <v>19.28755214921963</v>
+        <v>34.05053412848906</v>
       </c>
       <c r="N64" t="n">
-        <v>286</v>
+        <v>1126</v>
       </c>
       <c r="O64" t="n">
-        <v>140</v>
+        <v>397</v>
       </c>
       <c r="P64" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q64" t="n">
         <v>4</v>
       </c>
       <c r="R64" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S64" t="n">
-        <v>46</v>
+        <v>60</v>
       </c>
       <c r="T64" t="n">
-        <v>-33.3856938</v>
+        <v>-33.3918257</v>
       </c>
       <c r="U64" t="n">
-        <v>-70.5441996</v>
+        <v>-70.5825452</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3876586078-casa-en-venta-en-santa-teresita-con-piscina-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3894147344-club-manquehue-_JM</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5261,7 +5261,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>Estadio Manquehue</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5270,13 +5270,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>-7.801585576992902</v>
+        <v>-1.429666984183256</v>
       </c>
       <c r="F65" t="n">
-        <v>919007602</v>
+        <v>771966386</v>
       </c>
       <c r="G65" t="n">
-        <v>22500</v>
+        <v>18900</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
@@ -5284,59 +5284,59 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>484614270.514893</v>
+        <v>584767375.9735157</v>
       </c>
       <c r="J65" t="n">
-        <v>754705600.8309665</v>
+        <v>653105925.6577164</v>
       </c>
       <c r="K65" t="n">
-        <v>860128598.6968137</v>
+        <v>762629146.2091272</v>
       </c>
       <c r="L65" t="n">
-        <v>49.75639875581442</v>
+        <v>27.23321948985444</v>
       </c>
       <c r="M65" t="n">
-        <v>21.77034342770602</v>
+        <v>18.199262274735</v>
       </c>
       <c r="N65" t="n">
-        <v>280</v>
+        <v>239</v>
       </c>
       <c r="O65" t="n">
-        <v>74</v>
+        <v>128</v>
       </c>
       <c r="P65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q65" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
         <v>2</v>
       </c>
       <c r="S65" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>-33.3725014</v>
+        <v>-33.3907923</v>
       </c>
       <c r="U65" t="n">
-        <v>-70.5423126</v>
+        <v>-70.576588</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3838783300-increible-casa-con-gran-jardin-mirador-san-damian-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4105563934-casa-mediterranea-condominio-los-monjes-_JM</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5345,13 +5345,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>-8.667313701796298</v>
+        <v>-1.664847624371792</v>
       </c>
       <c r="F66" t="n">
-        <v>3676030408</v>
+        <v>1380553642</v>
       </c>
       <c r="G66" t="n">
-        <v>90000</v>
+        <v>33800</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5359,59 +5359,59 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>1045022405.495147</v>
+        <v>965777271.9150227</v>
       </c>
       <c r="J66" t="n">
-        <v>2144397506.223563</v>
+        <v>1233612004.618472</v>
       </c>
       <c r="K66" t="n">
-        <v>3490168749.122107</v>
+        <v>1360015881.847144</v>
       </c>
       <c r="L66" t="n">
-        <v>114.0248641649019</v>
+        <v>31.9580717807663</v>
       </c>
       <c r="M66" t="n">
-        <v>71.42485930576146</v>
+        <v>11.91149541601401</v>
       </c>
       <c r="N66" t="n">
-        <v>2577</v>
+        <v>750</v>
       </c>
       <c r="O66" t="n">
-        <v>652</v>
+        <v>300</v>
       </c>
       <c r="P66" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q66" t="n">
         <v>5</v>
       </c>
-      <c r="Q66" t="n">
+      <c r="R66" t="n">
         <v>3</v>
       </c>
-      <c r="R66" t="n">
-        <v>6</v>
-      </c>
       <c r="S66" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="T66" t="n">
-        <v>-33.3806006</v>
+        <v>-33.3318146</v>
       </c>
       <c r="U66" t="n">
-        <v>-70.5017314</v>
+        <v>-70.54787829999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4054786240-preciosa-casa-en-los-bravos-con-maravillosa-vista-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4164888756-moderna-mediterranea-remodelada-luminosa-_JM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>Borde Río - Casa Piedra</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5420,13 +5420,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>-9.738385844327247</v>
+        <v>-1.720544221944889</v>
       </c>
       <c r="F67" t="n">
-        <v>1631749054</v>
+        <v>1041541949</v>
       </c>
       <c r="G67" t="n">
-        <v>39950</v>
+        <v>25500</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
@@ -5434,49 +5434,49 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>927484737.5132129</v>
+        <v>766688533.5908592</v>
       </c>
       <c r="J67" t="n">
-        <v>1166961509.212906</v>
+        <v>929305306.3348312</v>
       </c>
       <c r="K67" t="n">
-        <v>1518105839.578063</v>
+        <v>1025552840.247629</v>
       </c>
       <c r="L67" t="n">
-        <v>50.61187514772556</v>
+        <v>27.85567938675905</v>
       </c>
       <c r="M67" t="n">
-        <v>39.82886677218555</v>
+        <v>12.07747786438762</v>
       </c>
       <c r="N67" t="n">
-        <v>1170</v>
+        <v>355</v>
       </c>
       <c r="O67" t="n">
-        <v>315</v>
+        <v>195</v>
       </c>
       <c r="P67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q67" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R67" t="n">
         <v>2</v>
       </c>
       <c r="S67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T67" t="n">
-        <v>-33.3165239</v>
+        <v>-33.3845184</v>
       </c>
       <c r="U67" t="n">
-        <v>-70.56922299999999</v>
+        <v>-70.5803214</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1872579401-casa-en-venta-de-5-dorm-en-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2061517273-seguridad-247-condominio-_JM</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5486,7 +5486,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5495,13 +5495,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>-10.40141042474583</v>
+        <v>-2.346147358967277</v>
       </c>
       <c r="F68" t="n">
-        <v>1572524119</v>
+        <v>1748156683</v>
       </c>
       <c r="G68" t="n">
-        <v>38500</v>
+        <v>42800</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5509,49 +5509,49 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>1020592416.770405</v>
+        <v>1044418882.285148</v>
       </c>
       <c r="J68" t="n">
-        <v>1289932781.316407</v>
+        <v>1342699650.557345</v>
       </c>
       <c r="K68" t="n">
-        <v>1438352916.211941</v>
+        <v>1716654970.609586</v>
       </c>
       <c r="L68" t="n">
-        <v>32.38622240572893</v>
+        <v>50.06600605320762</v>
       </c>
       <c r="M68" t="n">
-        <v>21.90744678921968</v>
+        <v>30.19715036600725</v>
       </c>
       <c r="N68" t="n">
-        <v>1011</v>
+        <v>1176</v>
       </c>
       <c r="O68" t="n">
-        <v>280</v>
+        <v>370</v>
       </c>
       <c r="P68" t="n">
         <v>5</v>
       </c>
       <c r="Q68" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R68" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S68" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="T68" t="n">
-        <v>-33.3581657</v>
+        <v>-33.3204944</v>
       </c>
       <c r="U68" t="n">
-        <v>-70.5400722</v>
+        <v>-70.5451101</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4084847464-condominio-el-golf-la-dehesa-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4047167616-casa-en-venta-de-5-dorm-en-lo-barnechea-_JM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>-11.78427950966704</v>
+        <v>-2.34898400320563</v>
       </c>
       <c r="F69" t="n">
-        <v>1196752122</v>
+        <v>1307033034</v>
       </c>
       <c r="G69" t="n">
-        <v>29300</v>
+        <v>32000</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -5584,59 +5584,59 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>584107537.3752755</v>
+        <v>885354301.2807709</v>
       </c>
       <c r="J69" t="n">
-        <v>964592273.3350897</v>
+        <v>1189214623.182828</v>
       </c>
       <c r="K69" t="n">
-        <v>1083081872.381541</v>
+        <v>1279098572.737653</v>
       </c>
       <c r="L69" t="n">
-        <v>51.72904125398559</v>
+        <v>33.10960559861436</v>
       </c>
       <c r="M69" t="n">
-        <v>24.06818456695851</v>
+        <v>9.907245380303282</v>
       </c>
       <c r="N69" t="n">
-        <v>281</v>
+        <v>1093</v>
       </c>
       <c r="O69" t="n">
-        <v>235</v>
+        <v>300</v>
       </c>
       <c r="P69" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q69" t="n">
         <v>4</v>
       </c>
       <c r="R69" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="S69" t="n">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="T69" t="n">
-        <v>-33.3393451</v>
+        <v>-33.3388329</v>
       </c>
       <c r="U69" t="n">
-        <v>-70.51458239999999</v>
+        <v>-70.52832290000001</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1938489451-casa-en-condominio-colegios-mayflower-y-nido-de-aguilas-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1980328311-colegio-la-maissonette-_JM</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>El Huinganal</t>
+          <t>Juan Xxiii</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5645,13 +5645,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>-12.72734632057789</v>
+        <v>-2.380543399388693</v>
       </c>
       <c r="F70" t="n">
-        <v>894500733</v>
+        <v>1225343469</v>
       </c>
       <c r="G70" t="n">
-        <v>21900</v>
+        <v>30000</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5659,59 +5659,59 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>611756561.9932473</v>
+        <v>676578223.5001392</v>
       </c>
       <c r="J70" t="n">
-        <v>709567235.0425349</v>
+        <v>941512215.0776819</v>
       </c>
       <c r="K70" t="n">
-        <v>804191653.6187876</v>
+        <v>1202930362.10953</v>
       </c>
       <c r="L70" t="n">
-        <v>27.12006447338354</v>
+        <v>55.90497182938435</v>
       </c>
       <c r="M70" t="n">
-        <v>26.0628575876082</v>
+        <v>30.14631667831308</v>
       </c>
       <c r="N70" t="n">
-        <v>445</v>
+        <v>330</v>
       </c>
       <c r="O70" t="n">
-        <v>140</v>
+        <v>240</v>
       </c>
       <c r="P70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q70" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R70" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S70" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="T70" t="n">
-        <v>-33.3405638</v>
+        <v>-33.3839207</v>
       </c>
       <c r="U70" t="n">
-        <v>-70.49693000000001</v>
+        <v>-70.5709645</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1883257409-casa-san-ramon-oriente-id-167799-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4058539148-exclusivo-condominio-el-pitreno-_JM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -5720,13 +5720,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>-13.15582650002811</v>
+        <v>-2.57127927766091</v>
       </c>
       <c r="F71" t="n">
-        <v>1053795384</v>
+        <v>2368997374</v>
       </c>
       <c r="G71" t="n">
-        <v>25800</v>
+        <v>58000</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
@@ -5734,59 +5734,59 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>610949516.5052081</v>
+        <v>1269966769.422626</v>
       </c>
       <c r="J71" t="n">
-        <v>723041599.2892851</v>
+        <v>1761788024.598945</v>
       </c>
       <c r="K71" t="n">
-        <v>958673285.6744732</v>
+        <v>2323696883.607176</v>
       </c>
       <c r="L71" t="n">
-        <v>48.09180682149695</v>
+        <v>59.81026658552875</v>
       </c>
       <c r="M71" t="n">
-        <v>45.74477942013709</v>
+        <v>34.46551690231179</v>
       </c>
       <c r="N71" t="n">
-        <v>300</v>
+        <v>4000</v>
       </c>
       <c r="O71" t="n">
-        <v>200</v>
+        <v>521</v>
       </c>
       <c r="P71" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q71" t="n">
         <v>6</v>
       </c>
       <c r="R71" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="S71" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="T71" t="n">
-        <v>-33.3925902</v>
+        <v>-33.333711</v>
       </c>
       <c r="U71" t="n">
-        <v>-70.51186079999999</v>
+        <v>-70.52004100000001</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3798822532-venta-casa-colegio-cordillera-s-carlos-apoq-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4170217018-se-vende-casa-remodelada-en-vitacura-95640-_JM</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>San Carlos De Apoquindo</t>
+          <t>Estadio Croata</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -5795,13 +5795,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>-13.36740055884638</v>
+        <v>-2.723462588366045</v>
       </c>
       <c r="F72" t="n">
-        <v>976190297</v>
+        <v>894500733</v>
       </c>
       <c r="G72" t="n">
-        <v>23900</v>
+        <v>21900</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
@@ -5809,49 +5809,49 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>624202650.4259667</v>
+        <v>604684389.3625458</v>
       </c>
       <c r="J72" t="n">
-        <v>817585586.016544</v>
+        <v>788903244.0852656</v>
       </c>
       <c r="K72" t="n">
-        <v>866900356.8057771</v>
+        <v>873015248.2889317</v>
       </c>
       <c r="L72" t="n">
-        <v>29.68468506915426</v>
+        <v>34.01315192175637</v>
       </c>
       <c r="M72" t="n">
-        <v>19.39915694407149</v>
+        <v>13.38535361673849</v>
       </c>
       <c r="N72" t="n">
-        <v>234</v>
+        <v>395</v>
       </c>
       <c r="O72" t="n">
-        <v>234</v>
+        <v>140</v>
       </c>
       <c r="P72" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q72" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R72" t="n">
         <v>2</v>
       </c>
       <c r="S72" t="n">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="T72" t="n">
-        <v>-33.3989457</v>
+        <v>-33.3826607</v>
       </c>
       <c r="U72" t="n">
-        <v>-70.5146483</v>
+        <v>-70.559969</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3847765376-gran-casa-sector-jardin-del-este-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4155694392-espectacular-casa-nueva-tahiti-_JM</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Estadio Manquehue</t>
+          <t>Juan Xxiii</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -5870,13 +5870,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>-13.94975602677535</v>
+        <v>-2.756163918921424</v>
       </c>
       <c r="F73" t="n">
-        <v>1838015204</v>
+        <v>1225343469</v>
       </c>
       <c r="G73" t="n">
-        <v>45000</v>
+        <v>30000</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
@@ -5884,59 +5884,59 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>869099831.3496712</v>
+        <v>657315118.6445516</v>
       </c>
       <c r="J73" t="n">
-        <v>1385402402.756366</v>
+        <v>968179567.4750384</v>
       </c>
       <c r="K73" t="n">
-        <v>1644754948.826403</v>
+        <v>1198658853.090883</v>
       </c>
       <c r="L73" t="n">
-        <v>55.98771273483472</v>
+        <v>55.91356734145174</v>
       </c>
       <c r="M73" t="n">
-        <v>32.67013254366569</v>
+        <v>26.56159148200489</v>
       </c>
       <c r="N73" t="n">
-        <v>842</v>
+        <v>330</v>
       </c>
       <c r="O73" t="n">
-        <v>293</v>
+        <v>240</v>
       </c>
       <c r="P73" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q73" t="n">
+        <v>4</v>
+      </c>
+      <c r="R73" t="n">
         <v>3</v>
       </c>
-      <c r="R73" t="n">
-        <v>4</v>
-      </c>
       <c r="S73" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="T73" t="n">
-        <v>-33.3916065</v>
+        <v>-33.3845648</v>
       </c>
       <c r="U73" t="n">
-        <v>-70.57754749999999</v>
+        <v>-70.5724201</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2983249392-club-de-polo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4205336556-en-condominio-con-piscina-y-quincho-_JM</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Jardín Del Este</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -5945,13 +5945,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>-14.42660555932013</v>
+        <v>-2.861600424329543</v>
       </c>
       <c r="F74" t="n">
-        <v>1429567381</v>
+        <v>935345515</v>
       </c>
       <c r="G74" t="n">
-        <v>35000</v>
+        <v>22900</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
@@ -5959,28 +5959,28 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>822658220.310781</v>
+        <v>753083946.8150852</v>
       </c>
       <c r="J74" t="n">
-        <v>948225657.2453243</v>
+        <v>875883573.6392397</v>
       </c>
       <c r="K74" t="n">
-        <v>1292770605.616946</v>
+        <v>910281226.9401067</v>
       </c>
       <c r="L74" t="n">
-        <v>49.57811273235123</v>
+        <v>17.94728030711628</v>
       </c>
       <c r="M74" t="n">
-        <v>50.76236021212652</v>
+        <v>6.788795126468671</v>
       </c>
       <c r="N74" t="n">
-        <v>337</v>
+        <v>370</v>
       </c>
       <c r="O74" t="n">
-        <v>268</v>
+        <v>230</v>
       </c>
       <c r="P74" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q74" t="n">
         <v>4</v>
@@ -5989,29 +5989,29 @@
         <v>2</v>
       </c>
       <c r="S74" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T74" t="n">
-        <v>-33.3912484</v>
+        <v>-33.4095716</v>
       </c>
       <c r="U74" t="n">
-        <v>-70.58727399999999</v>
+        <v>-70.51134</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4164894878-a-estrenar-nueva-oxford-los-dominicos-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3727379628-linda-casa-mediterranea-en-condominio-seguridad-24-horas-_JM</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Los Dominicos</t>
+          <t>La Dehesa</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6020,13 +6020,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>-14.50884871374012</v>
+        <v>-3.02230908249326</v>
       </c>
       <c r="F75" t="n">
-        <v>1347469369</v>
+        <v>1462243207</v>
       </c>
       <c r="G75" t="n">
-        <v>32990</v>
+        <v>35800</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
@@ -6034,59 +6034,59 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>759961270.8312922</v>
+        <v>866209110.4790043</v>
       </c>
       <c r="J75" t="n">
-        <v>984756043.4639397</v>
+        <v>1286901976.338854</v>
       </c>
       <c r="K75" t="n">
-        <v>1204592604.454404</v>
+        <v>1423349051.686326</v>
       </c>
       <c r="L75" t="n">
-        <v>45.15141964085785</v>
+        <v>43.29311411832199</v>
       </c>
       <c r="M75" t="n">
-        <v>36.83281031312019</v>
+        <v>13.62506499212778</v>
       </c>
       <c r="N75" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="O75" t="n">
-        <v>280</v>
+        <v>328</v>
       </c>
       <c r="P75" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q75" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R75" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="S75" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="T75" t="n">
-        <v>-33.4029151</v>
+        <v>-33.3415635</v>
       </c>
       <c r="U75" t="n">
-        <v>-70.5424204</v>
+        <v>-70.5203733</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3979950470-gran-casa-mediterranea-con-excelente-ubicacion-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3824790288-casa-en-venta-condominio4d4bestarpiscinasan-carlos-_JM</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Los Trapenses</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6095,13 +6095,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>-16.68427651323841</v>
+        <v>-3.030474492125013</v>
       </c>
       <c r="F76" t="n">
-        <v>1838015204</v>
+        <v>894500733</v>
       </c>
       <c r="G76" t="n">
-        <v>45000</v>
+        <v>21900</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
@@ -6109,49 +6109,49 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>1014723104.521324</v>
+        <v>713928682.7652264</v>
       </c>
       <c r="J76" t="n">
-        <v>1327452260.210802</v>
+        <v>839572973.5508622</v>
       </c>
       <c r="K76" t="n">
-        <v>1616539398.325197</v>
+        <v>869057688.1937656</v>
       </c>
       <c r="L76" t="n">
-        <v>45.33619112662497</v>
+        <v>18.47713186531503</v>
       </c>
       <c r="M76" t="n">
-        <v>38.4618685803525</v>
+        <v>6.542344880020155</v>
       </c>
       <c r="N76" t="n">
-        <v>864</v>
+        <v>375</v>
       </c>
       <c r="O76" t="n">
-        <v>373</v>
+        <v>178</v>
       </c>
       <c r="P76" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q76" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R76" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S76" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="T76" t="n">
-        <v>-33.327</v>
+        <v>-33.3871246</v>
       </c>
       <c r="U76" t="n">
-        <v>-70.54795799999999</v>
+        <v>-70.4957548</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3941848806-casa-de-diseno-en-sector-exclusivo-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1777531091-casa-mediterranea-remodelada-_JM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>La Llavería</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6170,13 +6170,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>-17.74660746003439</v>
+        <v>-3.172967311968318</v>
       </c>
       <c r="F77" t="n">
-        <v>2940824327</v>
+        <v>776050864</v>
       </c>
       <c r="G77" t="n">
-        <v>72000</v>
+        <v>19000</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
@@ -6184,49 +6184,49 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>1156716869.862871</v>
+        <v>497810857.5437672</v>
       </c>
       <c r="J77" t="n">
-        <v>1784060267.889923</v>
+        <v>655221638.3073243</v>
       </c>
       <c r="K77" t="n">
-        <v>2624214154.407137</v>
+        <v>755260895.5955653</v>
       </c>
       <c r="L77" t="n">
-        <v>82.25603758778466</v>
+        <v>39.29205371130374</v>
       </c>
       <c r="M77" t="n">
-        <v>64.83884428849633</v>
+        <v>18.44096999067698</v>
       </c>
       <c r="N77" t="n">
-        <v>2118</v>
+        <v>273</v>
       </c>
       <c r="O77" t="n">
-        <v>308</v>
+        <v>118</v>
       </c>
       <c r="P77" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R77" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S77" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="T77" t="n">
-        <v>-33.3724038</v>
+        <v>-33.3873026</v>
       </c>
       <c r="U77" t="n">
-        <v>-70.5645356</v>
+        <v>-70.54762890000001</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3795283994-casa-en-venta-de-3-dorm-en-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4014301174-gran-casa-con-excelente-ubicacion-_JM</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -6245,13 +6245,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>-23.02008662815424</v>
+        <v>-3.204964236609149</v>
       </c>
       <c r="F78" t="n">
-        <v>1633791293</v>
+        <v>1123231514</v>
       </c>
       <c r="G78" t="n">
-        <v>40000</v>
+        <v>27500</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
@@ -6259,49 +6259,49 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>731023191.6933835</v>
+        <v>674071443.0991799</v>
       </c>
       <c r="J78" t="n">
-        <v>811224515.5150867</v>
+        <v>934267367.0286422</v>
       </c>
       <c r="K78" t="n">
-        <v>1447046706.779603</v>
+        <v>1093288579.012422</v>
       </c>
       <c r="L78" t="n">
-        <v>88.26453113680623</v>
+        <v>44.87121681735783</v>
       </c>
       <c r="M78" t="n">
-        <v>101.3981655821416</v>
+        <v>20.2259175092824</v>
       </c>
       <c r="N78" t="n">
-        <v>501</v>
+        <v>540</v>
       </c>
       <c r="O78" t="n">
-        <v>200</v>
+        <v>248</v>
       </c>
       <c r="P78" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>4</v>
+      </c>
+      <c r="R78" t="n">
         <v>3</v>
       </c>
-      <c r="Q78" t="n">
-        <v>3</v>
-      </c>
-      <c r="R78" t="n">
-        <v>7</v>
-      </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="T78" t="n">
-        <v>-33.4005536</v>
+        <v>-33.3946444</v>
       </c>
       <c r="U78" t="n">
-        <v>-70.5314422</v>
+        <v>-70.5451887</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4170191126-moderno-y-exclusivo-departamento-90781-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4088013424-oportunidad-completamente-remodelada-_JM</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>La Llavería</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6320,13 +6320,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>-23.57320048526929</v>
+        <v>-3.288500013250268</v>
       </c>
       <c r="F79" t="n">
-        <v>2654910851</v>
+        <v>771966386</v>
       </c>
       <c r="G79" t="n">
-        <v>65000</v>
+        <v>18900</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
@@ -6334,59 +6334,59 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>890712832.6979307</v>
+        <v>566001307.129233</v>
       </c>
       <c r="J79" t="n">
-        <v>1637331824.610674</v>
+        <v>650282867.3560265</v>
       </c>
       <c r="K79" t="n">
-        <v>2268939337.375408</v>
+        <v>750581833.8208328</v>
       </c>
       <c r="L79" t="n">
-        <v>84.17514910303494</v>
+        <v>28.38465165814417</v>
       </c>
       <c r="M79" t="n">
-        <v>62.14861343889696</v>
+        <v>18.7123980582057</v>
       </c>
       <c r="N79" t="n">
-        <v>500</v>
+        <v>286</v>
       </c>
       <c r="O79" t="n">
-        <v>450</v>
+        <v>140</v>
       </c>
       <c r="P79" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q79" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R79" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S79" t="n">
-        <v>13</v>
+        <v>46</v>
       </c>
       <c r="T79" t="n">
-        <v>-33.3669086</v>
+        <v>-33.3856938</v>
       </c>
       <c r="U79" t="n">
-        <v>-70.545604</v>
+        <v>-70.5441996</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4179336334-casa-comercial-venta-las-condes-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3951874618-casa-en-vitacura-con-terreno-de-2453-m-_JM</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Las Condes</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Rotonda Atenas</t>
+          <t>Jardín Del Este</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6395,73 +6395,73 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>-29.37244195097637</v>
+        <v>-3.329276660255649</v>
       </c>
       <c r="F80" t="n">
-        <v>780000000</v>
+        <v>4288702143</v>
       </c>
       <c r="G80" t="n">
-        <v>780000000</v>
+        <v>105000</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>CLP</t>
+          <t>UF</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>369395409.6714396</v>
+        <v>1300194856.735745</v>
       </c>
       <c r="J80" t="n">
-        <v>495858183.8982863</v>
+        <v>3035151163.19799</v>
       </c>
       <c r="K80" t="n">
-        <v>634354342.7753102</v>
+        <v>4187653563.720171</v>
       </c>
       <c r="L80" t="n">
-        <v>53.4344176838716</v>
+        <v>95.13393408524841</v>
       </c>
       <c r="M80" t="n">
-        <v>57.30304053224998</v>
+        <v>41.30110536179043</v>
       </c>
       <c r="N80" t="n">
-        <v>200</v>
+        <v>2453</v>
       </c>
       <c r="O80" t="n">
-        <v>140</v>
+        <v>524</v>
       </c>
       <c r="P80" t="n">
         <v>5</v>
       </c>
       <c r="Q80" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R80" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S80" t="n">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="T80" t="n">
-        <v>-33.4184886</v>
+        <v>-33.3923595</v>
       </c>
       <c r="U80" t="n">
-        <v>-70.5638072</v>
+        <v>-70.5847479</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1949405103-entorno-natural-en-el-arrayan-para-desarrollo-inmobiliario-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2020102567-en-el-mejor-sector-de-santiago-a-pies-del-cerro-manquehue-_JM</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>El Arrayán</t>
+          <t>Estadio Manquehue</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6470,13 +6470,13 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>-39.96734705957697</v>
+        <v>-3.380765509039577</v>
       </c>
       <c r="F81" t="n">
-        <v>1960549551</v>
+        <v>1000697167</v>
       </c>
       <c r="G81" t="n">
-        <v>48000</v>
+        <v>24500</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
@@ -6484,49 +6484,49 @@
         </is>
       </c>
       <c r="I81" t="n">
-        <v>617782023.1138905</v>
+        <v>647837342.2920637</v>
       </c>
       <c r="J81" t="n">
-        <v>856905672.4415878</v>
+        <v>828645782.7383702</v>
       </c>
       <c r="K81" t="n">
-        <v>1618067086.922069</v>
+        <v>972682596.1850702</v>
       </c>
       <c r="L81" t="n">
-        <v>116.7322257253892</v>
+        <v>39.20194378103417</v>
       </c>
       <c r="M81" t="n">
-        <v>128.79409181804</v>
+        <v>20.76295901646457</v>
       </c>
       <c r="N81" t="n">
-        <v>10385</v>
+        <v>400</v>
       </c>
       <c r="O81" t="n">
-        <v>305</v>
+        <v>200</v>
       </c>
       <c r="P81" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q81" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R81" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="S81" t="n">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="T81" t="n">
-        <v>-33.3443566</v>
+        <v>-33.3869598</v>
       </c>
       <c r="U81" t="n">
-        <v>-70.4699251</v>
+        <v>-70.5764427</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2037765553-almirante-acevedo-club-de-polo-colegio-saint-george-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4125912720-casa-via-aurora-_JM</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Borde Río - Casa Piedra</t>
+          <t>Lo Curro</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6545,13 +6545,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>-42.97831305724794</v>
+        <v>-3.79801535497593</v>
       </c>
       <c r="F82" t="n">
-        <v>1143653905</v>
+        <v>3063358674</v>
       </c>
       <c r="G82" t="n">
-        <v>28000</v>
+        <v>75000</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
@@ -6559,59 +6559,59 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>619074280.6158991</v>
+        <v>1105538926.59276</v>
       </c>
       <c r="J82" t="n">
-        <v>708858468.0830567</v>
+        <v>1474211355.241034</v>
       </c>
       <c r="K82" t="n">
-        <v>838998493.4544519</v>
+        <v>3007367900.363147</v>
       </c>
       <c r="L82" t="n">
-        <v>31.02512317208919</v>
+        <v>129.006534036596</v>
       </c>
       <c r="M82" t="n">
-        <v>61.33741169697059</v>
+        <v>107.7964372685991</v>
       </c>
       <c r="N82" t="n">
-        <v>244</v>
+        <v>1000</v>
       </c>
       <c r="O82" t="n">
-        <v>128</v>
+        <v>900</v>
       </c>
       <c r="P82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="Q82" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="R82" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S82" t="n">
-        <v>72</v>
+        <v>26</v>
       </c>
       <c r="T82" t="n">
-        <v>-33.390902</v>
+        <v>-33.3673321</v>
       </c>
       <c r="U82" t="n">
-        <v>-70.5931128</v>
+        <v>-70.5469629</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4029221140-espectacular-casa-en-santa-maria-de-manquehue-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-1946224879-sector-los-trapenses-comercial-_JM</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Lo Barnechea</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Santa María De Manquehue</t>
+          <t>Los Trapenses</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6620,13 +6620,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>-45.97738450630628</v>
+        <v>-4.397192554239231</v>
       </c>
       <c r="F83" t="n">
-        <v>4901373878</v>
+        <v>2001394334</v>
       </c>
       <c r="G83" t="n">
-        <v>120000</v>
+        <v>49000</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
@@ -6634,49 +6634,49 @@
         </is>
       </c>
       <c r="I83" t="n">
-        <v>1360095591.869593</v>
+        <v>1100838383.445337</v>
       </c>
       <c r="J83" t="n">
-        <v>2424391676.054841</v>
+        <v>1457661595.523912</v>
       </c>
       <c r="K83" t="n">
-        <v>3786701995.161383</v>
+        <v>1937298146.855618</v>
       </c>
       <c r="L83" t="n">
-        <v>100.0913518743206</v>
+        <v>57.38367299919436</v>
       </c>
       <c r="M83" t="n">
-        <v>102.1692256416215</v>
+        <v>37.30171256111468</v>
       </c>
       <c r="N83" t="n">
-        <v>2000</v>
+        <v>1062</v>
       </c>
       <c r="O83" t="n">
-        <v>850</v>
+        <v>410</v>
       </c>
       <c r="P83" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Q83" t="n">
+        <v>5</v>
+      </c>
+      <c r="R83" t="n">
         <v>7</v>
       </c>
-      <c r="R83" t="n">
-        <v>6</v>
-      </c>
       <c r="S83" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="T83" t="n">
-        <v>-33.367176</v>
+        <v>-33.3474949</v>
       </c>
       <c r="U83" t="n">
-        <v>-70.5778047</v>
+        <v>-70.5421845</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-4018720458-espectacularpaseo-pie-andino-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4179281400-moderna-elegante-a-estrenar-gran-vista-desde-cada-rincon-_JM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>-47.72914926635305</v>
+        <v>-5.222834839867671</v>
       </c>
       <c r="F84" t="n">
-        <v>1756325640</v>
+        <v>2446602461</v>
       </c>
       <c r="G84" t="n">
-        <v>43000</v>
+        <v>59900</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
@@ -6709,49 +6709,49 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>771867064.6165577</v>
+        <v>1236970510.12079</v>
       </c>
       <c r="J84" t="n">
-        <v>951937590.5782057</v>
+        <v>1879594400.75236</v>
       </c>
       <c r="K84" t="n">
-        <v>1301973926.470403</v>
+        <v>2348434349.789304</v>
       </c>
       <c r="L84" t="n">
-        <v>55.68714452507958</v>
+        <v>59.13317464787187</v>
       </c>
       <c r="M84" t="n">
-        <v>84.50008250364502</v>
+        <v>30.166511456976</v>
       </c>
       <c r="N84" t="n">
-        <v>450</v>
+        <v>1400</v>
       </c>
       <c r="O84" t="n">
-        <v>280</v>
+        <v>492</v>
       </c>
       <c r="P84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q84" t="n">
         <v>5</v>
       </c>
       <c r="R84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="S84" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="T84" t="n">
-        <v>-33.3245489</v>
+        <v>-33.3377104</v>
       </c>
       <c r="U84" t="n">
-        <v>-70.53096650000001</v>
+        <v>-70.555567</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1868286737-casa-con-espectacular-terreno-lo-curro-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4198327852-espectacular-casa-remodelada-con-salida-al-sport-frances-_JM</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Lo Curro</t>
+          <t>Juan Xxiii</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6770,13 +6770,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>-57.45612747439884</v>
+        <v>-5.482806913499629</v>
       </c>
       <c r="F85" t="n">
-        <v>4901373878</v>
+        <v>1470412163</v>
       </c>
       <c r="G85" t="n">
-        <v>120000</v>
+        <v>36000</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -6784,59 +6784,59 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>1366728469.998903</v>
+        <v>798229591.4342457</v>
       </c>
       <c r="J85" t="n">
-        <v>1966890648.122933</v>
+        <v>1179994996.454232</v>
       </c>
       <c r="K85" t="n">
-        <v>3771274679.932458</v>
+        <v>1405715315.755458</v>
       </c>
       <c r="L85" t="n">
-        <v>122.251138477286</v>
+        <v>51.48205934318756</v>
       </c>
       <c r="M85" t="n">
-        <v>149.1940201493936</v>
+        <v>24.61172864448089</v>
       </c>
       <c r="N85" t="n">
-        <v>5440</v>
+        <v>640</v>
       </c>
       <c r="O85" t="n">
-        <v>450</v>
+        <v>240</v>
       </c>
       <c r="P85" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q85" t="n">
         <v>4</v>
       </c>
       <c r="R85" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T85" t="n">
-        <v>-33.367545</v>
+        <v>-33.3838555</v>
       </c>
       <c r="U85" t="n">
-        <v>-70.5564964</v>
+        <v>-70.56662470000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-1967132999-casa-en-venta-con-gran-terreno-en-lo-barnechea-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-2039833029-borderio-comoda-casa-5d-3-b-piscina-168236-_JM</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Lo Barnechea</t>
+          <t>Vitacura</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>La Dehesa</t>
+          <t>Borde Río - Casa Piedra</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6845,13 +6845,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>-69.26804911943888</v>
+        <v>-5.484116273286703</v>
       </c>
       <c r="F86" t="n">
-        <v>4697149966</v>
+        <v>1102809123</v>
       </c>
       <c r="G86" t="n">
-        <v>115000</v>
+        <v>27000</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
@@ -6859,49 +6859,49 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>1144028527.283284</v>
+        <v>705724317.5314134</v>
       </c>
       <c r="J86" t="n">
-        <v>1950449243.969325</v>
+        <v>919690698.8734571</v>
       </c>
       <c r="K86" t="n">
-        <v>3346111825.637604</v>
+        <v>1052372215.719177</v>
       </c>
       <c r="L86" t="n">
-        <v>112.9013382513301</v>
+        <v>37.69179123072325</v>
       </c>
       <c r="M86" t="n">
-        <v>140.8240040351377</v>
+        <v>19.9108705079705</v>
       </c>
       <c r="N86" t="n">
-        <v>2700</v>
+        <v>480</v>
       </c>
       <c r="O86" t="n">
-        <v>500</v>
+        <v>146</v>
       </c>
       <c r="P86" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q86" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="R86" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S86" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="T86" t="n">
-        <v>-33.352549</v>
+        <v>-33.3819761</v>
       </c>
       <c r="U86" t="n">
-        <v>-70.5198627</v>
+        <v>-70.57844969999999</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-2035145623-casa-comercial-esquina-venta-en-las-condes-mla-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-3927242992-casa-en-condominio-san-carlos-de-apoquindo-5d-5b-_JM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Alto Las Condes</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6920,13 +6920,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>-100.6274037375979</v>
+        <v>-6.038265208650159</v>
       </c>
       <c r="F87" t="n">
-        <v>1552101728</v>
+        <v>894500733</v>
       </c>
       <c r="G87" t="n">
-        <v>38000</v>
+        <v>21900</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -6934,59 +6934,59 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>515866137.4838958</v>
+        <v>661186303.7530566</v>
       </c>
       <c r="J87" t="n">
-        <v>669493630.0509378</v>
+        <v>775702099.4770254</v>
       </c>
       <c r="K87" t="n">
-        <v>878407669.8911431</v>
+        <v>847661783.0045099</v>
       </c>
       <c r="L87" t="n">
-        <v>54.15160296292343</v>
+        <v>24.03957387470965</v>
       </c>
       <c r="M87" t="n">
-        <v>131.8321875417859</v>
+        <v>15.31498156354973</v>
       </c>
       <c r="N87" t="n">
-        <v>403</v>
+        <v>372</v>
       </c>
       <c r="O87" t="n">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="P87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S87" t="n">
-        <v>54</v>
+        <v>19</v>
       </c>
       <c r="T87" t="n">
-        <v>-33.3937675</v>
+        <v>-33.3883239</v>
       </c>
       <c r="U87" t="n">
-        <v>-70.5463814</v>
+        <v>-70.49293419999999</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://www.portalinmobiliario.com/MLC-3836762818-casa-en-venta-de-6-dorm-en-vitacura-_JM</t>
+          <t>https://www.portalinmobiliario.com/MLC-4021085782-luminosa-casa-en-venta-_JM</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Vitacura</t>
+          <t>Las Condes</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Villa El Dorado</t>
+          <t>San Carlos De Apoquindo</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -6995,13 +6995,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>-114.3860034321664</v>
+        <v>-6.662507979226199</v>
       </c>
       <c r="F88" t="n">
-        <v>1470412163</v>
+        <v>976190297</v>
       </c>
       <c r="G88" t="n">
-        <v>36000</v>
+        <v>23900</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -7009,25 +7009,25 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>435823513.3491086</v>
+        <v>629930227.9641049</v>
       </c>
       <c r="J88" t="n">
-        <v>563035695.3352805</v>
+        <v>856979583.3400447</v>
       </c>
       <c r="K88" t="n">
-        <v>826378133.2094641</v>
+        <v>919093963.8796301</v>
       </c>
       <c r="L88" t="n">
-        <v>69.36587202127303</v>
+        <v>33.74219660969293</v>
       </c>
       <c r="M88" t="n">
-        <v>161.1578937503045</v>
+        <v>13.91056636324242</v>
       </c>
       <c r="N88" t="n">
-        <v>200</v>
+        <v>563</v>
       </c>
       <c r="O88" t="n">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="P88" t="n">
         <v>6</v>
@@ -7036,15 +7036,2115 @@
         <v>4</v>
       </c>
       <c r="R88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S88" t="n">
+        <v>21</v>
+      </c>
+      <c r="T88" t="n">
+        <v>-33.4060449</v>
+      </c>
+      <c r="U88" t="n">
+        <v>-70.5114827</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-3876586078-casa-en-venta-en-santa-teresita-con-piscina-_JM</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Lo Curro</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>-7.172045218697956</v>
+      </c>
+      <c r="F89" t="n">
+        <v>919007602</v>
+      </c>
+      <c r="G89" t="n">
+        <v>22500</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>520037966.4486262</v>
+      </c>
+      <c r="J89" t="n">
+        <v>728679114.6957523</v>
+      </c>
+      <c r="K89" t="n">
+        <v>866746406.3948127</v>
+      </c>
+      <c r="L89" t="n">
+        <v>47.58040033725254</v>
+      </c>
+      <c r="M89" t="n">
+        <v>26.11965726281536</v>
+      </c>
+      <c r="N89" t="n">
+        <v>280</v>
+      </c>
+      <c r="O89" t="n">
+        <v>74</v>
+      </c>
+      <c r="P89" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>4</v>
+      </c>
+      <c r="R89" t="n">
+        <v>2</v>
+      </c>
+      <c r="S89" t="n">
+        <v>4</v>
+      </c>
+      <c r="T89" t="n">
+        <v>-33.3725014</v>
+      </c>
+      <c r="U89" t="n">
+        <v>-70.5423126</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-4084847464-condominio-el-golf-la-dehesa-_JM</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>La Dehesa</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>-7.492083329280197</v>
+      </c>
+      <c r="F90" t="n">
+        <v>1196752122</v>
+      </c>
+      <c r="G90" t="n">
+        <v>29300</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>568794775.8608021</v>
+      </c>
+      <c r="J90" t="n">
+        <v>973038723.3387743</v>
+      </c>
+      <c r="K90" t="n">
+        <v>1123851250.021295</v>
+      </c>
+      <c r="L90" t="n">
+        <v>57.04361613235033</v>
+      </c>
+      <c r="M90" t="n">
+        <v>22.9912123017675</v>
+      </c>
+      <c r="N90" t="n">
+        <v>281</v>
+      </c>
+      <c r="O90" t="n">
+        <v>235</v>
+      </c>
+      <c r="P90" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>4</v>
+      </c>
+      <c r="R90" t="n">
+        <v>3</v>
+      </c>
+      <c r="S90" t="n">
+        <v>24</v>
+      </c>
+      <c r="T90" t="n">
+        <v>-33.3393451</v>
+      </c>
+      <c r="U90" t="n">
+        <v>-70.51458239999999</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-4138226282-exclusiva-mediterranea-valle-escondido-arquitecto-mardones-_JM</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Valle Escondido</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>-7.544265935693048</v>
+      </c>
+      <c r="F91" t="n">
+        <v>2797867589</v>
+      </c>
+      <c r="G91" t="n">
+        <v>68500</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>1136425687.194308</v>
+      </c>
+      <c r="J91" t="n">
+        <v>1814752154.877966</v>
+      </c>
+      <c r="K91" t="n">
+        <v>2660957860.362286</v>
+      </c>
+      <c r="L91" t="n">
+        <v>84.00773455868946</v>
+      </c>
+      <c r="M91" t="n">
+        <v>54.17353722267075</v>
+      </c>
+      <c r="N91" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O91" t="n">
+        <v>580</v>
+      </c>
+      <c r="P91" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>5</v>
+      </c>
+      <c r="R91" t="n">
+        <v>4</v>
+      </c>
+      <c r="S91" t="n">
+        <v>24</v>
+      </c>
+      <c r="T91" t="n">
+        <v>-33.3448698</v>
+      </c>
+      <c r="U91" t="n">
+        <v>-70.4937958</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-1709323389-venta-casa-san-carlos-de-apoquindo-_JM</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>San Carlos De Apoquindo</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>-7.91625935110544</v>
+      </c>
+      <c r="F92" t="n">
+        <v>916965363</v>
+      </c>
+      <c r="G92" t="n">
+        <v>22450</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>631477344.375525</v>
+      </c>
+      <c r="J92" t="n">
+        <v>805559751.3703781</v>
+      </c>
+      <c r="K92" t="n">
+        <v>853195163.8534007</v>
+      </c>
+      <c r="L92" t="n">
+        <v>27.52344802489205</v>
+      </c>
+      <c r="M92" t="n">
+        <v>13.82959010056103</v>
+      </c>
+      <c r="N92" t="n">
+        <v>400</v>
+      </c>
+      <c r="O92" t="n">
+        <v>160</v>
+      </c>
+      <c r="P92" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>3</v>
+      </c>
+      <c r="R92" t="n">
+        <v>2</v>
+      </c>
+      <c r="S92" t="n">
+        <v>32</v>
+      </c>
+      <c r="T92" t="n">
+        <v>-33.3970927</v>
+      </c>
+      <c r="U92" t="n">
+        <v>-70.50746479999999</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-1960135633-espectacular-casa-en-el-golf-_JM</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Barrio El Golf</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>-8.516828625088985</v>
+      </c>
+      <c r="F93" t="n">
+        <v>2654910851</v>
+      </c>
+      <c r="G93" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>931837464.6524274</v>
+      </c>
+      <c r="J93" t="n">
+        <v>1464672330.961733</v>
+      </c>
+      <c r="K93" t="n">
+        <v>2530167218.652893</v>
+      </c>
+      <c r="L93" t="n">
+        <v>109.1254146209597</v>
+      </c>
+      <c r="M93" t="n">
+        <v>81.26312587995248</v>
+      </c>
+      <c r="N93" t="n">
+        <v>892</v>
+      </c>
+      <c r="O93" t="n">
+        <v>871</v>
+      </c>
+      <c r="P93" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>4</v>
+      </c>
+      <c r="R93" t="n">
+        <v>4</v>
+      </c>
+      <c r="S93" t="n">
+        <v>75</v>
+      </c>
+      <c r="T93" t="n">
+        <v>-33.418827</v>
+      </c>
+      <c r="U93" t="n">
+        <v>-70.588898</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-2983249392-club-de-polo-_JM</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Jardín Del Este</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>-9.214054486392735</v>
+      </c>
+      <c r="F94" t="n">
+        <v>1429567381</v>
+      </c>
+      <c r="G94" t="n">
+        <v>35000</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>845361355.3097123</v>
+      </c>
+      <c r="J94" t="n">
+        <v>1067822349.563416</v>
+      </c>
+      <c r="K94" t="n">
+        <v>1331177647.893348</v>
+      </c>
+      <c r="L94" t="n">
+        <v>45.49598468155903</v>
+      </c>
+      <c r="M94" t="n">
+        <v>33.87689268579975</v>
+      </c>
+      <c r="N94" t="n">
+        <v>337</v>
+      </c>
+      <c r="O94" t="n">
+        <v>268</v>
+      </c>
+      <c r="P94" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>4</v>
+      </c>
+      <c r="R94" t="n">
+        <v>2</v>
+      </c>
+      <c r="S94" t="n">
+        <v>1</v>
+      </c>
+      <c r="T94" t="n">
+        <v>-33.3912484</v>
+      </c>
+      <c r="U94" t="n">
+        <v>-70.58727399999999</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-3847765376-gran-casa-sector-jardin-del-este-_JM</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Estadio Manquehue</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>-9.277564094662043</v>
+      </c>
+      <c r="F95" t="n">
+        <v>1838015204</v>
+      </c>
+      <c r="G95" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>807873618.4306388</v>
+      </c>
+      <c r="J95" t="n">
+        <v>1486990597.390032</v>
+      </c>
+      <c r="K95" t="n">
+        <v>1700058698.245542</v>
+      </c>
+      <c r="L95" t="n">
+        <v>59.99937601359873</v>
+      </c>
+      <c r="M95" t="n">
+        <v>23.60637701583907</v>
+      </c>
+      <c r="N95" t="n">
+        <v>842</v>
+      </c>
+      <c r="O95" t="n">
+        <v>293</v>
+      </c>
+      <c r="P95" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>3</v>
+      </c>
+      <c r="R95" t="n">
+        <v>4</v>
+      </c>
+      <c r="S95" t="n">
+        <v>57</v>
+      </c>
+      <c r="T95" t="n">
+        <v>-33.3916065</v>
+      </c>
+      <c r="U95" t="n">
+        <v>-70.57754749999999</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-1946991437-venta-casa-en-condominio-lo-barnechea-_JM</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>El Huinganal</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>-9.657979176160076</v>
+      </c>
+      <c r="F96" t="n">
+        <v>935345515</v>
+      </c>
+      <c r="G96" t="n">
+        <v>22900</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>635995227.7592064</v>
+      </c>
+      <c r="J96" t="n">
+        <v>738711879.5746644</v>
+      </c>
+      <c r="K96" t="n">
+        <v>864000875.4988582</v>
+      </c>
+      <c r="L96" t="n">
+        <v>30.86530135009239</v>
+      </c>
+      <c r="M96" t="n">
+        <v>26.61844771449369</v>
+      </c>
+      <c r="N96" t="n">
+        <v>445</v>
+      </c>
+      <c r="O96" t="n">
+        <v>200</v>
+      </c>
+      <c r="P96" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>4</v>
+      </c>
+      <c r="R96" t="n">
+        <v>2</v>
+      </c>
+      <c r="S96" t="n">
+        <v>16</v>
+      </c>
+      <c r="T96" t="n">
+        <v>-33.3406188</v>
+      </c>
+      <c r="U96" t="n">
+        <v>-70.4960912</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-3798064784-espectacular-casa-en-gran-vista-_JM</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Los Trapenses</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>-9.726235295040324</v>
+      </c>
+      <c r="F97" t="n">
+        <v>1960549551</v>
+      </c>
+      <c r="G97" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>1086246432.06957</v>
+      </c>
+      <c r="J97" t="n">
+        <v>1509361758.950638</v>
+      </c>
+      <c r="K97" t="n">
+        <v>1813745474.871102</v>
+      </c>
+      <c r="L97" t="n">
+        <v>48.19911717568059</v>
+      </c>
+      <c r="M97" t="n">
+        <v>29.89262112769069</v>
+      </c>
+      <c r="N97" t="n">
+        <v>1088</v>
+      </c>
+      <c r="O97" t="n">
+        <v>409</v>
+      </c>
+      <c r="P97" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>5</v>
+      </c>
+      <c r="R97" t="n">
+        <v>4</v>
+      </c>
+      <c r="S97" t="n">
+        <v>3</v>
+      </c>
+      <c r="T97" t="n">
+        <v>-33.3388513</v>
+      </c>
+      <c r="U97" t="n">
+        <v>-70.56431689999999</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-4054786240-preciosa-casa-en-los-bravos-con-maravillosa-vista-_JM</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Los Trapenses</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>-10.9009652345562</v>
+      </c>
+      <c r="F98" t="n">
+        <v>1631749054</v>
+      </c>
+      <c r="G98" t="n">
+        <v>39950</v>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I98" t="n">
+        <v>952806512.5122205</v>
+      </c>
+      <c r="J98" t="n">
+        <v>1089004684.736833</v>
+      </c>
+      <c r="K98" t="n">
+        <v>1513037031.91415</v>
+      </c>
+      <c r="L98" t="n">
+        <v>51.44427083317035</v>
+      </c>
+      <c r="M98" t="n">
+        <v>49.83857065723517</v>
+      </c>
+      <c r="N98" t="n">
+        <v>1170</v>
+      </c>
+      <c r="O98" t="n">
+        <v>315</v>
+      </c>
+      <c r="P98" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>5</v>
+      </c>
+      <c r="R98" t="n">
+        <v>2</v>
+      </c>
+      <c r="S98" t="n">
+        <v>6</v>
+      </c>
+      <c r="T98" t="n">
+        <v>-33.3165239</v>
+      </c>
+      <c r="U98" t="n">
+        <v>-70.56922299999999</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-1938489451-casa-en-condominio-colegios-mayflower-y-nido-de-aguilas-_JM</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>El Huinganal</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>-11.64159427120942</v>
+      </c>
+      <c r="F99" t="n">
+        <v>894500733</v>
+      </c>
+      <c r="G99" t="n">
+        <v>21900</v>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I99" t="n">
+        <v>631123623.0897973</v>
+      </c>
+      <c r="J99" t="n">
+        <v>724995263.9629499</v>
+      </c>
+      <c r="K99" t="n">
+        <v>810099725.8839496</v>
+      </c>
+      <c r="L99" t="n">
+        <v>24.68652026991707</v>
+      </c>
+      <c r="M99" t="n">
+        <v>23.38021742521514</v>
+      </c>
+      <c r="N99" t="n">
+        <v>445</v>
+      </c>
+      <c r="O99" t="n">
+        <v>140</v>
+      </c>
+      <c r="P99" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>5</v>
+      </c>
+      <c r="R99" t="n">
+        <v>2</v>
+      </c>
+      <c r="S99" t="n">
+        <v>16</v>
+      </c>
+      <c r="T99" t="n">
+        <v>-33.3405638</v>
+      </c>
+      <c r="U99" t="n">
+        <v>-70.49693000000001</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-3838783300-increible-casa-con-gran-jardin-mirador-san-damian-_JM</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>San Carlos De Apoquindo</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>-11.85389332094529</v>
+      </c>
+      <c r="F100" t="n">
+        <v>3676030408</v>
+      </c>
+      <c r="G100" t="n">
+        <v>90000</v>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I100" t="n">
+        <v>1100431357.187136</v>
+      </c>
+      <c r="J100" t="n">
+        <v>2270556083.760123</v>
+      </c>
+      <c r="K100" t="n">
+        <v>3406881112.038842</v>
+      </c>
+      <c r="L100" t="n">
+        <v>101.5808317331735</v>
+      </c>
+      <c r="M100" t="n">
+        <v>61.9000047738244</v>
+      </c>
+      <c r="N100" t="n">
+        <v>2577</v>
+      </c>
+      <c r="O100" t="n">
+        <v>652</v>
+      </c>
+      <c r="P100" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>3</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6</v>
+      </c>
+      <c r="S100" t="n">
+        <v>16</v>
+      </c>
+      <c r="T100" t="n">
+        <v>-33.3806006</v>
+      </c>
+      <c r="U100" t="n">
+        <v>-70.5017314</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-4170191126-moderno-y-exclusivo-departamento-90781-_JM</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Lo Curro</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>-12.52933939491104</v>
+      </c>
+      <c r="F101" t="n">
+        <v>2654910851</v>
+      </c>
+      <c r="G101" t="n">
+        <v>65000</v>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I101" t="n">
+        <v>1022881428.091227</v>
+      </c>
+      <c r="J101" t="n">
+        <v>1618159027.754086</v>
+      </c>
+      <c r="K101" t="n">
+        <v>2452166214.463298</v>
+      </c>
+      <c r="L101" t="n">
+        <v>88.32783192859841</v>
+      </c>
+      <c r="M101" t="n">
+        <v>64.06983525499763</v>
+      </c>
+      <c r="N101" t="n">
+        <v>500</v>
+      </c>
+      <c r="O101" t="n">
+        <v>450</v>
+      </c>
+      <c r="P101" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>5</v>
+      </c>
+      <c r="R101" t="n">
+        <v>4</v>
+      </c>
+      <c r="S101" t="n">
+        <v>13</v>
+      </c>
+      <c r="T101" t="n">
+        <v>-33.3669086</v>
+      </c>
+      <c r="U101" t="n">
+        <v>-70.545604</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-3798822532-venta-casa-colegio-cordillera-s-carlos-apoq-las-condes-_JM</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>San Carlos De Apoquindo</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>-13.92399469612389</v>
+      </c>
+      <c r="F102" t="n">
+        <v>976190297</v>
+      </c>
+      <c r="G102" t="n">
+        <v>23900</v>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>620958740.2227677</v>
+      </c>
+      <c r="J102" t="n">
+        <v>758949962.4140646</v>
+      </c>
+      <c r="K102" t="n">
+        <v>870514144.4872314</v>
+      </c>
+      <c r="L102" t="n">
+        <v>32.88166764916608</v>
+      </c>
+      <c r="M102" t="n">
+        <v>28.62380200862496</v>
+      </c>
+      <c r="N102" t="n">
+        <v>234</v>
+      </c>
+      <c r="O102" t="n">
+        <v>234</v>
+      </c>
+      <c r="P102" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>4</v>
+      </c>
+      <c r="R102" t="n">
+        <v>2</v>
+      </c>
+      <c r="S102" t="n">
+        <v>28</v>
+      </c>
+      <c r="T102" t="n">
+        <v>-33.3989457</v>
+      </c>
+      <c r="U102" t="n">
+        <v>-70.5146483</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-4179336334-casa-comercial-venta-las-condes-_JM</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Rotonda Atenas</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>-14.45771878431037</v>
+      </c>
+      <c r="F103" t="n">
+        <v>780000000</v>
+      </c>
+      <c r="G103" t="n">
+        <v>780000000</v>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>CLP</t>
+        </is>
+      </c>
+      <c r="I103" t="n">
+        <v>365993633.4263675</v>
+      </c>
+      <c r="J103" t="n">
+        <v>460520630.0149742</v>
+      </c>
+      <c r="K103" t="n">
+        <v>713419222.3687006</v>
+      </c>
+      <c r="L103" t="n">
+        <v>75.44191645248037</v>
+      </c>
+      <c r="M103" t="n">
+        <v>69.37351969978795</v>
+      </c>
+      <c r="N103" t="n">
+        <v>200</v>
+      </c>
+      <c r="O103" t="n">
+        <v>140</v>
+      </c>
+      <c r="P103" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>5</v>
+      </c>
+      <c r="R103" t="n">
+        <v>4</v>
+      </c>
+      <c r="S103" t="n">
+        <v>77</v>
+      </c>
+      <c r="T103" t="n">
+        <v>-33.4184886</v>
+      </c>
+      <c r="U103" t="n">
+        <v>-70.5638072</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-1883257409-casa-san-ramon-oriente-id-167799-_JM</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>San Carlos De Apoquindo</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>-16.25003694187297</v>
+      </c>
+      <c r="F104" t="n">
+        <v>1053795384</v>
+      </c>
+      <c r="G104" t="n">
+        <v>25800</v>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I104" t="n">
+        <v>609500591.4025961</v>
+      </c>
+      <c r="J104" t="n">
+        <v>763635284.0293517</v>
+      </c>
+      <c r="K104" t="n">
+        <v>929704368.2440537</v>
+      </c>
+      <c r="L104" t="n">
+        <v>41.9315062488849</v>
+      </c>
+      <c r="M104" t="n">
+        <v>37.99720966789369</v>
+      </c>
+      <c r="N104" t="n">
+        <v>300</v>
+      </c>
+      <c r="O104" t="n">
+        <v>200</v>
+      </c>
+      <c r="P104" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>6</v>
+      </c>
+      <c r="R104" t="n">
+        <v>2</v>
+      </c>
+      <c r="S104" t="n">
+        <v>16</v>
+      </c>
+      <c r="T104" t="n">
+        <v>-33.3925902</v>
+      </c>
+      <c r="U104" t="n">
+        <v>-70.51186079999999</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-3979950470-gran-casa-mediterranea-con-excelente-ubicacion-_JM</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Los Trapenses</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>-18.05113479312272</v>
+      </c>
+      <c r="F105" t="n">
+        <v>1838015204</v>
+      </c>
+      <c r="G105" t="n">
+        <v>45000</v>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I105" t="n">
+        <v>1009298616.429099</v>
+      </c>
+      <c r="J105" t="n">
+        <v>1332182624.299147</v>
+      </c>
+      <c r="K105" t="n">
+        <v>1597541122.797201</v>
+      </c>
+      <c r="L105" t="n">
+        <v>44.15629626437841</v>
+      </c>
+      <c r="M105" t="n">
+        <v>37.97021297789171</v>
+      </c>
+      <c r="N105" t="n">
+        <v>864</v>
+      </c>
+      <c r="O105" t="n">
+        <v>373</v>
+      </c>
+      <c r="P105" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>3</v>
+      </c>
+      <c r="R105" t="n">
+        <v>3</v>
+      </c>
+      <c r="S105" t="n">
+        <v>23</v>
+      </c>
+      <c r="T105" t="n">
+        <v>-33.327</v>
+      </c>
+      <c r="U105" t="n">
+        <v>-70.54795799999999</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-1955676239-casa-de-lujo-en-venta-en-cerro-san-luis-_JM</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Barrio El Golf</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>-18.3744267177908</v>
+      </c>
+      <c r="F106" t="n">
+        <v>1307033034</v>
+      </c>
+      <c r="G106" t="n">
+        <v>32000</v>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I106" t="n">
+        <v>736491720.4433688</v>
+      </c>
+      <c r="J106" t="n">
+        <v>893787764.2884158</v>
+      </c>
+      <c r="K106" t="n">
+        <v>1142804656.238244</v>
+      </c>
+      <c r="L106" t="n">
+        <v>45.45966638045883</v>
+      </c>
+      <c r="M106" t="n">
+        <v>46.23527936082088</v>
+      </c>
+      <c r="N106" t="n">
+        <v>317</v>
+      </c>
+      <c r="O106" t="n">
+        <v>173</v>
+      </c>
+      <c r="P106" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>3</v>
+      </c>
+      <c r="R106" t="n">
+        <v>2</v>
+      </c>
+      <c r="S106" t="n">
+        <v>41</v>
+      </c>
+      <c r="T106" t="n">
+        <v>-33.4115008</v>
+      </c>
+      <c r="U106" t="n">
+        <v>-70.59783849999999</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-3795283994-casa-en-venta-de-3-dorm-en-las-condes-_JM</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Los Dominicos</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>-20.32911794450508</v>
+      </c>
+      <c r="F107" t="n">
+        <v>1633791293</v>
+      </c>
+      <c r="G107" t="n">
+        <v>40000</v>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I107" t="n">
+        <v>745615969.9204717</v>
+      </c>
+      <c r="J107" t="n">
+        <v>870015276.6747146</v>
+      </c>
+      <c r="K107" t="n">
+        <v>1456924861.269585</v>
+      </c>
+      <c r="L107" t="n">
+        <v>81.75820705905386</v>
+      </c>
+      <c r="M107" t="n">
+        <v>87.78880518564154</v>
+      </c>
+      <c r="N107" t="n">
+        <v>501</v>
+      </c>
+      <c r="O107" t="n">
+        <v>200</v>
+      </c>
+      <c r="P107" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>3</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7</v>
+      </c>
+      <c r="S107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
+        <v>-33.4005536</v>
+      </c>
+      <c r="U107" t="n">
+        <v>-70.5314422</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-4029221140-espectacular-casa-en-santa-maria-de-manquehue-_JM</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Santa María De Manquehue</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>-22.50759335876795</v>
+      </c>
+      <c r="F108" t="n">
+        <v>4901373878</v>
+      </c>
+      <c r="G108" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I108" t="n">
+        <v>1377245208.903442</v>
+      </c>
+      <c r="J108" t="n">
+        <v>2364902496.48933</v>
+      </c>
+      <c r="K108" t="n">
+        <v>4369091240.75883</v>
+      </c>
+      <c r="L108" t="n">
+        <v>126.5103333561003</v>
+      </c>
+      <c r="M108" t="n">
+        <v>107.254797408182</v>
+      </c>
+      <c r="N108" t="n">
+        <v>2000</v>
+      </c>
+      <c r="O108" t="n">
+        <v>850</v>
+      </c>
+      <c r="P108" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>7</v>
+      </c>
+      <c r="R108" t="n">
+        <v>6</v>
+      </c>
+      <c r="S108" t="n">
+        <v>18</v>
+      </c>
+      <c r="T108" t="n">
+        <v>-33.367176</v>
+      </c>
+      <c r="U108" t="n">
+        <v>-70.5778047</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-3941848806-casa-de-diseno-en-sector-exclusivo-_JM</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Lo Curro</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>-24.25461013520286</v>
+      </c>
+      <c r="F109" t="n">
+        <v>2940824327</v>
+      </c>
+      <c r="G109" t="n">
+        <v>72000</v>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I109" t="n">
+        <v>1126653972.506484</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1697732058.110295</v>
+      </c>
+      <c r="K109" t="n">
+        <v>2529046035.164992</v>
+      </c>
+      <c r="L109" t="n">
+        <v>82.60385117657951</v>
+      </c>
+      <c r="M109" t="n">
+        <v>73.22075724206807</v>
+      </c>
+      <c r="N109" t="n">
+        <v>2118</v>
+      </c>
+      <c r="O109" t="n">
+        <v>308</v>
+      </c>
+      <c r="P109" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>4</v>
+      </c>
+      <c r="R109" t="n">
+        <v>4</v>
+      </c>
+      <c r="S109" t="n">
+        <v>36</v>
+      </c>
+      <c r="T109" t="n">
+        <v>-33.3724038</v>
+      </c>
+      <c r="U109" t="n">
+        <v>-70.5645356</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-1949405103-entorno-natural-en-el-arrayan-para-desarrollo-inmobiliario-_JM</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>El Arrayán</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>-42.86906409984928</v>
+      </c>
+      <c r="F110" t="n">
+        <v>1960549551</v>
+      </c>
+      <c r="G110" t="n">
+        <v>48000</v>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I110" t="n">
+        <v>619994800.3877194</v>
+      </c>
+      <c r="J110" t="n">
+        <v>788006729.3203764</v>
+      </c>
+      <c r="K110" t="n">
+        <v>1622738441.096522</v>
+      </c>
+      <c r="L110" t="n">
+        <v>127.25064436615</v>
+      </c>
+      <c r="M110" t="n">
+        <v>148.7985797647812</v>
+      </c>
+      <c r="N110" t="n">
+        <v>10385</v>
+      </c>
+      <c r="O110" t="n">
+        <v>305</v>
+      </c>
+      <c r="P110" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>5</v>
+      </c>
+      <c r="R110" t="n">
+        <v>12</v>
+      </c>
+      <c r="S110" t="n">
+        <v>34</v>
+      </c>
+      <c r="T110" t="n">
+        <v>-33.3443566</v>
+      </c>
+      <c r="U110" t="n">
+        <v>-70.4699251</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-2037765553-almirante-acevedo-club-de-polo-colegio-saint-george-_JM</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Borde Río - Casa Piedra</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>-47.49820330381627</v>
+      </c>
+      <c r="F111" t="n">
+        <v>1143653905</v>
+      </c>
+      <c r="G111" t="n">
+        <v>28000</v>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I111" t="n">
+        <v>593328236.8654171</v>
+      </c>
+      <c r="J111" t="n">
+        <v>735774311.6215953</v>
+      </c>
+      <c r="K111" t="n">
+        <v>794174326.6087201</v>
+      </c>
+      <c r="L111" t="n">
+        <v>27.29724136476743</v>
+      </c>
+      <c r="M111" t="n">
+        <v>55.43542183192922</v>
+      </c>
+      <c r="N111" t="n">
+        <v>244</v>
+      </c>
+      <c r="O111" t="n">
+        <v>128</v>
+      </c>
+      <c r="P111" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>3</v>
+      </c>
+      <c r="R111" t="n">
+        <v>2</v>
+      </c>
+      <c r="S111" t="n">
+        <v>72</v>
+      </c>
+      <c r="T111" t="n">
+        <v>-33.390902</v>
+      </c>
+      <c r="U111" t="n">
+        <v>-70.5931128</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-4018720458-espectacularpaseo-pie-andino-_JM</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Los Trapenses</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>-49.32792508024178</v>
+      </c>
+      <c r="F112" t="n">
+        <v>1756325640</v>
+      </c>
+      <c r="G112" t="n">
+        <v>43000</v>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I112" t="n">
+        <v>745885541.1670233</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1005661404.444686</v>
+      </c>
+      <c r="K112" t="n">
+        <v>1260253735.854618</v>
+      </c>
+      <c r="L112" t="n">
+        <v>51.14725417663038</v>
+      </c>
+      <c r="M112" t="n">
+        <v>74.64383461845404</v>
+      </c>
+      <c r="N112" t="n">
+        <v>450</v>
+      </c>
+      <c r="O112" t="n">
+        <v>280</v>
+      </c>
+      <c r="P112" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>5</v>
+      </c>
+      <c r="R112" t="n">
+        <v>2</v>
+      </c>
+      <c r="S112" t="n">
+        <v>19</v>
+      </c>
+      <c r="T112" t="n">
+        <v>-33.3245489</v>
+      </c>
+      <c r="U112" t="n">
+        <v>-70.53096650000001</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-1868286737-casa-con-espectacular-terreno-lo-curro-_JM</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Lo Curro</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>-65.26341209696564</v>
+      </c>
+      <c r="F113" t="n">
+        <v>4901373878</v>
+      </c>
+      <c r="G113" t="n">
+        <v>120000</v>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I113" t="n">
+        <v>1282967227.495877</v>
+      </c>
+      <c r="J113" t="n">
+        <v>1944647061.03457</v>
+      </c>
+      <c r="K113" t="n">
+        <v>3632230852.725478</v>
+      </c>
+      <c r="L113" t="n">
+        <v>120.8066837578111</v>
+      </c>
+      <c r="M113" t="n">
+        <v>152.0443928469172</v>
+      </c>
+      <c r="N113" t="n">
+        <v>5440</v>
+      </c>
+      <c r="O113" t="n">
+        <v>450</v>
+      </c>
+      <c r="P113" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>4</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="n">
+        <v>-33.367545</v>
+      </c>
+      <c r="U113" t="n">
+        <v>-70.5564964</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-1967132999-casa-en-venta-con-gran-terreno-en-lo-barnechea-_JM</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Lo Barnechea</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>La Dehesa</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>-81.9414708830118</v>
+      </c>
+      <c r="F114" t="n">
+        <v>4697149966</v>
+      </c>
+      <c r="G114" t="n">
+        <v>115000</v>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I114" t="n">
+        <v>1148998369.063724</v>
+      </c>
+      <c r="J114" t="n">
+        <v>1970573076.817892</v>
+      </c>
+      <c r="K114" t="n">
+        <v>3082433402.030797</v>
+      </c>
+      <c r="L114" t="n">
+        <v>98.11536835209435</v>
+      </c>
+      <c r="M114" t="n">
+        <v>138.3646676826125</v>
+      </c>
+      <c r="N114" t="n">
+        <v>2700</v>
+      </c>
+      <c r="O114" t="n">
+        <v>500</v>
+      </c>
+      <c r="P114" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>5</v>
+      </c>
+      <c r="R114" t="n">
+        <v>4</v>
+      </c>
+      <c r="S114" t="n">
+        <v>36</v>
+      </c>
+      <c r="T114" t="n">
+        <v>-33.352549</v>
+      </c>
+      <c r="U114" t="n">
+        <v>-70.5198627</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-2035145623-casa-comercial-esquina-venta-en-las-condes-mla-_JM</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Las Condes</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Alto Las Condes</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>-95.39648270504495</v>
+      </c>
+      <c r="F115" t="n">
+        <v>1552101728</v>
+      </c>
+      <c r="G115" t="n">
+        <v>38000</v>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I115" t="n">
+        <v>560535318.9984958</v>
+      </c>
+      <c r="J115" t="n">
+        <v>691748945.2798882</v>
+      </c>
+      <c r="K115" t="n">
+        <v>892197565.0537406</v>
+      </c>
+      <c r="L115" t="n">
+        <v>47.94546465423971</v>
+      </c>
+      <c r="M115" t="n">
+        <v>124.3735590188728</v>
+      </c>
+      <c r="N115" t="n">
+        <v>403</v>
+      </c>
+      <c r="O115" t="n">
+        <v>184</v>
+      </c>
+      <c r="P115" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>4</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0</v>
+      </c>
+      <c r="S115" t="n">
+        <v>54</v>
+      </c>
+      <c r="T115" t="n">
+        <v>-33.3937675</v>
+      </c>
+      <c r="U115" t="n">
+        <v>-70.5463814</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>https://www.portalinmobiliario.com/MLC-3836762818-casa-en-venta-de-6-dorm-en-vitacura-_JM</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Vitacura</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Villa El Dorado</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>sobrevalorada</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>-105.1645975376665</v>
+      </c>
+      <c r="F116" t="n">
+        <v>1470412163</v>
+      </c>
+      <c r="G116" t="n">
+        <v>36000</v>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>UF</t>
+        </is>
+      </c>
+      <c r="I116" t="n">
+        <v>420140006.0138393</v>
+      </c>
+      <c r="J116" t="n">
+        <v>614220962.4269387</v>
+      </c>
+      <c r="K116" t="n">
+        <v>824469159.8717283</v>
+      </c>
+      <c r="L116" t="n">
+        <v>65.82796397249039</v>
+      </c>
+      <c r="M116" t="n">
+        <v>139.3946564750963</v>
+      </c>
+      <c r="N116" t="n">
+        <v>200</v>
+      </c>
+      <c r="O116" t="n">
+        <v>80</v>
+      </c>
+      <c r="P116" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>4</v>
+      </c>
+      <c r="R116" t="n">
+        <v>4</v>
+      </c>
+      <c r="S116" t="n">
         <v>50</v>
       </c>
-      <c r="T88" t="n">
+      <c r="T116" t="n">
         <v>-33.3919203</v>
       </c>
-      <c r="U88" t="n">
+      <c r="U116" t="n">
         <v>-70.56255350000001</v>
       </c>
     </row>

--- a/casas_candidatas.xlsx
+++ b/casas_candidatas.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
